--- a/DCU_itk库移植与混合精度改造.xlsx
+++ b/DCU_itk库移植与混合精度改造.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCU能否对比" sheetId="1" r:id="Rd6cf612a5762428e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="2" r:id="R183f89ad82df4434"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="Ra38b378962084d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCU能否对比" sheetId="1" r:id="Rfba8ffa8b5ac46e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计摘要" sheetId="2" r:id="R22608a3405234263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="3" r:id="Rf1a30b6e2d864036"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1112,22 +1112,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G3" s="111" t="n">
-        <x:v>16.6986266136</x:v>
+        <x:v>16.7551226139</x:v>
       </x:c>
       <x:c r="H3" s="111" t="n">
-        <x:v>0.21751537323</x:v>
+        <x:v>0.216934013367</x:v>
       </x:c>
       <x:c r="I3" s="111" t="n">
-        <x:v>0.217458152771</x:v>
+        <x:v>0.217103481293</x:v>
       </x:c>
       <x:c r="J3" s="111" t="n">
-        <x:v>1.0002631331972192</x:v>
+        <x:v>0.9992194140554969</x:v>
       </x:c>
       <x:c r="K3" s="111" t="n">
         <x:v>4.1071645572</x:v>
       </x:c>
       <x:c r="L3" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M3" s="7" t="str">
         <x:v>混合精度已进入实现路径：档C：ON+float 时内部使用 FP64 迭代/缓冲，输出再转回 float；OFF 不覆盖官方路径。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -1156,22 +1156,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G4" s="111" t="n">
-        <x:v>13.0068173885</x:v>
+        <x:v>13.0097884178</x:v>
       </x:c>
       <x:c r="H4" s="111" t="n">
-        <x:v>0.217412424088</x:v>
+        <x:v>0.21747546196</x:v>
       </x:c>
       <x:c r="I4" s="111" t="n">
-        <x:v>0.217868185043</x:v>
+        <x:v>0.216662025452</x:v>
       </x:c>
       <x:c r="J4" s="111" t="n">
-        <x:v>0.9979080885310994</x:v>
+        <x:v>1.0037544027676424</x:v>
       </x:c>
       <x:c r="K4" s="111" t="n">
         <x:v>3.33930030245</x:v>
       </x:c>
       <x:c r="L4" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M4" s="7" t="str">
         <x:v>混合精度已进入实现路径：档C：ON+float 时内部使用 FP64 迭代/缓冲，输出再转回 float；OFF 不覆盖官方路径。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -1200,16 +1200,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G5" s="111" t="n">
-        <x:v>36.8579905987</x:v>
+        <x:v>36.9774539471</x:v>
       </x:c>
       <x:c r="H5" s="111" t="n">
-        <x:v>0.218008756638</x:v>
+        <x:v>0.218014860153</x:v>
       </x:c>
       <x:c r="I5" s="111" t="n">
-        <x:v>0.218806123734</x:v>
+        <x:v>0.218015193939</x:v>
       </x:c>
       <x:c r="J5" s="111" t="n">
-        <x:v>0.9963558282446915</x:v>
+        <x:v>0.9999984689782672</x:v>
       </x:c>
       <x:c r="K5" s="111" t="n">
         <x:v>2.75805494515</x:v>
@@ -1244,22 +1244,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G6" s="111" t="n">
-        <x:v>35.8346711636</x:v>
+        <x:v>35.8092115402</x:v>
       </x:c>
       <x:c r="H6" s="111" t="n">
-        <x:v>0.218348360062</x:v>
+        <x:v>0.217504167557</x:v>
       </x:c>
       <x:c r="I6" s="111" t="n">
-        <x:v>0.218392801285</x:v>
+        <x:v>0.217347383499</x:v>
       </x:c>
       <x:c r="J6" s="111" t="n">
-        <x:v>0.9997965078393679</x:v>
+        <x:v>1.0007213524058858</x:v>
       </x:c>
       <x:c r="K6" s="111" t="n">
         <x:v>2.66192833931</x:v>
       </x:c>
       <x:c r="L6" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M6" s="7" t="str">
         <x:v>混合精度已进入实现路径：档C：ON+float 时内部使用 FP64 迭代/缓冲，输出再转回 float；OFF 不覆盖官方路径。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -1288,22 +1288,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G7" s="111" t="n">
-        <x:v>0.174873034159</x:v>
+        <x:v>8.720006</x:v>
       </x:c>
       <x:c r="H7" s="111" t="n">
-        <x:v>0.0120689868927</x:v>
+        <x:v>1.244804</x:v>
       </x:c>
       <x:c r="I7" s="111" t="n">
-        <x:v>0.0120539665222</x:v>
+        <x:v>1.254793</x:v>
       </x:c>
       <x:c r="J7" s="111" t="n">
-        <x:v>1.0012460935968535</x:v>
+        <x:v>0.9920393244144652</x:v>
       </x:c>
       <x:c r="K7" s="111" t="n">
-        <x:v>2.48402555752</x:v>
+        <x:v>2.36861246233</x:v>
       </x:c>
       <x:c r="L7" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M7" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（共享后端；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -1332,22 +1332,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G8" s="111" t="n">
-        <x:v>728.071411</x:v>
+        <x:v>747.529608</x:v>
       </x:c>
       <x:c r="H8" s="111" t="n">
-        <x:v>3604.771044</x:v>
+        <x:v>3627.556588</x:v>
       </x:c>
       <x:c r="I8" s="111" t="n">
-        <x:v>3591.086106</x:v>
+        <x:v>3628.421911</x:v>
       </x:c>
       <x:c r="J8" s="111" t="n">
-        <x:v>1.003810807537345</x:v>
+        <x:v>0.9997615153305693</x:v>
       </x:c>
       <x:c r="K8" s="111" t="n">
         <x:v>0.0000768296111298</x:v>
       </x:c>
       <x:c r="L8" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -1376,16 +1376,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G9" s="111" t="n">
-        <x:v>1.389768</x:v>
+        <x:v>1.463134</x:v>
       </x:c>
       <x:c r="H9" s="111" t="n">
-        <x:v>0.156143</x:v>
+        <x:v>0.15488</x:v>
       </x:c>
       <x:c r="I9" s="111" t="n">
-        <x:v>0.153103</x:v>
+        <x:v>0.1519</x:v>
       </x:c>
       <x:c r="J9" s="111" t="n">
-        <x:v>1.0198559139925412</x:v>
+        <x:v>1.0196181698485844</x:v>
       </x:c>
       <x:c r="K9" s="111" t="n">
         <x:v>0</x:v>
@@ -1420,16 +1420,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G10" s="111" t="n">
-        <x:v>1.210344</x:v>
+        <x:v>1.199134</x:v>
       </x:c>
       <x:c r="H10" s="111" t="n">
-        <x:v>0.225344</x:v>
+        <x:v>0.227011</x:v>
       </x:c>
       <x:c r="I10" s="111" t="n">
-        <x:v>0.219394</x:v>
+        <x:v>0.219911</x:v>
       </x:c>
       <x:c r="J10" s="111" t="n">
-        <x:v>1.0271201582540999</x:v>
+        <x:v>1.0322857883416472</x:v>
       </x:c>
       <x:c r="K10" s="111" t="n">
         <x:v>5.48032443191e-18</x:v>
@@ -1464,16 +1464,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G11" s="111" t="n">
-        <x:v>3.683784</x:v>
+        <x:v>3.41004</x:v>
       </x:c>
       <x:c r="H11" s="111" t="n">
-        <x:v>0.410988</x:v>
+        <x:v>0.30106</x:v>
       </x:c>
       <x:c r="I11" s="111" t="n">
-        <x:v>0.317276</x:v>
+        <x:v>0.300901</x:v>
       </x:c>
       <x:c r="J11" s="111" t="n">
-        <x:v>1.2953642885059067</x:v>
+        <x:v>1.0005284129996246</x:v>
       </x:c>
       <x:c r="K11" s="111" t="n">
         <x:v>0</x:v>
@@ -1508,22 +1508,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G12" s="111" t="n">
-        <x:v>4.768775</x:v>
+        <x:v>3.55927</x:v>
       </x:c>
       <x:c r="H12" s="111" t="n">
-        <x:v>0.471249</x:v>
+        <x:v>0.337551</x:v>
       </x:c>
       <x:c r="I12" s="111" t="n">
-        <x:v>0.364868</x:v>
+        <x:v>0.338321</x:v>
       </x:c>
       <x:c r="J12" s="111" t="n">
-        <x:v>1.291560235482421</x:v>
+        <x:v>0.9977240549655505</x:v>
       </x:c>
       <x:c r="K12" s="111" t="n">
         <x:v>4.11893136566e-8</x:v>
       </x:c>
       <x:c r="L12" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M12" s="7" t="str">
         <x:v>混合精度已进入实现路径：档C：ON+float 时内部使用 FP64 迭代/缓冲，输出再转回 float；OFF 不覆盖官方路径。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -1552,16 +1552,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G13" s="111" t="n">
-        <x:v>8.01766</x:v>
+        <x:v>8.065434</x:v>
       </x:c>
       <x:c r="H13" s="111" t="n">
-        <x:v>0.414588</x:v>
+        <x:v>0.308011</x:v>
       </x:c>
       <x:c r="I13" s="111" t="n">
-        <x:v>0.329476</x:v>
+        <x:v>0.30291</x:v>
       </x:c>
       <x:c r="J13" s="111" t="n">
-        <x:v>1.2583253408442496</x:v>
+        <x:v>1.0168399854742332</x:v>
       </x:c>
       <x:c r="K13" s="111" t="n">
         <x:v>0</x:v>
@@ -1596,16 +1596,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G14" s="111" t="n">
-        <x:v>1.48887</x:v>
+        <x:v>1.347466</x:v>
       </x:c>
       <x:c r="H14" s="111" t="n">
-        <x:v>2.381617</x:v>
+        <x:v>2.139031</x:v>
       </x:c>
       <x:c r="I14" s="111" t="n">
-        <x:v>2.307806</x:v>
+        <x:v>2.107181</x:v>
       </x:c>
       <x:c r="J14" s="111" t="n">
-        <x:v>1.0319831909614587</x:v>
+        <x:v>1.01511498063052</x:v>
       </x:c>
       <x:c r="K14" s="111" t="n">
         <x:v>2.907559689e-15</x:v>
@@ -1640,16 +1640,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G15" s="111" t="n">
-        <x:v>2.655313</x:v>
+        <x:v>2.307284</x:v>
       </x:c>
       <x:c r="H15" s="111" t="n">
-        <x:v>3.209664</x:v>
+        <x:v>2.825464</x:v>
       </x:c>
       <x:c r="I15" s="111" t="n">
-        <x:v>3.154323</x:v>
+        <x:v>2.801054</x:v>
       </x:c>
       <x:c r="J15" s="111" t="n">
-        <x:v>1.017544493699599</x:v>
+        <x:v>1.0087145767271892</x:v>
       </x:c>
       <x:c r="K15" s="111" t="n">
         <x:v>6.24204321668e-15</x:v>
@@ -1684,16 +1684,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G16" s="111" t="n">
-        <x:v>3.737755</x:v>
+        <x:v>3.428786</x:v>
       </x:c>
       <x:c r="H16" s="111" t="n">
-        <x:v>4.562121</x:v>
+        <x:v>4.129269</x:v>
       </x:c>
       <x:c r="I16" s="111" t="n">
-        <x:v>4.50146</x:v>
+        <x:v>4.093049</x:v>
       </x:c>
       <x:c r="J16" s="111" t="n">
-        <x:v>1.013475850057537</x:v>
+        <x:v>1.0088491488863192</x:v>
       </x:c>
       <x:c r="K16" s="111" t="n">
         <x:v>0</x:v>
@@ -1728,16 +1728,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G17" s="111" t="n">
-        <x:v>2.783736</x:v>
+        <x:v>2.493858</x:v>
       </x:c>
       <x:c r="H17" s="111" t="n">
-        <x:v>3.343367</x:v>
+        <x:v>2.935267</x:v>
       </x:c>
       <x:c r="I17" s="111" t="n">
-        <x:v>3.281395</x:v>
+        <x:v>2.911696</x:v>
       </x:c>
       <x:c r="J17" s="111" t="n">
-        <x:v>1.0188858701863082</x:v>
+        <x:v>1.0080952819250362</x:v>
       </x:c>
       <x:c r="K17" s="111" t="n">
         <x:v>6.24204321668e-15</x:v>
@@ -1772,16 +1772,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G18" s="111" t="n">
-        <x:v>2.783736</x:v>
+        <x:v>2.493858</x:v>
       </x:c>
       <x:c r="H18" s="111" t="n">
-        <x:v>3.343367</x:v>
+        <x:v>2.935267</x:v>
       </x:c>
       <x:c r="I18" s="111" t="n">
-        <x:v>3.281395</x:v>
+        <x:v>2.911696</x:v>
       </x:c>
       <x:c r="J18" s="111" t="n">
-        <x:v>1.0188858701863082</x:v>
+        <x:v>1.0080952819250362</x:v>
       </x:c>
       <x:c r="K18" s="111" t="n">
         <x:v>6.24204321668e-15</x:v>
@@ -1816,22 +1816,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G19" s="111" t="n">
-        <x:v>2.51465</x:v>
+        <x:v>2.234093</x:v>
       </x:c>
       <x:c r="H19" s="111" t="n">
-        <x:v>3.138712</x:v>
+        <x:v>2.729293</x:v>
       </x:c>
       <x:c r="I19" s="111" t="n">
-        <x:v>3.062871</x:v>
+        <x:v>2.735652</x:v>
       </x:c>
       <x:c r="J19" s="111" t="n">
-        <x:v>1.0247614084954932</x:v>
+        <x:v>0.9976755084345524</x:v>
       </x:c>
       <x:c r="K19" s="111" t="n">
         <x:v>2.7323739549e-15</x:v>
       </x:c>
       <x:c r="L19" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M19" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -1860,22 +1860,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G20" s="111" t="n">
-        <x:v>1.49465</x:v>
+        <x:v>1.349036</x:v>
       </x:c>
       <x:c r="H20" s="111" t="n">
-        <x:v>2.355327</x:v>
+        <x:v>2.09567</x:v>
       </x:c>
       <x:c r="I20" s="111" t="n">
-        <x:v>2.309086</x:v>
+        <x:v>2.105121</x:v>
       </x:c>
       <x:c r="J20" s="111" t="n">
-        <x:v>1.0200256724955241</x:v>
+        <x:v>0.9955104718446114</x:v>
       </x:c>
       <x:c r="K20" s="111" t="n">
         <x:v>2.82248488104e-15</x:v>
       </x:c>
       <x:c r="L20" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M20" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -1904,16 +1904,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G21" s="111" t="n">
-        <x:v>1.50931</x:v>
+        <x:v>1.406677</x:v>
       </x:c>
       <x:c r="H21" s="111" t="n">
-        <x:v>2.346787</x:v>
+        <x:v>2.109741</x:v>
       </x:c>
       <x:c r="I21" s="111" t="n">
-        <x:v>2.293636</x:v>
+        <x:v>2.07481</x:v>
       </x:c>
       <x:c r="J21" s="111" t="n">
-        <x:v>1.023173249809473</x:v>
+        <x:v>1.0168357584549912</x:v>
       </x:c>
       <x:c r="K21" s="111" t="n">
         <x:v>2.666419982e-15</x:v>
@@ -1948,13 +1948,13 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G22" s="111" t="n">
-        <x:v>3.858177</x:v>
+        <x:v>3.09457</x:v>
       </x:c>
       <x:c r="H22" s="111" t="n">
         <x:v>2644.786571</x:v>
       </x:c>
       <x:c r="I22" s="111" t="n">
-        <x:v>2634.511995</x:v>
+        <x:v>2673.311233</x:v>
       </x:c>
       <x:c r="J22" s="111" t="n">
         <x:v>1.0038999921122016</x:v>
@@ -2432,16 +2432,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G33" s="111" t="n">
-        <x:v>0.49495</x:v>
+        <x:v>0.493441</x:v>
       </x:c>
       <x:c r="H33" s="111" t="n">
-        <x:v>66.875445</x:v>
+        <x:v>66.865897</x:v>
       </x:c>
       <x:c r="I33" s="111" t="n">
-        <x:v>66.940928</x:v>
+        <x:v>66.966487</x:v>
       </x:c>
       <x:c r="J33" s="111" t="n">
-        <x:v>0.9990217793216132</x:v>
+        <x:v>0.9984979053776556</x:v>
       </x:c>
       <x:c r="K33" s="111" t="n">
         <x:v>0.00000131094793036</x:v>
@@ -2476,22 +2476,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G34" s="111" t="n">
-        <x:v>4.00623</x:v>
+        <x:v>5.265726</x:v>
       </x:c>
       <x:c r="H34" s="111" t="n">
-        <x:v>3.927878</x:v>
+        <x:v>3.922302</x:v>
       </x:c>
       <x:c r="I34" s="111" t="n">
-        <x:v>3.923799</x:v>
+        <x:v>3.925981</x:v>
       </x:c>
       <x:c r="J34" s="111" t="n">
-        <x:v>1.0010395537589973</x:v>
+        <x:v>0.9990629093722053</x:v>
       </x:c>
       <x:c r="K34" s="111" t="n">
         <x:v>8.881784197e-16</x:v>
       </x:c>
       <x:c r="L34" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M34" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -2520,16 +2520,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G35" s="111" t="n">
-        <x:v>4.020571</x:v>
+        <x:v>3.736851</x:v>
       </x:c>
       <x:c r="H35" s="111" t="n">
-        <x:v>1.706794</x:v>
+        <x:v>1.703725</x:v>
       </x:c>
       <x:c r="I35" s="111" t="n">
-        <x:v>1.704004</x:v>
+        <x:v>1.702275</x:v>
       </x:c>
       <x:c r="J35" s="111" t="n">
-        <x:v>1.0016373201001876</x:v>
+        <x:v>1.0008518012659529</x:v>
       </x:c>
       <x:c r="K35" s="111" t="n">
         <x:v>0</x:v>
@@ -2564,16 +2564,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G36" s="111" t="n">
-        <x:v>16.053881</x:v>
+        <x:v>16.099948</x:v>
       </x:c>
       <x:c r="H36" s="111" t="n">
-        <x:v>53.529598</x:v>
+        <x:v>53.456427</x:v>
       </x:c>
       <x:c r="I36" s="111" t="n">
-        <x:v>53.56136</x:v>
+        <x:v>53.485788</x:v>
       </x:c>
       <x:c r="J36" s="111" t="n">
-        <x:v>0.9994069978805616</x:v>
+        <x:v>0.9994510504360522</x:v>
       </x:c>
       <x:c r="K36" s="111" t="n">
         <x:v>4.0099439713e-7</x:v>
@@ -2608,16 +2608,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G37" s="111" t="n">
-        <x:v>43.924987</x:v>
+        <x:v>44.162701</x:v>
       </x:c>
       <x:c r="H37" s="111" t="n">
-        <x:v>7.52223</x:v>
+        <x:v>7.522842</x:v>
       </x:c>
       <x:c r="I37" s="111" t="n">
-        <x:v>7.52533</x:v>
+        <x:v>7.523612</x:v>
       </x:c>
       <x:c r="J37" s="111" t="n">
-        <x:v>0.9995880579323432</x:v>
+        <x:v>0.9998976555409822</x:v>
       </x:c>
       <x:c r="K37" s="111" t="n">
         <x:v>0.00657660588948</x:v>
@@ -2728,22 +2728,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G40" s="111" t="n">
-        <x:v>58.480117</x:v>
+        <x:v>58.380312</x:v>
       </x:c>
       <x:c r="H40" s="111" t="n">
-        <x:v>4.272835</x:v>
+        <x:v>4.243702</x:v>
       </x:c>
       <x:c r="I40" s="111" t="n">
-        <x:v>4.254635</x:v>
+        <x:v>4.257773</x:v>
       </x:c>
       <x:c r="J40" s="111" t="n">
-        <x:v>1.004277687745247</x:v>
+        <x:v>0.996695220717497</x:v>
       </x:c>
       <x:c r="K40" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L40" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M40" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -2772,22 +2772,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G41" s="111" t="n">
-        <x:v>71.400995</x:v>
+        <x:v>71.34114</x:v>
       </x:c>
       <x:c r="H41" s="111" t="n">
-        <x:v>4.243055</x:v>
+        <x:v>4.254213</x:v>
       </x:c>
       <x:c r="I41" s="111" t="n">
-        <x:v>4.315246</x:v>
+        <x:v>4.252963</x:v>
       </x:c>
       <x:c r="J41" s="111" t="n">
-        <x:v>0.9832707104067763</x:v>
+        <x:v>1.0002939127380135</x:v>
       </x:c>
       <x:c r="K41" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L41" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M41" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -2816,22 +2816,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G42" s="111" t="n">
-        <x:v>57.944096</x:v>
+        <x:v>57.832451</x:v>
       </x:c>
       <x:c r="H42" s="111" t="n">
-        <x:v>4.264355</x:v>
+        <x:v>4.264703</x:v>
       </x:c>
       <x:c r="I42" s="111" t="n">
-        <x:v>4.289936</x:v>
+        <x:v>4.243682</x:v>
       </x:c>
       <x:c r="J42" s="111" t="n">
-        <x:v>0.9940369739781666</x:v>
+        <x:v>1.0049534814342829</x:v>
       </x:c>
       <x:c r="K42" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L42" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M42" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -2992,16 +2992,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G46" s="111" t="n">
-        <x:v>1.990996</x:v>
+        <x:v>1.992986</x:v>
       </x:c>
       <x:c r="H46" s="111" t="n">
-        <x:v>0.213243</x:v>
+        <x:v>0.163881</x:v>
       </x:c>
       <x:c r="I46" s="111" t="n">
-        <x:v>0.214473</x:v>
+        <x:v>0.1644</x:v>
       </x:c>
       <x:c r="J46" s="111" t="n">
-        <x:v>0.9942650123791805</x:v>
+        <x:v>0.9968430656934307</x:v>
       </x:c>
       <x:c r="K46" s="111" t="n">
         <x:v>0</x:v>
@@ -3476,22 +3476,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G57" s="111" t="n">
-        <x:v>0.436409</x:v>
+        <x:v>0.457849</x:v>
       </x:c>
       <x:c r="H57" s="111" t="n">
-        <x:v>0.176743</x:v>
+        <x:v>0.165404</x:v>
       </x:c>
       <x:c r="I57" s="111" t="n">
-        <x:v>0.180234</x:v>
+        <x:v>0.164703</x:v>
       </x:c>
       <x:c r="J57" s="111" t="n">
-        <x:v>0.9806307355992765</x:v>
+        <x:v>1.004256145911125</x:v>
       </x:c>
       <x:c r="K57" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L57" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M57" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -3564,22 +3564,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G59" s="111" t="n">
-        <x:v>85.387395</x:v>
+        <x:v>85.415876</x:v>
       </x:c>
       <x:c r="H59" s="111" t="n">
-        <x:v>0.707705</x:v>
+        <x:v>0.699363</x:v>
       </x:c>
       <x:c r="I59" s="111" t="n">
-        <x:v>0.704154</x:v>
+        <x:v>0.709414</x:v>
       </x:c>
       <x:c r="J59" s="111" t="n">
-        <x:v>1.005042930949764</x:v>
+        <x:v>0.985831968356982</x:v>
       </x:c>
       <x:c r="K59" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L59" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M59" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -3608,22 +3608,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G60" s="111" t="n">
-        <x:v>33.825116</x:v>
+        <x:v>33.85332</x:v>
       </x:c>
       <x:c r="H60" s="111" t="n">
-        <x:v>0.440829</x:v>
+        <x:v>0.449761</x:v>
       </x:c>
       <x:c r="I60" s="111" t="n">
-        <x:v>0.441498</x:v>
+        <x:v>0.437221</x:v>
       </x:c>
       <x:c r="J60" s="111" t="n">
-        <x:v>0.9984847043474716</x:v>
+        <x:v>1.0286811475203614</x:v>
       </x:c>
       <x:c r="K60" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L60" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M60" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -3652,22 +3652,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G61" s="111" t="n">
-        <x:v>43.898237</x:v>
+        <x:v>44.11973</x:v>
       </x:c>
       <x:c r="H61" s="111" t="n">
-        <x:v>4245.505939</x:v>
+        <x:v>4043.908548</x:v>
       </x:c>
       <x:c r="I61" s="111" t="n">
-        <x:v>4036.767899</x:v>
+        <x:v>4052.409013</x:v>
       </x:c>
       <x:c r="J61" s="111" t="n">
-        <x:v>1.0517092003361672</x:v>
+        <x:v>0.9979023674627288</x:v>
       </x:c>
       <x:c r="K61" s="111" t="n">
         <x:v>5.73868331905e-7</x:v>
       </x:c>
       <x:c r="L61" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M61" s="7" t="str">
         <x:v>混合精度已进入实现路径：官方路径：保持 ITK 已有 InternalRealType/官方实现，不额外包一层混精。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -3696,22 +3696,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G62" s="111" t="n">
-        <x:v>33.453156</x:v>
+        <x:v>33.484109</x:v>
       </x:c>
       <x:c r="H62" s="111" t="n">
-        <x:v>0.557107</x:v>
+        <x:v>0.548102</x:v>
       </x:c>
       <x:c r="I62" s="111" t="n">
-        <x:v>0.554547</x:v>
+        <x:v>0.551481</x:v>
       </x:c>
       <x:c r="J62" s="111" t="n">
-        <x:v>1.0046163805773</x:v>
+        <x:v>0.9938728623470255</x:v>
       </x:c>
       <x:c r="K62" s="111" t="n">
         <x:v>0.0000222529822503</x:v>
       </x:c>
       <x:c r="L62" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M62" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -3784,16 +3784,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G64" s="111" t="n">
-        <x:v>79.804632</x:v>
+        <x:v>79.928356</x:v>
       </x:c>
       <x:c r="H64" s="111" t="n">
-        <x:v>1.015813</x:v>
+        <x:v>1.009423</x:v>
       </x:c>
       <x:c r="I64" s="111" t="n">
-        <x:v>1.013684</x:v>
+        <x:v>1.001473</x:v>
       </x:c>
       <x:c r="J64" s="111" t="n">
-        <x:v>1.002100260041591</x:v>
+        <x:v>1.0079383068739745</x:v>
       </x:c>
       <x:c r="K64" s="111" t="n">
         <x:v>0</x:v>
@@ -3828,16 +3828,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G65" s="111" t="n">
-        <x:v>6.222395</x:v>
+        <x:v>4.1337</x:v>
       </x:c>
       <x:c r="H65" s="111" t="n">
-        <x:v>0.273366</x:v>
+        <x:v>0.251664</x:v>
       </x:c>
       <x:c r="I65" s="111" t="n">
-        <x:v>0.268126</x:v>
+        <x:v>0.250275</x:v>
       </x:c>
       <x:c r="J65" s="111" t="n">
-        <x:v>1.019543050655289</x:v>
+        <x:v>1.005549895115373</x:v>
       </x:c>
       <x:c r="K65" s="111" t="n">
         <x:v>0</x:v>
@@ -3872,22 +3872,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G66" s="111" t="n">
-        <x:v>0.012491</x:v>
+        <x:v>0.01144</x:v>
       </x:c>
       <x:c r="H66" s="111" t="n">
-        <x:v>0.338775</x:v>
+        <x:v>0.289811</x:v>
       </x:c>
       <x:c r="I66" s="111" t="n">
-        <x:v>0.310064</x:v>
+        <x:v>0.291372</x:v>
       </x:c>
       <x:c r="J66" s="111" t="n">
-        <x:v>1.0925970122297333</x:v>
+        <x:v>0.9946425874826681</x:v>
       </x:c>
       <x:c r="K66" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L66" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M66" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -3916,22 +3916,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G67" s="111" t="n">
-        <x:v>0.361398</x:v>
+        <x:v>0.345167</x:v>
       </x:c>
       <x:c r="H67" s="111" t="n">
-        <x:v>0.47863</x:v>
+        <x:v>0.454409</x:v>
       </x:c>
       <x:c r="I67" s="111" t="n">
-        <x:v>0.47575</x:v>
+        <x:v>0.457739</x:v>
       </x:c>
       <x:c r="J67" s="111" t="n">
-        <x:v>1.0060535995796112</x:v>
+        <x:v>0.9927251119087515</x:v>
       </x:c>
       <x:c r="K67" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L67" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M67" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -3960,22 +3960,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G68" s="111" t="n">
-        <x:v>0.131693</x:v>
+        <x:v>0.117763</x:v>
       </x:c>
       <x:c r="H68" s="111" t="n">
-        <x:v>0.448789</x:v>
+        <x:v>0.422409</x:v>
       </x:c>
       <x:c r="I68" s="111" t="n">
-        <x:v>0.441849</x:v>
+        <x:v>0.490029</x:v>
       </x:c>
       <x:c r="J68" s="111" t="n">
-        <x:v>1.015706723337611</x:v>
+        <x:v>0.8620081668635937</x:v>
       </x:c>
       <x:c r="K68" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L68" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M68" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4004,16 +4004,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G69" s="111" t="n">
-        <x:v>7.294696</x:v>
+        <x:v>6.560296</x:v>
       </x:c>
       <x:c r="H69" s="111" t="n">
-        <x:v>0.458329</x:v>
+        <x:v>0.441579</x:v>
       </x:c>
       <x:c r="I69" s="111" t="n">
-        <x:v>0.457159</x:v>
+        <x:v>0.437028</x:v>
       </x:c>
       <x:c r="J69" s="111" t="n">
-        <x:v>1.0025592846252618</x:v>
+        <x:v>1.0104135204151679</x:v>
       </x:c>
       <x:c r="K69" s="111" t="n">
         <x:v>0</x:v>
@@ -4048,22 +4048,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G70" s="111" t="n">
-        <x:v>81.453196</x:v>
+        <x:v>81.335987</x:v>
       </x:c>
       <x:c r="H70" s="111" t="n">
-        <x:v>1.343757</x:v>
+        <x:v>1.327786</x:v>
       </x:c>
       <x:c r="I70" s="111" t="n">
-        <x:v>1.334767</x:v>
+        <x:v>1.477098</x:v>
       </x:c>
       <x:c r="J70" s="111" t="n">
-        <x:v>1.0067352579139281</x:v>
+        <x:v>0.898915305551832</x:v>
       </x:c>
       <x:c r="K70" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L70" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M70" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4092,22 +4092,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G71" s="111" t="n">
-        <x:v>3.046361</x:v>
+        <x:v>3.057019</x:v>
       </x:c>
       <x:c r="H71" s="111" t="n">
-        <x:v>0.456579</x:v>
+        <x:v>0.436679</x:v>
       </x:c>
       <x:c r="I71" s="111" t="n">
-        <x:v>0.45284</x:v>
+        <x:v>0.438478</x:v>
       </x:c>
       <x:c r="J71" s="111" t="n">
-        <x:v>1.0082567794364454</x:v>
+        <x:v>0.995897171579874</x:v>
       </x:c>
       <x:c r="K71" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L71" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M71" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4168,16 +4168,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G73" s="111" t="n">
-        <x:v>10.305655</x:v>
+        <x:v>10.32044</x:v>
       </x:c>
       <x:c r="H73" s="111" t="n">
-        <x:v>0.268234</x:v>
+        <x:v>0.270241</x:v>
       </x:c>
       <x:c r="I73" s="111" t="n">
-        <x:v>0.267744</x:v>
+        <x:v>0.263711</x:v>
       </x:c>
       <x:c r="J73" s="111" t="n">
-        <x:v>1.0018301063702642</x:v>
+        <x:v>1.0247619553223037</x:v>
       </x:c>
       <x:c r="K73" s="111" t="n">
         <x:v>35.8102691298</x:v>
@@ -4212,22 +4212,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G74" s="111" t="n">
-        <x:v>0.674514</x:v>
+        <x:v>0.673133</x:v>
       </x:c>
       <x:c r="H74" s="111" t="n">
-        <x:v>0.225644</x:v>
+        <x:v>0.209404</x:v>
       </x:c>
       <x:c r="I74" s="111" t="n">
-        <x:v>0.223054</x:v>
+        <x:v>0.211654</x:v>
       </x:c>
       <x:c r="J74" s="111" t="n">
-        <x:v>1.0116115380132165</x:v>
+        <x:v>0.9893694425808158</x:v>
       </x:c>
       <x:c r="K74" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L74" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M74" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4344,22 +4344,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G77" s="111" t="n">
-        <x:v>0.096262</x:v>
+        <x:v>0.108192</x:v>
       </x:c>
       <x:c r="H77" s="111" t="n">
-        <x:v>0.452729</x:v>
+        <x:v>0.438109</x:v>
       </x:c>
       <x:c r="I77" s="111" t="n">
-        <x:v>0.454879</x:v>
+        <x:v>0.433698</x:v>
       </x:c>
       <x:c r="J77" s="111" t="n">
-        <x:v>0.9952734683289403</x:v>
+        <x:v>1.010170671757767</x:v>
       </x:c>
       <x:c r="K77" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L77" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M77" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4388,22 +4388,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G78" s="111" t="n">
-        <x:v>8.124392</x:v>
+        <x:v>5.421585</x:v>
       </x:c>
       <x:c r="H78" s="111" t="n">
-        <x:v>0.46776</x:v>
+        <x:v>0.446029</x:v>
       </x:c>
       <x:c r="I78" s="111" t="n">
-        <x:v>0.466979</x:v>
+        <x:v>0.452409</x:v>
       </x:c>
       <x:c r="J78" s="111" t="n">
-        <x:v>1.0016724520802864</x:v>
+        <x:v>0.9858977164468434</x:v>
       </x:c>
       <x:c r="K78" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L78" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M78" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4432,22 +4432,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G79" s="111" t="n">
-        <x:v>0.060001</x:v>
+        <x:v>0.060292</x:v>
       </x:c>
       <x:c r="H79" s="111" t="n">
-        <x:v>0.190674</x:v>
+        <x:v>0.167323</x:v>
       </x:c>
       <x:c r="I79" s="111" t="n">
-        <x:v>0.188484</x:v>
+        <x:v>0.213814</x:v>
       </x:c>
       <x:c r="J79" s="111" t="n">
-        <x:v>1.0116190233653786</x:v>
+        <x:v>0.7825633494532631</x:v>
       </x:c>
       <x:c r="K79" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L79" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M79" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4476,16 +4476,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G80" s="111" t="n">
-        <x:v>0.53618</x:v>
+        <x:v>0.612062</x:v>
       </x:c>
       <x:c r="H80" s="111" t="n">
-        <x:v>0.214204</x:v>
+        <x:v>0.206585</x:v>
       </x:c>
       <x:c r="I80" s="111" t="n">
-        <x:v>0.211534</x:v>
+        <x:v>0.204604</x:v>
       </x:c>
       <x:c r="J80" s="111" t="n">
-        <x:v>1.0126220843930527</x:v>
+        <x:v>1.0096821176516588</x:v>
       </x:c>
       <x:c r="K80" s="111" t="n">
         <x:v>0</x:v>
@@ -4520,22 +4520,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G81" s="111" t="n">
-        <x:v>2.327916</x:v>
+        <x:v>2.392266</x:v>
       </x:c>
       <x:c r="H81" s="111" t="n">
-        <x:v>0.269826</x:v>
+        <x:v>0.248335</x:v>
       </x:c>
       <x:c r="I81" s="111" t="n">
-        <x:v>0.268096</x:v>
+        <x:v>0.251455</x:v>
       </x:c>
       <x:c r="J81" s="111" t="n">
-        <x:v>1.0064529123895918</x:v>
+        <x:v>0.9875922133184865</x:v>
       </x:c>
       <x:c r="K81" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L81" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M81" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4564,16 +4564,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G82" s="111" t="n">
-        <x:v>22.862726</x:v>
+        <x:v>22.900841</x:v>
       </x:c>
       <x:c r="H82" s="111" t="n">
-        <x:v>6.48386</x:v>
+        <x:v>5.869103</x:v>
       </x:c>
       <x:c r="I82" s="111" t="n">
-        <x:v>5.784185</x:v>
+        <x:v>5.7129</x:v>
       </x:c>
       <x:c r="J82" s="111" t="n">
-        <x:v>1.1209634546612877</x:v>
+        <x:v>1.027342155472702</x:v>
       </x:c>
       <x:c r="K82" s="111" t="n">
         <x:v>0</x:v>
@@ -4608,22 +4608,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G83" s="111" t="n">
-        <x:v>0.00573</x:v>
+        <x:v>0.00574</x:v>
       </x:c>
       <x:c r="H83" s="111" t="n">
-        <x:v>0.111672</x:v>
+        <x:v>0.111311</x:v>
       </x:c>
       <x:c r="I83" s="111" t="n">
-        <x:v>0.133862</x:v>
+        <x:v>0.109661</x:v>
       </x:c>
       <x:c r="J83" s="111" t="n">
-        <x:v>0.8342322690532039</x:v>
+        <x:v>1.0150463701771824</x:v>
       </x:c>
       <x:c r="K83" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L83" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M83" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4652,22 +4652,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G84" s="111" t="n">
-        <x:v>1.99367</x:v>
+        <x:v>2.010859</x:v>
       </x:c>
       <x:c r="H84" s="111" t="n">
-        <x:v>0.4599</x:v>
+        <x:v>0.422508</x:v>
       </x:c>
       <x:c r="I84" s="111" t="n">
-        <x:v>0.458369</x:v>
+        <x:v>0.472979</x:v>
       </x:c>
       <x:c r="J84" s="111" t="n">
-        <x:v>1.0033401037155654</x:v>
+        <x:v>0.8932912454887003</x:v>
       </x:c>
       <x:c r="K84" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L84" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M84" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4696,16 +4696,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G85" s="111" t="n">
-        <x:v>31.849006</x:v>
+        <x:v>31.797841</x:v>
       </x:c>
       <x:c r="H85" s="111" t="n">
-        <x:v>0.455809</x:v>
+        <x:v>0.451469</x:v>
       </x:c>
       <x:c r="I85" s="111" t="n">
-        <x:v>0.460629</x:v>
+        <x:v>0.452279</x:v>
       </x:c>
       <x:c r="J85" s="111" t="n">
-        <x:v>0.9895360474481633</x:v>
+        <x:v>0.9982090700651589</x:v>
       </x:c>
       <x:c r="K85" s="111" t="n">
         <x:v>0</x:v>
@@ -4740,16 +4740,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G86" s="111" t="n">
-        <x:v>0.50529</x:v>
+        <x:v>0.493689</x:v>
       </x:c>
       <x:c r="H86" s="111" t="n">
-        <x:v>0.226835</x:v>
+        <x:v>0.214964</x:v>
       </x:c>
       <x:c r="I86" s="111" t="n">
-        <x:v>0.225575</x:v>
+        <x:v>0.210794</x:v>
       </x:c>
       <x:c r="J86" s="111" t="n">
-        <x:v>1.0055857253685028</x:v>
+        <x:v>1.0197823467461122</x:v>
       </x:c>
       <x:c r="K86" s="111" t="n">
         <x:v>0</x:v>
@@ -4784,22 +4784,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G87" s="111" t="n">
-        <x:v>0.51366</x:v>
+        <x:v>0.50582</x:v>
       </x:c>
       <x:c r="H87" s="111" t="n">
-        <x:v>0.224794</x:v>
+        <x:v>0.209814</x:v>
       </x:c>
       <x:c r="I87" s="111" t="n">
-        <x:v>0.222255</x:v>
+        <x:v>0.213264</x:v>
       </x:c>
       <x:c r="J87" s="111" t="n">
-        <x:v>1.0114238149872894</x:v>
+        <x:v>0.9838228674319154</x:v>
       </x:c>
       <x:c r="K87" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L87" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M87" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4828,22 +4828,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G88" s="111" t="n">
-        <x:v>174.726779</x:v>
+        <x:v>174.451642</x:v>
       </x:c>
       <x:c r="H88" s="111" t="n">
-        <x:v>3.137372</x:v>
+        <x:v>3.052669</x:v>
       </x:c>
       <x:c r="I88" s="111" t="n">
-        <x:v>3.102612</x:v>
+        <x:v>3.062209</x:v>
       </x:c>
       <x:c r="J88" s="111" t="n">
-        <x:v>1.0112034634043832</x:v>
+        <x:v>0.9968846019327876</x:v>
       </x:c>
       <x:c r="K88" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L88" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M88" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -4916,16 +4916,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G90" s="111" t="n">
-        <x:v>226.041834</x:v>
+        <x:v>225.66149</x:v>
       </x:c>
       <x:c r="H90" s="111" t="n">
-        <x:v>3.097402</x:v>
+        <x:v>3.078679</x:v>
       </x:c>
       <x:c r="I90" s="111" t="n">
-        <x:v>3.082941</x:v>
+        <x:v>3.065939</x:v>
       </x:c>
       <x:c r="J90" s="111" t="n">
-        <x:v>1.0046906509076885</x:v>
+        <x:v>1.0041553338145344</x:v>
       </x:c>
       <x:c r="K90" s="111" t="n">
         <x:v>0</x:v>
@@ -5180,16 +5180,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G96" s="111" t="n">
-        <x:v>3.261955</x:v>
+        <x:v>3.250905</x:v>
       </x:c>
       <x:c r="H96" s="111" t="n">
-        <x:v>0.285616</x:v>
+        <x:v>0.286945</x:v>
       </x:c>
       <x:c r="I96" s="111" t="n">
-        <x:v>0.282866</x:v>
+        <x:v>0.279846</x:v>
       </x:c>
       <x:c r="J96" s="111" t="n">
-        <x:v>1.0097219177985335</x:v>
+        <x:v>1.0253675235665332</x:v>
       </x:c>
       <x:c r="K96" s="111" t="n">
         <x:v>0</x:v>
@@ -5708,22 +5708,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G108" s="111" t="n">
-        <x:v>4.470589</x:v>
+        <x:v>4.483989</x:v>
       </x:c>
       <x:c r="H108" s="111" t="n">
-        <x:v>0.291126</x:v>
+        <x:v>0.279945</x:v>
       </x:c>
       <x:c r="I108" s="111" t="n">
-        <x:v>0.287856</x:v>
+        <x:v>0.281166</x:v>
       </x:c>
       <x:c r="J108" s="111" t="n">
-        <x:v>1.0113598465899616</x:v>
+        <x:v>0.9956573696677407</x:v>
       </x:c>
       <x:c r="K108" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L108" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M108" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -5752,16 +5752,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G109" s="111" t="n">
-        <x:v>126.776305</x:v>
+        <x:v>126.634134</x:v>
       </x:c>
       <x:c r="H109" s="111" t="n">
-        <x:v>8241.898249</x:v>
+        <x:v>8269.371563</x:v>
       </x:c>
       <x:c r="I109" s="111" t="n">
-        <x:v>8269.269622</x:v>
+        <x:v>8269.373843</x:v>
       </x:c>
       <x:c r="J109" s="111" t="n">
-        <x:v>0.9966899890496762</x:v>
+        <x:v>0.9999997242838403</x:v>
       </x:c>
       <x:c r="K109" s="111" t="n">
         <x:v>0</x:v>
@@ -5796,16 +5796,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G110" s="111" t="n">
-        <x:v>3.651263</x:v>
+        <x:v>3.630172</x:v>
       </x:c>
       <x:c r="H110" s="111" t="n">
-        <x:v>0.285856</x:v>
+        <x:v>0.282726</x:v>
       </x:c>
       <x:c r="I110" s="111" t="n">
-        <x:v>0.281745</x:v>
+        <x:v>0.280046</x:v>
       </x:c>
       <x:c r="J110" s="111" t="n">
-        <x:v>1.0145912083621713</x:v>
+        <x:v>1.0095698563807374</x:v>
       </x:c>
       <x:c r="K110" s="111" t="n">
         <x:v>1.34633290421e-17</x:v>
@@ -5840,16 +5840,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G111" s="111" t="n">
-        <x:v>3.195324</x:v>
+        <x:v>3.186933</x:v>
       </x:c>
       <x:c r="H111" s="111" t="n">
-        <x:v>0.287506</x:v>
+        <x:v>0.285906</x:v>
       </x:c>
       <x:c r="I111" s="111" t="n">
-        <x:v>0.285365</x:v>
+        <x:v>0.279846</x:v>
       </x:c>
       <x:c r="J111" s="111" t="n">
-        <x:v>1.0075026720165403</x:v>
+        <x:v>1.0216547672648528</x:v>
       </x:c>
       <x:c r="K111" s="111" t="n">
         <x:v>0</x:v>
@@ -6016,16 +6016,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G115" s="111" t="n">
-        <x:v>4.747075</x:v>
+        <x:v>4.715903</x:v>
       </x:c>
       <x:c r="H115" s="111" t="n">
-        <x:v>0.288855</x:v>
+        <x:v>0.283056</x:v>
       </x:c>
       <x:c r="I115" s="111" t="n">
-        <x:v>0.286495</x:v>
+        <x:v>0.282985</x:v>
       </x:c>
       <x:c r="J115" s="111" t="n">
-        <x:v>1.0082374910556902</x:v>
+        <x:v>1.0002508966906372</x:v>
       </x:c>
       <x:c r="K115" s="111" t="n">
         <x:v>0</x:v>
@@ -6060,22 +6060,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G116" s="111" t="n">
-        <x:v>4.675063</x:v>
+        <x:v>3.728054</x:v>
       </x:c>
       <x:c r="H116" s="111" t="n">
-        <x:v>0.287856</x:v>
+        <x:v>0.282116</x:v>
       </x:c>
       <x:c r="I116" s="111" t="n">
-        <x:v>0.288526</x:v>
+        <x:v>0.279846</x:v>
       </x:c>
       <x:c r="J116" s="111" t="n">
-        <x:v>0.9976778522559492</x:v>
+        <x:v>1.0081116042394747</x:v>
       </x:c>
       <x:c r="K116" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L116" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M116" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -6456,22 +6456,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G125" s="111" t="n">
-        <x:v>12.786837</x:v>
+        <x:v>12.763718</x:v>
       </x:c>
       <x:c r="H125" s="111" t="n">
-        <x:v>30.792532</x:v>
+        <x:v>30.29362</x:v>
       </x:c>
       <x:c r="I125" s="111" t="n">
-        <x:v>30.540918</x:v>
+        <x:v>30.493511</x:v>
       </x:c>
       <x:c r="J125" s="111" t="n">
-        <x:v>1.0082385866724766</x:v>
+        <x:v>0.9934448020760875</x:v>
       </x:c>
       <x:c r="K125" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L125" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M125" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -6500,22 +6500,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G126" s="111" t="n">
-        <x:v>143.695496</x:v>
+        <x:v>143.470653</x:v>
       </x:c>
       <x:c r="H126" s="111" t="n">
-        <x:v>13.558034</x:v>
+        <x:v>13.5792</x:v>
       </x:c>
       <x:c r="I126" s="111" t="n">
-        <x:v>13.547345</x:v>
+        <x:v>13.66949</x:v>
       </x:c>
       <x:c r="J126" s="111" t="n">
-        <x:v>1.0007890106880721</x:v>
+        <x:v>0.9933947791761069</x:v>
       </x:c>
       <x:c r="K126" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L126" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M126" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -6720,16 +6720,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G131" s="111" t="n">
-        <x:v>3.375717</x:v>
+        <x:v>3.354066</x:v>
       </x:c>
       <x:c r="H131" s="111" t="n">
-        <x:v>0.285796</x:v>
+        <x:v>0.286526</x:v>
       </x:c>
       <x:c r="I131" s="111" t="n">
-        <x:v>0.281946</x:v>
+        <x:v>0.282016</x:v>
       </x:c>
       <x:c r="J131" s="111" t="n">
-        <x:v>1.0136550970753266</x:v>
+        <x:v>1.015992000453875</x:v>
       </x:c>
       <x:c r="K131" s="111" t="n">
         <x:v>0</x:v>
@@ -6852,16 +6852,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G134" s="111" t="n">
-        <x:v>158.532626</x:v>
+        <x:v>158.314151</x:v>
       </x:c>
       <x:c r="H134" s="111" t="n">
-        <x:v>3.177174</x:v>
+        <x:v>3.066309</x:v>
       </x:c>
       <x:c r="I134" s="111" t="n">
-        <x:v>3.123142</x:v>
+        <x:v>3.042008</x:v>
       </x:c>
       <x:c r="J134" s="111" t="n">
-        <x:v>1.0173005262008579</x:v>
+        <x:v>1.0079884734030942</x:v>
       </x:c>
       <x:c r="K134" s="111" t="n">
         <x:v>0</x:v>
@@ -7248,22 +7248,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G143" s="111" t="n">
-        <x:v>4.676043</x:v>
+        <x:v>4.728564</x:v>
       </x:c>
       <x:c r="H143" s="111" t="n">
-        <x:v>0.291366</x:v>
+        <x:v>0.282436</x:v>
       </x:c>
       <x:c r="I143" s="111" t="n">
-        <x:v>0.287526</x:v>
+        <x:v>0.286546</x:v>
       </x:c>
       <x:c r="J143" s="111" t="n">
-        <x:v>1.0133553139542164</x:v>
+        <x:v>0.9856567531914596</x:v>
       </x:c>
       <x:c r="K143" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L143" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M143" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -7292,22 +7292,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G144" s="111" t="n">
-        <x:v>4.047001</x:v>
+        <x:v>4.039208</x:v>
       </x:c>
       <x:c r="H144" s="111" t="n">
-        <x:v>0.186784</x:v>
+        <x:v>0.206174</x:v>
       </x:c>
       <x:c r="I144" s="111" t="n">
-        <x:v>0.209994</x:v>
+        <x:v>0.167324</x:v>
       </x:c>
       <x:c r="J144" s="111" t="n">
-        <x:v>0.8894730325628352</x:v>
+        <x:v>1.2321842652578232</x:v>
       </x:c>
       <x:c r="K144" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L144" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M144" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -7336,16 +7336,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G145" s="111" t="n">
-        <x:v>419.13297</x:v>
+        <x:v>443.799794</x:v>
       </x:c>
       <x:c r="H145" s="111" t="n">
-        <x:v>0.814726</x:v>
+        <x:v>0.779675</x:v>
       </x:c>
       <x:c r="I145" s="111" t="n">
-        <x:v>0.724675</x:v>
+        <x:v>0.662592</x:v>
       </x:c>
       <x:c r="J145" s="111" t="n">
-        <x:v>1.1242639804050092</x:v>
+        <x:v>1.1767045180141023</x:v>
       </x:c>
       <x:c r="K145" s="111" t="n">
         <x:v>0.0000578037612304</x:v>
@@ -7380,22 +7380,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G146" s="111" t="n">
-        <x:v>2.056111</x:v>
+        <x:v>2.05095</x:v>
       </x:c>
       <x:c r="H146" s="111" t="n">
-        <x:v>0.223374</x:v>
+        <x:v>0.178383</x:v>
       </x:c>
       <x:c r="I146" s="111" t="n">
-        <x:v>0.222055</x:v>
+        <x:v>0.230364</x:v>
       </x:c>
       <x:c r="J146" s="111" t="n">
-        <x:v>1.005939969827295</x:v>
+        <x:v>0.7743527634526228</x:v>
       </x:c>
       <x:c r="K146" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L146" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M146" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -7424,16 +7424,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G147" s="111" t="n">
-        <x:v>145.27278</x:v>
+        <x:v>145.040076</x:v>
       </x:c>
       <x:c r="H147" s="111" t="n">
-        <x:v>0.348977</x:v>
+        <x:v>0.383028</x:v>
       </x:c>
       <x:c r="I147" s="111" t="n">
-        <x:v>0.344437</x:v>
+        <x:v>0.326407</x:v>
       </x:c>
       <x:c r="J147" s="111" t="n">
-        <x:v>1.0131809300394556</x:v>
+        <x:v>1.173467480783194</x:v>
       </x:c>
       <x:c r="K147" s="111" t="n">
         <x:v>0</x:v>
@@ -7468,22 +7468,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G148" s="111" t="n">
-        <x:v>15.349086</x:v>
+        <x:v>15.173612</x:v>
       </x:c>
       <x:c r="H148" s="111" t="n">
-        <x:v>18.370787</x:v>
+        <x:v>17.750142</x:v>
       </x:c>
       <x:c r="I148" s="111" t="n">
-        <x:v>18.348596</x:v>
+        <x:v>18.717791</x:v>
       </x:c>
       <x:c r="J148" s="111" t="n">
-        <x:v>1.0012094113358865</x:v>
+        <x:v>0.9483032479633949</x:v>
       </x:c>
       <x:c r="K148" s="111" t="n">
         <x:v>363.72062453</x:v>
       </x:c>
       <x:c r="L148" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M148" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -7512,22 +7512,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G149" s="111" t="n">
-        <x:v>2.468569</x:v>
+        <x:v>2.479938</x:v>
       </x:c>
       <x:c r="H149" s="111" t="n">
-        <x:v>0.199724</x:v>
+        <x:v>0.221465</x:v>
       </x:c>
       <x:c r="I149" s="111" t="n">
-        <x:v>0.229015</x:v>
+        <x:v>0.184423</x:v>
       </x:c>
       <x:c r="J149" s="111" t="n">
-        <x:v>0.872100080780735</x:v>
+        <x:v>1.2008534727230333</x:v>
       </x:c>
       <x:c r="K149" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L149" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M149" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -7556,22 +7556,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G150" s="111" t="n">
-        <x:v>2.073781</x:v>
+        <x:v>2.06861</x:v>
       </x:c>
       <x:c r="H150" s="111" t="n">
-        <x:v>0.213264</x:v>
+        <x:v>0.211024</x:v>
       </x:c>
       <x:c r="I150" s="111" t="n">
-        <x:v>0.219934</x:v>
+        <x:v>0.173063</x:v>
       </x:c>
       <x:c r="J150" s="111" t="n">
-        <x:v>0.9696727199978176</x:v>
+        <x:v>1.2193478675395666</x:v>
       </x:c>
       <x:c r="K150" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L150" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M150" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -7600,22 +7600,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G151" s="111" t="n">
-        <x:v>5.085852</x:v>
+        <x:v>6.385313</x:v>
       </x:c>
       <x:c r="H151" s="111" t="n">
-        <x:v>25.476239</x:v>
+        <x:v>25.111424</x:v>
       </x:c>
       <x:c r="I151" s="111" t="n">
-        <x:v>25.183762</x:v>
+        <x:v>25.139044</x:v>
       </x:c>
       <x:c r="J151" s="111" t="n">
-        <x:v>1.0116137136302352</x:v>
+        <x:v>0.9989013106464988</x:v>
       </x:c>
       <x:c r="K151" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L151" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M151" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -7644,16 +7644,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G152" s="111" t="n">
-        <x:v>2.50918</x:v>
+        <x:v>2.007829</x:v>
       </x:c>
       <x:c r="H152" s="111" t="n">
-        <x:v>0.235294</x:v>
+        <x:v>0.237534</x:v>
       </x:c>
       <x:c r="I152" s="111" t="n">
-        <x:v>0.232015</x:v>
+        <x:v>0.181374</x:v>
       </x:c>
       <x:c r="J152" s="111" t="n">
-        <x:v>1.0141327069370516</x:v>
+        <x:v>1.3096364418273843</x:v>
       </x:c>
       <x:c r="K152" s="111" t="n">
         <x:v>0</x:v>
@@ -7688,22 +7688,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G153" s="111" t="n">
-        <x:v>5.085852</x:v>
+        <x:v>6.385313</x:v>
       </x:c>
       <x:c r="H153" s="111" t="n">
-        <x:v>25.476239</x:v>
+        <x:v>25.111424</x:v>
       </x:c>
       <x:c r="I153" s="111" t="n">
-        <x:v>25.183762</x:v>
+        <x:v>25.139044</x:v>
       </x:c>
       <x:c r="J153" s="111" t="n">
-        <x:v>1.0116137136302352</x:v>
+        <x:v>0.9989013106464988</x:v>
       </x:c>
       <x:c r="K153" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L153" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M153" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 COMPUTETYPE；按提示词仅可用于档A，档B/C及通用算子不能据此宣称已对齐。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -7732,16 +7732,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G154" s="111" t="n">
-        <x:v>5.253425</x:v>
+        <x:v>4.272112</x:v>
       </x:c>
       <x:c r="H154" s="111" t="n">
-        <x:v>0.225984</x:v>
+        <x:v>0.190183</x:v>
       </x:c>
       <x:c r="I154" s="111" t="n">
-        <x:v>0.240254</x:v>
+        <x:v>0.192513</x:v>
       </x:c>
       <x:c r="J154" s="111" t="n">
-        <x:v>0.9406045268757232</x:v>
+        <x:v>0.9878969212468769</x:v>
       </x:c>
       <x:c r="K154" s="111" t="n">
         <x:v>0</x:v>
@@ -7776,16 +7776,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G155" s="111" t="n">
-        <x:v>4.133263</x:v>
+        <x:v>4.099129</x:v>
       </x:c>
       <x:c r="H155" s="111" t="n">
-        <x:v>0.273205</x:v>
+        <x:v>0.291316</x:v>
       </x:c>
       <x:c r="I155" s="111" t="n">
-        <x:v>0.340857</x:v>
+        <x:v>0.299336</x:v>
       </x:c>
       <x:c r="J155" s="111" t="n">
-        <x:v>0.8015238061709161</x:v>
+        <x:v>0.973207365635941</x:v>
       </x:c>
       <x:c r="K155" s="111" t="n">
         <x:v>0</x:v>
@@ -7820,16 +7820,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G156" s="111" t="n">
-        <x:v>2.454089</x:v>
+        <x:v>2.151002</x:v>
       </x:c>
       <x:c r="H156" s="111" t="n">
-        <x:v>0.235544</x:v>
+        <x:v>0.211874</x:v>
       </x:c>
       <x:c r="I156" s="111" t="n">
-        <x:v>0.191694</x:v>
+        <x:v>0.196154</x:v>
       </x:c>
       <x:c r="J156" s="111" t="n">
-        <x:v>1.2287499869583816</x:v>
+        <x:v>1.080141113614813</x:v>
       </x:c>
       <x:c r="K156" s="111" t="n">
         <x:v>0</x:v>
@@ -8028,22 +8028,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G161" s="111" t="n">
-        <x:v>7.402718</x:v>
+        <x:v>7.417722</x:v>
       </x:c>
       <x:c r="H161" s="111" t="n">
-        <x:v>149.568869</x:v>
+        <x:v>149.691331</x:v>
       </x:c>
       <x:c r="I161" s="111" t="n">
-        <x:v>149.827231</x:v>
+        <x:v>149.583271</x:v>
       </x:c>
       <x:c r="J161" s="111" t="n">
-        <x:v>0.9982756005148357</x:v>
+        <x:v>1.0007224069862732</x:v>
       </x:c>
       <x:c r="K161" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L161" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M161" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -8072,16 +8072,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G162" s="111" t="n">
-        <x:v>0.50864</x:v>
+        <x:v>0.51207</x:v>
       </x:c>
       <x:c r="H162" s="111" t="n">
-        <x:v>187.147426</x:v>
+        <x:v>187.82627</x:v>
       </x:c>
       <x:c r="I162" s="111" t="n">
-        <x:v>185.378385</x:v>
+        <x:v>186.401252</x:v>
       </x:c>
       <x:c r="J162" s="111" t="n">
-        <x:v>1.009542865528794</x:v>
+        <x:v>1.0076448950031731</x:v>
       </x:c>
       <x:c r="K162" s="111" t="n">
         <x:v>0</x:v>
@@ -8116,22 +8116,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G163" s="111" t="n">
-        <x:v>7.583891</x:v>
+        <x:v>7.615722</x:v>
       </x:c>
       <x:c r="H163" s="111" t="n">
-        <x:v>149.485248</x:v>
+        <x:v>149.608772</x:v>
       </x:c>
       <x:c r="I163" s="111" t="n">
-        <x:v>149.703879</x:v>
+        <x:v>149.605611</x:v>
       </x:c>
       <x:c r="J163" s="111" t="n">
-        <x:v>0.9985395769203816</x:v>
+        <x:v>1.0000211288866698</x:v>
       </x:c>
       <x:c r="K163" s="111" t="n">
         <x:v>1.39961440215e-8</x:v>
       </x:c>
       <x:c r="L163" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M163" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -8160,22 +8160,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G164" s="111" t="n">
-        <x:v>109.383703</x:v>
+        <x:v>107.498147</x:v>
       </x:c>
       <x:c r="H164" s="111" t="n">
-        <x:v>0.246505</x:v>
+        <x:v>0.192761</x:v>
       </x:c>
       <x:c r="I164" s="111" t="n">
-        <x:v>0.194814</x:v>
+        <x:v>0.19467</x:v>
       </x:c>
       <x:c r="J164" s="111" t="n">
-        <x:v>1.265335140184997</x:v>
+        <x:v>0.9901936610674473</x:v>
       </x:c>
       <x:c r="K164" s="111" t="n">
         <x:v>0.773649437391</x:v>
       </x:c>
       <x:c r="L164" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M164" s="7" t="str">
         <x:v>混合精度已进入实现路径：应用层精度对比：Image&lt;float&gt; 与 Image&lt;double&gt;；OFF/ON 均保持该算子官方内部 RealType，不给通用 kernel 统一接 COMPUTETYPE。源码命中 HIP backend；仍需按算子三档确认类型/缓冲策略。DCU移植验收=通过（共享后端；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -8204,16 +8204,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G165" s="111" t="n">
-        <x:v>51.179643</x:v>
+        <x:v>51.208631</x:v>
       </x:c>
       <x:c r="H165" s="111" t="n">
-        <x:v>0.200544</x:v>
+        <x:v>0.19375</x:v>
       </x:c>
       <x:c r="I165" s="111" t="n">
-        <x:v>0.247355</x:v>
+        <x:v>0.198001</x:v>
       </x:c>
       <x:c r="J165" s="111" t="n">
-        <x:v>0.8107537749388531</x:v>
+        <x:v>0.9785304114625684</x:v>
       </x:c>
       <x:c r="K165" s="111" t="n">
         <x:v>1.2723035331</x:v>
@@ -8248,22 +8248,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G166" s="111" t="n">
-        <x:v>435.398491</x:v>
+        <x:v>435.176167</x:v>
       </x:c>
       <x:c r="H166" s="111" t="n">
-        <x:v>149.717458</x:v>
+        <x:v>149.737046</x:v>
       </x:c>
       <x:c r="I166" s="111" t="n">
-        <x:v>149.840075</x:v>
+        <x:v>149.706065</x:v>
       </x:c>
       <x:c r="J166" s="111" t="n">
-        <x:v>0.9991816808687528</x:v>
+        <x:v>1.0002069455235498</x:v>
       </x:c>
       <x:c r="K166" s="111" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="L166" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M166" s="7" t="str">
         <x:v>混合精度已完成：档B：度量、直方图、互信息和点集距离内部保持官方 RealType/FP64，ON 不全局切为 COMPUTETYPE=float。HIP 源码入口：itkHipANTSNeighborhoodCorrelationImageToImageMetricv4.h、itkHipRegistrationFilters.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -8292,16 +8292,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G167" s="111" t="n">
-        <x:v>8.122572</x:v>
+        <x:v>8.103734</x:v>
       </x:c>
       <x:c r="H167" s="111" t="n">
-        <x:v>149.738599</x:v>
+        <x:v>149.697871</x:v>
       </x:c>
       <x:c r="I167" s="111" t="n">
-        <x:v>149.80545</x:v>
+        <x:v>149.796742</x:v>
       </x:c>
       <x:c r="J167" s="111" t="n">
-        <x:v>0.9995537478776639</x:v>
+        <x:v>0.9993399656182108</x:v>
       </x:c>
       <x:c r="K167" s="111" t="n">
         <x:v>0.86817931385</x:v>
@@ -8336,16 +8336,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G168" s="111" t="n">
-        <x:v>0.949922</x:v>
+        <x:v>0.941882</x:v>
       </x:c>
       <x:c r="H168" s="111" t="n">
-        <x:v>471.629974</x:v>
+        <x:v>471.597351</x:v>
       </x:c>
       <x:c r="I168" s="111" t="n">
-        <x:v>471.556343</x:v>
+        <x:v>471.518881</x:v>
       </x:c>
       <x:c r="J168" s="111" t="n">
-        <x:v>1.0001561446497178</x:v>
+        <x:v>1.000166419634848</x:v>
       </x:c>
       <x:c r="K168" s="111" t="n">
         <x:v>0</x:v>
@@ -8383,13 +8383,13 @@
         <x:v>0.00007</x:v>
       </x:c>
       <x:c r="H169" s="111" t="n">
-        <x:v>0.166113</x:v>
+        <x:v>0.13124</x:v>
       </x:c>
       <x:c r="I169" s="111" t="n">
-        <x:v>0.126262</x:v>
+        <x:v>0.130911</x:v>
       </x:c>
       <x:c r="J169" s="111" t="n">
-        <x:v>1.3156214854825679</x:v>
+        <x:v>1.0025131577942266</x:v>
       </x:c>
       <x:c r="K169" s="111" t="n">
         <x:v>1</x:v>
@@ -8424,16 +8424,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G170" s="111" t="n">
-        <x:v>0.50244</x:v>
+        <x:v>0.50379</x:v>
       </x:c>
       <x:c r="H170" s="111" t="n">
-        <x:v>0.141852</x:v>
+        <x:v>0.133762</x:v>
       </x:c>
       <x:c r="I170" s="111" t="n">
-        <x:v>0.137073</x:v>
+        <x:v>0.132593</x:v>
       </x:c>
       <x:c r="J170" s="111" t="n">
-        <x:v>1.0348646341730319</x:v>
+        <x:v>1.0088164533572663</x:v>
       </x:c>
       <x:c r="K170" s="111" t="n">
         <x:v>0</x:v>
@@ -8468,22 +8468,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G171" s="111" t="n">
-        <x:v>0.5024</x:v>
+        <x:v>0.50362</x:v>
       </x:c>
       <x:c r="H171" s="111" t="n">
-        <x:v>0.137563</x:v>
+        <x:v>0.133173</x:v>
       </x:c>
       <x:c r="I171" s="111" t="n">
-        <x:v>0.136653</x:v>
+        <x:v>0.134383</x:v>
       </x:c>
       <x:c r="J171" s="111" t="n">
-        <x:v>1.0066592025056165</x:v>
+        <x:v>0.9909958848961551</x:v>
       </x:c>
       <x:c r="K171" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L171" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M171" s="7" t="str">
         <x:v>混合精度已完成：档B：度量、直方图、互信息和点集距离内部保持官方 RealType/FP64，ON 不全局切为 COMPUTETYPE=float。HIP 源码入口：itkHipJensenHavrdaCharvatTsallisPointSetToPointSetMetricv4.h、itkHipRegistrationFilters.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -8512,16 +8512,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G172" s="111" t="n">
-        <x:v>84.218811</x:v>
+        <x:v>84.875065</x:v>
       </x:c>
       <x:c r="H172" s="111" t="n">
-        <x:v>187.146556</x:v>
+        <x:v>186.581836</x:v>
       </x:c>
       <x:c r="I172" s="111" t="n">
-        <x:v>187.765973</x:v>
+        <x:v>187.063155</x:v>
       </x:c>
       <x:c r="J172" s="111" t="n">
-        <x:v>0.996701122199601</x:v>
+        <x:v>0.9974269705864847</x:v>
       </x:c>
       <x:c r="K172" s="111" t="n">
         <x:v>0.738684350719</x:v>
@@ -8556,22 +8556,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G173" s="111" t="n">
-        <x:v>72.041488</x:v>
+        <x:v>71.60646</x:v>
       </x:c>
       <x:c r="H173" s="111" t="n">
-        <x:v>188.203026</x:v>
+        <x:v>187.086406</x:v>
       </x:c>
       <x:c r="I173" s="111" t="n">
-        <x:v>187.176721</x:v>
+        <x:v>188.166986</x:v>
       </x:c>
       <x:c r="J173" s="111" t="n">
-        <x:v>1.0054830803452317</x:v>
+        <x:v>0.9942573348121758</x:v>
       </x:c>
       <x:c r="K173" s="111" t="n">
         <x:v>0.470684992287</x:v>
       </x:c>
       <x:c r="L173" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M173" s="7" t="str">
         <x:v>混合精度已完成：档B：度量、直方图、互信息和点集距离内部保持官方 RealType/FP64，ON 不全局切为 COMPUTETYPE=float。HIP 源码入口：itkHipMattesMutualInformationImageToImageMetricv4.h、itkHipRegistrationFilters.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -8600,16 +8600,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G174" s="111" t="n">
-        <x:v>7.590862</x:v>
+        <x:v>7.585282</x:v>
       </x:c>
       <x:c r="H174" s="111" t="n">
-        <x:v>149.742559</x:v>
+        <x:v>149.694971</x:v>
       </x:c>
       <x:c r="I174" s="111" t="n">
-        <x:v>149.81766</x:v>
+        <x:v>149.804912</x:v>
       </x:c>
       <x:c r="J174" s="111" t="n">
-        <x:v>0.9994987173074257</x:v>
+        <x:v>0.9992661055066072</x:v>
       </x:c>
       <x:c r="K174" s="111" t="n">
         <x:v>1.74003566711</x:v>
@@ -8644,16 +8644,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G175" s="111" t="n">
-        <x:v>0.49891</x:v>
+        <x:v>0.509911</x:v>
       </x:c>
       <x:c r="H175" s="111" t="n">
-        <x:v>149.714759</x:v>
+        <x:v>149.839845</x:v>
       </x:c>
       <x:c r="I175" s="111" t="n">
-        <x:v>149.696092</x:v>
+        <x:v>149.735033</x:v>
       </x:c>
       <x:c r="J175" s="111" t="n">
-        <x:v>1.0001246993141277</x:v>
+        <x:v>1.000699983149568</x:v>
       </x:c>
       <x:c r="K175" s="111" t="n">
         <x:v>0</x:v>
@@ -8688,22 +8688,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G176" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H176" s="111" t="n">
-        <x:v>0.976229</x:v>
+        <x:v>0.883507</x:v>
       </x:c>
       <x:c r="I176" s="111" t="n">
-        <x:v>0.937339</x:v>
+        <x:v>0.966589</x:v>
       </x:c>
       <x:c r="J176" s="111" t="n">
-        <x:v>1.04148979184692</x:v>
+        <x:v>0.9140461975048341</x:v>
       </x:c>
       <x:c r="K176" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L176" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M176" s="7" t="str">
         <x:v>混合精度已完成：档C：迭代控制与更新保持 FP64-safe 设备路径，I/O 类型不变，OFF 不覆盖官方路径。HIP 源码入口：itkHipDemonsRegistrationFilter.h、itkHipDiffeomorphicDemonsRegistrationFilter.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -8732,22 +8732,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G177" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H177" s="111" t="n">
-        <x:v>0.931499</x:v>
+        <x:v>0.846156</x:v>
       </x:c>
       <x:c r="I177" s="111" t="n">
-        <x:v>0.929299</x:v>
+        <x:v>0.994379</x:v>
       </x:c>
       <x:c r="J177" s="111" t="n">
-        <x:v>1.0023673758392078</x:v>
+        <x:v>0.8509391288432278</x:v>
       </x:c>
       <x:c r="K177" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L177" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M177" s="7" t="str">
         <x:v>混合精度已完成：档C：迭代控制与更新保持 FP64-safe 设备路径，I/O 类型不变，OFF 不覆盖官方路径。HIP 源码入口：itkHipDiffeomorphicDemonsRegistrationFilter.h、itkHipRegistrationFilters.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -8776,16 +8776,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G178" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H178" s="111" t="n">
-        <x:v>0.895228</x:v>
+        <x:v>0.876077</x:v>
       </x:c>
       <x:c r="I178" s="111" t="n">
-        <x:v>0.910729</x:v>
+        <x:v>0.991729</x:v>
       </x:c>
       <x:c r="J178" s="111" t="n">
-        <x:v>0.9829795691144128</x:v>
+        <x:v>0.8833834646360044</x:v>
       </x:c>
       <x:c r="K178" s="111" t="n">
         <x:v>0</x:v>
@@ -8820,16 +8820,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G179" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H179" s="111" t="n">
-        <x:v>0.922718</x:v>
+        <x:v>0.874767</x:v>
       </x:c>
       <x:c r="I179" s="111" t="n">
-        <x:v>0.968669</x:v>
+        <x:v>1.00006</x:v>
       </x:c>
       <x:c r="J179" s="111" t="n">
-        <x:v>0.9525627433106665</x:v>
+        <x:v>0.8747145171289723</x:v>
       </x:c>
       <x:c r="K179" s="111" t="n">
         <x:v>0</x:v>
@@ -8864,22 +8864,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G180" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H180" s="111" t="n">
-        <x:v>0.970919</x:v>
+        <x:v>0.846926</x:v>
       </x:c>
       <x:c r="I180" s="111" t="n">
-        <x:v>0.940579</x:v>
+        <x:v>1.0261</x:v>
       </x:c>
       <x:c r="J180" s="111" t="n">
-        <x:v>1.0322567269734917</x:v>
+        <x:v>0.8253834908878277</x:v>
       </x:c>
       <x:c r="K180" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L180" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M180" s="7" t="str">
         <x:v>混合精度已完成：档C：迭代控制与更新保持 FP64-safe 设备路径，I/O 类型不变，OFF 不覆盖官方路径。HIP 源码入口：itkHipFastSymmetricForcesDemonsRegistrationFilter.h、itkHipRegistrationFilters.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -8908,16 +8908,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G181" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H181" s="111" t="n">
-        <x:v>747.653093</x:v>
+        <x:v>748.146367</x:v>
       </x:c>
       <x:c r="I181" s="111" t="n">
-        <x:v>747.726801</x:v>
+        <x:v>748.321341</x:v>
       </x:c>
       <x:c r="J181" s="111" t="n">
-        <x:v>0.9999014238891779</x:v>
+        <x:v>0.999766177990105</x:v>
       </x:c>
       <x:c r="K181" s="111" t="n">
         <x:v>0</x:v>
@@ -8952,16 +8952,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G182" s="111" t="n">
-        <x:v>1.619398</x:v>
+        <x:v>1.620615</x:v>
       </x:c>
       <x:c r="H182" s="111" t="n">
-        <x:v>0.306756</x:v>
+        <x:v>0.297491</x:v>
       </x:c>
       <x:c r="I182" s="111" t="n">
-        <x:v>0.310426</x:v>
+        <x:v>0.300121</x:v>
       </x:c>
       <x:c r="J182" s="111" t="n">
-        <x:v>0.9881775366754073</x:v>
+        <x:v>0.9912368677966553</x:v>
       </x:c>
       <x:c r="K182" s="111" t="n">
         <x:v>0</x:v>
@@ -8996,16 +8996,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G183" s="111" t="n">
-        <x:v>2.422622</x:v>
+        <x:v>2.428197</x:v>
       </x:c>
       <x:c r="H183" s="111" t="n">
-        <x:v>0.306885</x:v>
+        <x:v>0.289681</x:v>
       </x:c>
       <x:c r="I183" s="111" t="n">
-        <x:v>0.314425</x:v>
+        <x:v>0.29169</x:v>
       </x:c>
       <x:c r="J183" s="111" t="n">
-        <x:v>0.9760197185338316</x:v>
+        <x:v>0.9931125509959204</x:v>
       </x:c>
       <x:c r="K183" s="111" t="n">
         <x:v>0</x:v>
@@ -9040,22 +9040,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G184" s="111" t="n">
-        <x:v>2.428882</x:v>
+        <x:v>2.442528</x:v>
       </x:c>
       <x:c r="H184" s="111" t="n">
-        <x:v>0.305475</x:v>
+        <x:v>0.285971</x:v>
       </x:c>
       <x:c r="I184" s="111" t="n">
-        <x:v>0.299285</x:v>
+        <x:v>0.286231</x:v>
       </x:c>
       <x:c r="J184" s="111" t="n">
-        <x:v>1.0206826269275104</x:v>
+        <x:v>0.999091642764061</x:v>
       </x:c>
       <x:c r="K184" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L184" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M184" s="7" t="str">
         <x:v>混合精度已完成：档C：float I/O 下设备端迭代缓冲和有限差分保持 FP64，边界处转换回 float，OFF 不覆盖官方路径。HIP 源码入口：itkHipCurvesLevelSetImageFilter.h、itkHipLevelSetImageFilters.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -9084,22 +9084,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G185" s="111" t="n">
-        <x:v>2.432902</x:v>
+        <x:v>2.419957</x:v>
       </x:c>
       <x:c r="H185" s="111" t="n">
-        <x:v>0.310125</x:v>
+        <x:v>0.286061</x:v>
       </x:c>
       <x:c r="I185" s="111" t="n">
-        <x:v>0.298635</x:v>
+        <x:v>0.292611</x:v>
       </x:c>
       <x:c r="J185" s="111" t="n">
-        <x:v>1.0384750615299614</x:v>
+        <x:v>0.9776153323012463</x:v>
       </x:c>
       <x:c r="K185" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L185" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M185" s="7" t="str">
         <x:v>混合精度已完成：档C：float I/O 下设备端迭代缓冲和有限差分保持 FP64，边界处转换回 float，OFF 不覆盖官方路径。HIP 源码入口：itkHipGeodesicActiveContourLevelSetImageFilter.h、itkHipLevelSetImageFilters.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -9128,16 +9128,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G186" s="111" t="n">
-        <x:v>2.424772</x:v>
+        <x:v>2.419017</x:v>
       </x:c>
       <x:c r="H186" s="111" t="n">
-        <x:v>0.343736</x:v>
+        <x:v>0.287111</x:v>
       </x:c>
       <x:c r="I186" s="111" t="n">
-        <x:v>0.297455</x:v>
+        <x:v>0.286301</x:v>
       </x:c>
       <x:c r="J186" s="111" t="n">
-        <x:v>1.1555899211645457</x:v>
+        <x:v>1.0028291902578055</x:v>
       </x:c>
       <x:c r="K186" s="111" t="n">
         <x:v>0</x:v>
@@ -9172,16 +9172,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G187" s="111" t="n">
-        <x:v>1.622708</x:v>
+        <x:v>1.622525</x:v>
       </x:c>
       <x:c r="H187" s="111" t="n">
-        <x:v>0.302935</x:v>
+        <x:v>0.292911</x:v>
       </x:c>
       <x:c r="I187" s="111" t="n">
-        <x:v>0.344905</x:v>
+        <x:v>0.295421</x:v>
       </x:c>
       <x:c r="J187" s="111" t="n">
-        <x:v>0.8783143184355112</x:v>
+        <x:v>0.9915036507221896</x:v>
       </x:c>
       <x:c r="K187" s="111" t="n">
         <x:v>0</x:v>
@@ -9216,16 +9216,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G188" s="111" t="n">
-        <x:v>2.421922</x:v>
+        <x:v>2.425067</x:v>
       </x:c>
       <x:c r="H188" s="111" t="n">
-        <x:v>0.306646</x:v>
+        <x:v>0.288271</x:v>
       </x:c>
       <x:c r="I188" s="111" t="n">
-        <x:v>0.300335</x:v>
+        <x:v>0.287591</x:v>
       </x:c>
       <x:c r="J188" s="111" t="n">
-        <x:v>1.0210132019245175</x:v>
+        <x:v>1.002364468985469</x:v>
       </x:c>
       <x:c r="K188" s="111" t="n">
         <x:v>0</x:v>
@@ -9260,22 +9260,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G189" s="111" t="n">
-        <x:v>2.464933</x:v>
+        <x:v>2.425397</x:v>
       </x:c>
       <x:c r="H189" s="111" t="n">
-        <x:v>0.299696</x:v>
+        <x:v>0.286061</x:v>
       </x:c>
       <x:c r="I189" s="111" t="n">
-        <x:v>0.301166</x:v>
+        <x:v>0.284401</x:v>
       </x:c>
       <x:c r="J189" s="111" t="n">
-        <x:v>0.995118970932974</x:v>
+        <x:v>1.0058368289844268</x:v>
       </x:c>
       <x:c r="K189" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L189" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M189" s="7" t="str">
         <x:v>混合精度已完成：档C：float I/O 下设备端迭代缓冲和有限差分保持 FP64，边界处转换回 float，OFF 不覆盖官方路径。HIP 源码入口：itkHipLevelSetImageFilters.h、itkHipNarrowBandCurvesLevelSetImageFilter.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -9304,22 +9304,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G190" s="111" t="n">
-        <x:v>2.420832</x:v>
+        <x:v>2.427037</x:v>
       </x:c>
       <x:c r="H190" s="111" t="n">
-        <x:v>0.302675</x:v>
+        <x:v>0.293671</x:v>
       </x:c>
       <x:c r="I190" s="111" t="n">
-        <x:v>0.303865</x:v>
+        <x:v>0.289891</x:v>
       </x:c>
       <x:c r="J190" s="111" t="n">
-        <x:v>0.9960837872081353</x:v>
+        <x:v>1.013039383768382</x:v>
       </x:c>
       <x:c r="K190" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L190" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M190" s="7" t="str">
         <x:v>混合精度已完成：档C：float I/O 下设备端迭代缓冲和有限差分保持 FP64，边界处转换回 float，OFF 不覆盖官方路径。HIP 源码入口：itkHipLevelSetImageFilters.h、itkHipNarrowBandThresholdSegmentationLevelSetImageFilter.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -9348,16 +9348,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G191" s="111" t="n">
-        <x:v>1.625128</x:v>
+        <x:v>1.621965</x:v>
       </x:c>
       <x:c r="H191" s="111" t="n">
-        <x:v>0.342066</x:v>
+        <x:v>0.288231</x:v>
       </x:c>
       <x:c r="I191" s="111" t="n">
-        <x:v>0.341296</x:v>
+        <x:v>0.2878</x:v>
       </x:c>
       <x:c r="J191" s="111" t="n">
-        <x:v>1.0022561061366086</x:v>
+        <x:v>1.0014975677553857</x:v>
       </x:c>
       <x:c r="K191" s="111" t="n">
         <x:v>0</x:v>
@@ -9392,22 +9392,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G192" s="111" t="n">
-        <x:v>2.435212</x:v>
+        <x:v>2.422757</x:v>
       </x:c>
       <x:c r="H192" s="111" t="n">
-        <x:v>0.312536</x:v>
+        <x:v>0.295711</x:v>
       </x:c>
       <x:c r="I192" s="111" t="n">
-        <x:v>0.366077</x:v>
+        <x:v>0.286041</x:v>
       </x:c>
       <x:c r="J192" s="111" t="n">
-        <x:v>0.8537438844833191</x:v>
+        <x:v>1.0338063424474113</x:v>
       </x:c>
       <x:c r="K192" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L192" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M192" s="7" t="str">
         <x:v>混合精度已完成：档C：float I/O 下设备端迭代缓冲和有限差分保持 FP64，边界处转换回 float，OFF 不覆盖官方路径。HIP 源码入口：itkHipLevelSetImageFilters.h、itkHipShapeDetectionLevelSetImageFilter.h。OFF/ON 两套完整构建通过；未新增墙钟和 max_abs 实测值。</x:v>
@@ -9436,16 +9436,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G193" s="111" t="n">
-        <x:v>2.441303</x:v>
+        <x:v>2.428527</x:v>
       </x:c>
       <x:c r="H193" s="111" t="n">
-        <x:v>0.307376</x:v>
+        <x:v>0.289021</x:v>
       </x:c>
       <x:c r="I193" s="111" t="n">
-        <x:v>0.301545</x:v>
+        <x:v>0.283531</x:v>
       </x:c>
       <x:c r="J193" s="111" t="n">
-        <x:v>1.0193370807010562</x:v>
+        <x:v>1.0193629620746938</x:v>
       </x:c>
       <x:c r="K193" s="111" t="n">
         <x:v>0</x:v>
@@ -9480,16 +9480,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G194" s="111" t="n">
-        <x:v>1.625438</x:v>
+        <x:v>1.612175</x:v>
       </x:c>
       <x:c r="H194" s="111" t="n">
-        <x:v>0.345086</x:v>
+        <x:v>0.330981</x:v>
       </x:c>
       <x:c r="I194" s="111" t="n">
-        <x:v>0.307136</x:v>
+        <x:v>0.311591</x:v>
       </x:c>
       <x:c r="J194" s="111" t="n">
-        <x:v>1.1235608981037715</x:v>
+        <x:v>1.0622290117493767</x:v>
       </x:c>
       <x:c r="K194" s="111" t="n">
         <x:v>0</x:v>
@@ -9524,16 +9524,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G195" s="111" t="n">
-        <x:v>2.435422</x:v>
+        <x:v>2.425028</x:v>
       </x:c>
       <x:c r="H195" s="111" t="n">
-        <x:v>0.308535</x:v>
+        <x:v>0.293541</x:v>
       </x:c>
       <x:c r="I195" s="111" t="n">
-        <x:v>0.312826</x:v>
+        <x:v>0.298001</x:v>
       </x:c>
       <x:c r="J195" s="111" t="n">
-        <x:v>0.9862831094602111</x:v>
+        <x:v>0.9850336072697742</x:v>
       </x:c>
       <x:c r="K195" s="111" t="n">
         <x:v>0</x:v>
@@ -9568,22 +9568,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G196" s="111" t="n">
-        <x:v>728.071411</x:v>
+        <x:v>747.529608</x:v>
       </x:c>
       <x:c r="H196" s="111" t="n">
-        <x:v>3604.771044</x:v>
+        <x:v>3627.556588</x:v>
       </x:c>
       <x:c r="I196" s="111" t="n">
-        <x:v>3591.086106</x:v>
+        <x:v>3628.421911</x:v>
       </x:c>
       <x:c r="J196" s="111" t="n">
-        <x:v>1.003810807537345</x:v>
+        <x:v>0.9997615153305693</x:v>
       </x:c>
       <x:c r="K196" s="111" t="n">
         <x:v>0.0000768296111298</x:v>
       </x:c>
       <x:c r="L196" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M196" s="7" t="str">
         <x:v>混合精度已完成策略改造：偏置场估计与校正采用保守的FP64内部统计/迭代语义；float I/O保持float，内部RealType不降为FP32；不把偏置场拟合误改成全局COMPUTETYPE=float，也不把CPU参考路径冒充DCU加速。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND/CPU_REFERENCE；静态覆盖=COVERED；保留原接口语义。</x:v>
@@ -9612,22 +9612,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G197" s="111" t="n">
-        <x:v>112.371323</x:v>
+        <x:v>111.698582</x:v>
       </x:c>
       <x:c r="H197" s="111" t="n">
-        <x:v>569.907297</x:v>
+        <x:v>519.607122</x:v>
       </x:c>
       <x:c r="I197" s="111" t="n">
-        <x:v>525.699212</x:v>
+        <x:v>520.820355</x:v>
       </x:c>
       <x:c r="J197" s="111" t="n">
-        <x:v>1.084093877241726</x:v>
+        <x:v>0.9976705345934493</x:v>
       </x:c>
       <x:c r="K197" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L197" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M197" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -9876,16 +9876,16 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G203" s="111" t="n">
-        <x:v>184.606295</x:v>
+        <x:v>184.076857</x:v>
       </x:c>
       <x:c r="H203" s="111" t="n">
-        <x:v>564.458557</x:v>
+        <x:v>520.53403</x:v>
       </x:c>
       <x:c r="I203" s="111" t="n">
-        <x:v>530.235913</x:v>
+        <x:v>516.996122</x:v>
       </x:c>
       <x:c r="J203" s="111" t="n">
-        <x:v>1.0645422974207333</x:v>
+        <x:v>1.0068432002667904</x:v>
       </x:c>
       <x:c r="K203" s="111" t="n">
         <x:v>0</x:v>
@@ -9920,22 +9920,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G204" s="111" t="n">
-        <x:v>184.712317</x:v>
+        <x:v>185.105806</x:v>
       </x:c>
       <x:c r="H204" s="111" t="n">
-        <x:v>196.706727</x:v>
+        <x:v>196.38646</x:v>
       </x:c>
       <x:c r="I204" s="111" t="n">
-        <x:v>196.699941</x:v>
+        <x:v>197.850064</x:v>
       </x:c>
       <x:c r="J204" s="111" t="n">
-        <x:v>1.0000344992477654</x:v>
+        <x:v>0.9926024587993058</x:v>
       </x:c>
       <x:c r="K204" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L204" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M204" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -9964,22 +9964,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G205" s="111" t="n">
-        <x:v>24618.421348</x:v>
+        <x:v>24563.433701</x:v>
       </x:c>
       <x:c r="H205" s="111" t="n">
-        <x:v>9.199354</x:v>
+        <x:v>7.091807</x:v>
       </x:c>
       <x:c r="I205" s="111" t="n">
-        <x:v>11.945758</x:v>
+        <x:v>7.075597</x:v>
       </x:c>
       <x:c r="J205" s="111" t="n">
-        <x:v>0.7700937855931788</x:v>
+        <x:v>1.002290972761733</x:v>
       </x:c>
       <x:c r="K205" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L205" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M205" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -10064,7 +10064,7 @@
         <x:v>1.0060008630454718</x:v>
       </x:c>
       <x:c r="K207" s="111" t="n">
-        <x:v>0.305643781775</x:v>
+        <x:v>3.70277061859</x:v>
       </x:c>
       <x:c r="L207" s="7" t="str">
         <x:v>是</x:v>
@@ -10152,7 +10152,7 @@
         <x:v>1.0122714278008522</x:v>
       </x:c>
       <x:c r="K209" s="111" t="n">
-        <x:v>0.305643781775</x:v>
+        <x:v>3.70277061859</x:v>
       </x:c>
       <x:c r="L209" s="7" t="str">
         <x:v>是</x:v>
@@ -10192,14 +10192,12 @@
       <x:c r="I210" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J210" s="111" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="J210" s="111" t="e"/>
       <x:c r="K210" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L210" s="7" t="str">
-        <x:v>不适用</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M210" s="7" t="str">
         <x:v>不能做混合精度：每个像素不是一个亮度，而是彩色、箭头（位移）或多个数。混合精度对比需要一张灰度亮度图，套不上。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -10260,16 +10258,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G212" s="111" t="n">
-        <x:v>1.759765</x:v>
+        <x:v>1.785665</x:v>
       </x:c>
       <x:c r="H212" s="111" t="n">
-        <x:v>3.304596</x:v>
+        <x:v>3.2298</x:v>
       </x:c>
       <x:c r="I212" s="111" t="n">
-        <x:v>3.225764</x:v>
+        <x:v>3.17196</x:v>
       </x:c>
       <x:c r="J212" s="111" t="n">
-        <x:v>1.0244382416072597</x:v>
+        <x:v>1.0182347822797262</x:v>
       </x:c>
       <x:c r="K212" s="111" t="n">
         <x:v>0</x:v>
@@ -10304,16 +10302,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G213" s="111" t="n">
-        <x:v>17.835956</x:v>
+        <x:v>17.488542</x:v>
       </x:c>
       <x:c r="H213" s="111" t="n">
-        <x:v>18.788315</x:v>
+        <x:v>18.492164</x:v>
       </x:c>
       <x:c r="I213" s="111" t="n">
-        <x:v>18.470749</x:v>
+        <x:v>18.390124</x:v>
       </x:c>
       <x:c r="J213" s="111" t="n">
-        <x:v>1.0171929140502098</x:v>
+        <x:v>1.0055486303409373</x:v>
       </x:c>
       <x:c r="K213" s="111" t="n">
         <x:v>0</x:v>
@@ -10348,22 +10346,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G214" s="111" t="n">
-        <x:v>18.02088</x:v>
+        <x:v>17.723863</x:v>
       </x:c>
       <x:c r="H214" s="111" t="n">
-        <x:v>19.408287</x:v>
+        <x:v>18.856126</x:v>
       </x:c>
       <x:c r="I214" s="111" t="n">
-        <x:v>18.951678</x:v>
+        <x:v>18.963466</x:v>
       </x:c>
       <x:c r="J214" s="111" t="n">
-        <x:v>1.0240933283058102</x:v>
+        <x:v>0.9943396423417533</x:v>
       </x:c>
       <x:c r="K214" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L214" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M214" s="7" t="str">
         <x:v>FFT/频域路径：I/O float/double按同一开关对照；FFT内部不以全局COMPUTETYPE=float代替三档策略。已有 DCU/HIP 入口；使用 build-mixed-on/off 对照构建并运行代表性基准。</x:v>
@@ -10392,22 +10390,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G215" s="111" t="n">
-        <x:v>2.51465</x:v>
+        <x:v>2.307284</x:v>
       </x:c>
       <x:c r="H215" s="111" t="n">
-        <x:v>3.138712</x:v>
+        <x:v>2.825464</x:v>
       </x:c>
       <x:c r="I215" s="111" t="n">
-        <x:v>3.062871</x:v>
+        <x:v>4.093049</x:v>
       </x:c>
       <x:c r="J215" s="111" t="n">
-        <x:v>1.0247614084954932</x:v>
+        <x:v>0.6903078853930164</x:v>
       </x:c>
       <x:c r="K215" s="111" t="n">
         <x:v>6.24204321668e-15</x:v>
       </x:c>
       <x:c r="L215" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M215" s="7" t="str">
         <x:v>不能做混合精度：这是空壳接口，不能单独拿一张图计时。没有可比较的输入输出，所以不能做混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -10556,22 +10554,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G219" s="111" t="n">
-        <x:v>10.343056</x:v>
+        <x:v>10.391621</x:v>
       </x:c>
       <x:c r="H219" s="111" t="n">
-        <x:v>1602.978609</x:v>
+        <x:v>1517.862508</x:v>
       </x:c>
       <x:c r="I219" s="111" t="n">
-        <x:v>1526.515899</x:v>
+        <x:v>1520.782246</x:v>
       </x:c>
       <x:c r="J219" s="111" t="n">
-        <x:v>1.0500896912047164</x:v>
+        <x:v>0.9980801077815844</x:v>
       </x:c>
       <x:c r="K219" s="111" t="n">
         <x:v>8.881784197e-16</x:v>
       </x:c>
       <x:c r="L219" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M219" s="7" t="str">
         <x:v>不能做混合精度：结果往往是一个统计量，或把整张图压成一条/一列，不是整张逐像素灰度图。混合精度要比两张同尺寸亮度图的差，这里对不上。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -10600,16 +10598,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G220" s="111" t="n">
-        <x:v>23.332376</x:v>
+        <x:v>23.334209</x:v>
       </x:c>
       <x:c r="H220" s="111" t="n">
-        <x:v>1.627572</x:v>
+        <x:v>1.626025</x:v>
       </x:c>
       <x:c r="I220" s="111" t="n">
-        <x:v>1.627232</x:v>
+        <x:v>1.625075</x:v>
       </x:c>
       <x:c r="J220" s="111" t="n">
-        <x:v>1.0002089437769168</x:v>
+        <x:v>1.0005845884036122</x:v>
       </x:c>
       <x:c r="K220" s="111" t="n">
         <x:v>0.038273277231</x:v>
@@ -10644,16 +10642,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G221" s="111" t="n">
-        <x:v>7.584011</x:v>
+        <x:v>7.092411</x:v>
       </x:c>
       <x:c r="H221" s="111" t="n">
-        <x:v>1158.574588</x:v>
+        <x:v>1081.270249</x:v>
       </x:c>
       <x:c r="I221" s="111" t="n">
-        <x:v>1091.447084</x:v>
+        <x:v>1079.402834</x:v>
       </x:c>
       <x:c r="J221" s="111" t="n">
-        <x:v>1.0615032143876248</x:v>
+        <x:v>1.001730044559064</x:v>
       </x:c>
       <x:c r="K221" s="111" t="n">
         <x:v>0</x:v>
@@ -10688,22 +10686,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G222" s="111" t="n">
-        <x:v>3.143742</x:v>
+        <x:v>3.837971</x:v>
       </x:c>
       <x:c r="H222" s="111" t="n">
-        <x:v>0.142832</x:v>
+        <x:v>0.137211</x:v>
       </x:c>
       <x:c r="I222" s="111" t="n">
-        <x:v>0.141193</x:v>
+        <x:v>0.163541</x:v>
       </x:c>
       <x:c r="J222" s="111" t="n">
-        <x:v>1.0116082242037492</x:v>
+        <x:v>0.8390006175821354</x:v>
       </x:c>
       <x:c r="K222" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L222" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M222" s="7" t="str">
         <x:v>档B/保精度路径：float I/O可保留，但距离、符号和有限差分内部保持FP64；spacing启动参数接入统一类型选择。新增 itkHipMixedPrecision.h 类型选择；Iso/Maurer 的 spacing kernel 参数与 OFF/ON 对齐，内部距离计算保持FP64。</x:v>
@@ -10732,22 +10730,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G223" s="111" t="n">
-        <x:v>3.354287</x:v>
+        <x:v>3.629131</x:v>
       </x:c>
       <x:c r="H223" s="111" t="n">
-        <x:v>2.723634</x:v>
+        <x:v>2.716298</x:v>
       </x:c>
       <x:c r="I223" s="111" t="n">
-        <x:v>2.719934</x:v>
+        <x:v>2.718158</x:v>
       </x:c>
       <x:c r="J223" s="111" t="n">
-        <x:v>1.0013603271255849</x:v>
+        <x:v>0.9993157130674524</x:v>
       </x:c>
       <x:c r="K223" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L223" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M223" s="7" t="str">
         <x:v>档B/保精度路径：float I/O可保留，但距离、符号和有限差分内部保持FP64；spacing启动参数接入统一类型选择。新增 itkHipMixedPrecision.h 类型选择；Iso/Maurer 的 spacing kernel 参数与 OFF/ON 对齐，内部距离计算保持FP64。</x:v>
@@ -10776,22 +10774,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G224" s="111" t="n">
-        <x:v>8.13468297323</x:v>
+        <x:v>7.2603225708</x:v>
       </x:c>
       <x:c r="H224" s="111" t="n">
-        <x:v>2.26942698161</x:v>
+        <x:v>2.25234031677</x:v>
       </x:c>
       <x:c r="I224" s="111" t="n">
-        <x:v>2.25432713826</x:v>
+        <x:v>2.25631395976</x:v>
       </x:c>
       <x:c r="J224" s="111" t="n">
-        <x:v>1.0066981597718134</x:v>
+        <x:v>0.9982388785156376</x:v>
       </x:c>
       <x:c r="K224" s="111" t="n">
         <x:v>0.0000370085975023</x:v>
       </x:c>
       <x:c r="L224" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M224" s="7" t="str">
         <x:v>不能做混合精度：这是空壳接口，不能单独拿一张图计时。没有可比较的输入输出，所以不能做混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -10820,22 +10818,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G225" s="111" t="n">
-        <x:v>39.536635081</x:v>
+        <x:v>47.6717154185</x:v>
       </x:c>
       <x:c r="H225" s="111" t="n">
-        <x:v>4.11001841227</x:v>
+        <x:v>4.03801600138</x:v>
       </x:c>
       <x:c r="I225" s="111" t="n">
-        <x:v>4.0590763092</x:v>
+        <x:v>4.03960545858</x:v>
       </x:c>
       <x:c r="J225" s="111" t="n">
-        <x:v>1.012550171317188</x:v>
+        <x:v>0.9996065315743586</x:v>
       </x:c>
       <x:c r="K225" s="111" t="n">
         <x:v>0.00138523908407</x:v>
       </x:c>
       <x:c r="L225" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M225" s="7" t="str">
         <x:v>不能做混合精度：这是空壳接口，不能单独拿一张图计时。没有可比较的输入输出，所以不能做混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -10864,22 +10862,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G226" s="111" t="n">
-        <x:v>0.205993652344</x:v>
+        <x:v>0.160535176595</x:v>
       </x:c>
       <x:c r="H226" s="111" t="n">
-        <x:v>0.297784805298</x:v>
+        <x:v>0.291347503662</x:v>
       </x:c>
       <x:c r="I226" s="111" t="n">
-        <x:v>0.300010045369</x:v>
+        <x:v>0.290711720785</x:v>
       </x:c>
       <x:c r="J226" s="111" t="n">
-        <x:v>0.9925827814589907</x:v>
+        <x:v>1.0021869874227403</x:v>
       </x:c>
       <x:c r="K226" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L226" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M226" s="7" t="str">
         <x:v>FFT/频域路径：I/O float/double按同一开关对照；FFT内部不以全局COMPUTETYPE=float代替三档策略。新增 itkHipMixedPrecision.h 类型选择，并在 HIP kernel 中显式使用 COMPUTETYPE。</x:v>
@@ -10908,16 +10906,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G227" s="111" t="n">
-        <x:v>9.29133097331</x:v>
+        <x:v>8.39726130168</x:v>
       </x:c>
       <x:c r="H227" s="111" t="n">
-        <x:v>0.298579533895</x:v>
+        <x:v>0.287294387817</x:v>
       </x:c>
       <x:c r="I227" s="111" t="n">
-        <x:v>0.298897425334</x:v>
+        <x:v>0.288963317871</x:v>
       </x:c>
       <x:c r="J227" s="111" t="n">
-        <x:v>0.998936453070331</x:v>
+        <x:v>0.9942244224412421</x:v>
       </x:c>
       <x:c r="K227" s="111" t="n">
         <x:v>0</x:v>
@@ -10952,22 +10950,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G228" s="111" t="n">
-        <x:v>8.13468297323</x:v>
+        <x:v>7.2603225708</x:v>
       </x:c>
       <x:c r="H228" s="111" t="n">
-        <x:v>2.26942698161</x:v>
+        <x:v>2.25234031677</x:v>
       </x:c>
       <x:c r="I228" s="111" t="n">
-        <x:v>2.25432713826</x:v>
+        <x:v>2.25631395976</x:v>
       </x:c>
       <x:c r="J228" s="111" t="n">
-        <x:v>1.0066981597718134</x:v>
+        <x:v>0.9982388785156376</x:v>
       </x:c>
       <x:c r="K228" s="111" t="n">
-        <x:v>0.0000139609783935</x:v>
+        <x:v>0.0000370085975023</x:v>
       </x:c>
       <x:c r="L228" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M228" s="7" t="str">
         <x:v>不能做混合精度：每个像素不是一个亮度，而是彩色、箭头（位移）或多个数。混合精度对比需要一张灰度亮度图，套不上。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -10996,22 +10994,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G229" s="111" t="n">
-        <x:v>39.536635081</x:v>
+        <x:v>47.6717154185</x:v>
       </x:c>
       <x:c r="H229" s="111" t="n">
-        <x:v>4.11001841227</x:v>
+        <x:v>4.03801600138</x:v>
       </x:c>
       <x:c r="I229" s="111" t="n">
-        <x:v>4.0590763092</x:v>
+        <x:v>4.03960545858</x:v>
       </x:c>
       <x:c r="J229" s="111" t="n">
-        <x:v>1.012550171317188</x:v>
+        <x:v>0.9996065315743586</x:v>
       </x:c>
       <x:c r="K229" s="111" t="n">
-        <x:v>0.000268077826012</x:v>
+        <x:v>0.00138523908407</x:v>
       </x:c>
       <x:c r="L229" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M229" s="7" t="str">
         <x:v>不能做混合精度：每个像素不是一个亮度，而是彩色、箭头（位移）或多个数。混合精度对比需要一张灰度亮度图，套不上。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -11040,19 +11038,19 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G230" s="111" t="n">
-        <x:v>5.18337885539</x:v>
+        <x:v>4.91229693095</x:v>
       </x:c>
       <x:c r="H230" s="111" t="n">
-        <x:v>2.28198369344</x:v>
+        <x:v>2.34834353129</x:v>
       </x:c>
       <x:c r="I230" s="111" t="n">
-        <x:v>2.27332115173</x:v>
+        <x:v>2.26267178853</x:v>
       </x:c>
       <x:c r="J230" s="111" t="n">
-        <x:v>1.0038105226370713</x:v>
+        <x:v>1.0378630887582942</x:v>
       </x:c>
       <x:c r="K230" s="111" t="n">
-        <x:v>0.0000293569813523</x:v>
+        <x:v>0.0000782239242948</x:v>
       </x:c>
       <x:c r="L230" s="7" t="str">
         <x:v>是</x:v>
@@ -11116,22 +11114,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G232" s="111" t="n">
-        <x:v>53.2822608948</x:v>
+        <x:v>62.2416337331</x:v>
       </x:c>
       <x:c r="H232" s="111" t="n">
-        <x:v>4.19998168945</x:v>
+        <x:v>4.16771570841</x:v>
       </x:c>
       <x:c r="I232" s="111" t="n">
-        <x:v>4.19060389201</x:v>
+        <x:v>4.17264302572</x:v>
       </x:c>
       <x:c r="J232" s="111" t="n">
-        <x:v>1.002237815284303</x:v>
+        <x:v>0.9988191375874648</x:v>
       </x:c>
       <x:c r="K232" s="111" t="n">
-        <x:v>0.00000576637281426</x:v>
+        <x:v>0.00000939879432311</x:v>
       </x:c>
       <x:c r="L232" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M232" s="7" t="str">
         <x:v>不能做混合精度：依赖特定傅里叶变换库，当前统一测试口径不具备可比的混合精度时间。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -11160,19 +11158,19 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G233" s="111" t="n">
-        <x:v>8.32486152649</x:v>
+        <x:v>7.83220926921</x:v>
       </x:c>
       <x:c r="H233" s="111" t="n">
-        <x:v>2.24216779073</x:v>
+        <x:v>2.22301483154</x:v>
       </x:c>
       <x:c r="I233" s="111" t="n">
-        <x:v>2.24296251933</x:v>
+        <x:v>2.2280216217</x:v>
       </x:c>
       <x:c r="J233" s="111" t="n">
-        <x:v>0.9996456790547542</x:v>
+        <x:v>0.9977528089892683</x:v>
       </x:c>
       <x:c r="K233" s="111" t="n">
-        <x:v>1.10313060375e-7</x:v>
+        <x:v>7.27498048381e-8</x:v>
       </x:c>
       <x:c r="L233" s="7" t="str">
         <x:v>否</x:v>
@@ -11204,22 +11202,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G234" s="111" t="n">
-        <x:v>30.5463473002</x:v>
+        <x:v>39.1206741333</x:v>
       </x:c>
       <x:c r="H234" s="111" t="n">
-        <x:v>4.08554077148</x:v>
+        <x:v>4.01035944621</x:v>
       </x:c>
       <x:c r="I234" s="111" t="n">
-        <x:v>4.0340423584</x:v>
+        <x:v>4.09436225891</x:v>
       </x:c>
       <x:c r="J234" s="111" t="n">
-        <x:v>1.0127659574453318</x:v>
+        <x:v>0.9794832974250882</x:v>
       </x:c>
       <x:c r="K234" s="111" t="n">
-        <x:v>1.69404973523e-8</x:v>
+        <x:v>5.10058993471e-9</x:v>
       </x:c>
       <x:c r="L234" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M234" s="7" t="str">
         <x:v>不能做混合精度：依赖特定傅里叶变换库，当前统一测试口径不具备可比的混合精度时间。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -11248,22 +11246,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G235" s="111" t="n">
-        <x:v>36.9629859924</x:v>
+        <x:v>44.2893505096</x:v>
       </x:c>
       <x:c r="H235" s="111" t="n">
-        <x:v>4.22199567159</x:v>
+        <x:v>4.18504079183</x:v>
       </x:c>
       <x:c r="I235" s="111" t="n">
-        <x:v>4.2146841685</x:v>
+        <x:v>4.20069694519</x:v>
       </x:c>
       <x:c r="J235" s="111" t="n">
-        <x:v>1.0017347689168847</x:v>
+        <x:v>0.996272962900138</x:v>
       </x:c>
       <x:c r="K235" s="111" t="n">
-        <x:v>0.000452652930617</x:v>
+        <x:v>0.00247085012833</x:v>
       </x:c>
       <x:c r="L235" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M235" s="7" t="str">
         <x:v>不能做混合精度：依赖特定傅里叶变换库，当前统一测试口径不具备可比的混合精度时间。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -11292,16 +11290,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G236" s="111" t="n">
-        <x:v>5.18337885539</x:v>
+        <x:v>4.91229693095</x:v>
       </x:c>
       <x:c r="H236" s="111" t="n">
-        <x:v>2.28198369344</x:v>
+        <x:v>2.34834353129</x:v>
       </x:c>
       <x:c r="I236" s="111" t="n">
-        <x:v>2.27332115173</x:v>
+        <x:v>2.26267178853</x:v>
       </x:c>
       <x:c r="J236" s="111" t="n">
-        <x:v>1.0038105226370713</x:v>
+        <x:v>1.0378630887582942</x:v>
       </x:c>
       <x:c r="K236" s="111" t="n">
         <x:v>0.0000782239242948</x:v>
@@ -11368,22 +11366,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G238" s="111" t="n">
-        <x:v>0.26265780131</x:v>
+        <x:v>0.330607096354</x:v>
       </x:c>
       <x:c r="H238" s="111" t="n">
-        <x:v>0.304381052653</x:v>
+        <x:v>0.299374262492</x:v>
       </x:c>
       <x:c r="I238" s="111" t="n">
-        <x:v>0.304619471232</x:v>
+        <x:v>0.297546386719</x:v>
       </x:c>
       <x:c r="J238" s="111" t="n">
-        <x:v>0.9992173232458327</x:v>
+        <x:v>1.0061431623927808</x:v>
       </x:c>
       <x:c r="K238" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L238" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M238" s="7" t="str">
         <x:v>不能做混合精度：输出是频谱（每个点两个数：实部+虚部），不是灰度亮度图。不能按「一张单精度灰图 vs 一张双精度灰图」去填混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -11412,22 +11410,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G239" s="111" t="n">
-        <x:v>53.2822608948</x:v>
+        <x:v>62.2416337331</x:v>
       </x:c>
       <x:c r="H239" s="111" t="n">
-        <x:v>4.19998168945</x:v>
+        <x:v>4.16771570841</x:v>
       </x:c>
       <x:c r="I239" s="111" t="n">
-        <x:v>4.19060389201</x:v>
+        <x:v>4.17264302572</x:v>
       </x:c>
       <x:c r="J239" s="111" t="n">
-        <x:v>1.002237815284303</x:v>
+        <x:v>0.9988191375874648</x:v>
       </x:c>
       <x:c r="K239" s="111" t="n">
         <x:v>0.00000939879432311</x:v>
       </x:c>
       <x:c r="L239" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M239" s="7" t="str">
         <x:v>不能做混合精度：这是空壳接口，不能单独拿一张图计时。没有可比较的输入输出，所以不能做混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -11456,22 +11454,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G240" s="111" t="n">
-        <x:v>8.45789909363</x:v>
+        <x:v>8.27066103617</x:v>
       </x:c>
       <x:c r="H240" s="111" t="n">
-        <x:v>0.488678614299</x:v>
+        <x:v>0.485022862752</x:v>
       </x:c>
       <x:c r="I240" s="111" t="n">
-        <x:v>0.495036443075</x:v>
+        <x:v>0.483671824137</x:v>
       </x:c>
       <x:c r="J240" s="111" t="n">
-        <x:v>0.987156847006036</x:v>
+        <x:v>1.002793296089576</x:v>
       </x:c>
       <x:c r="K240" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L240" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M240" s="7" t="str">
         <x:v>不能做混合精度：输出是频谱（每个点两个数：实部+虚部），不是灰度亮度图。不能按「一张单精度灰图 vs 一张双精度灰图」去填混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -11500,16 +11498,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G241" s="111" t="n">
-        <x:v>8.32486152649</x:v>
+        <x:v>7.83220926921</x:v>
       </x:c>
       <x:c r="H241" s="111" t="n">
-        <x:v>2.24216779073</x:v>
+        <x:v>2.22301483154</x:v>
       </x:c>
       <x:c r="I241" s="111" t="n">
-        <x:v>2.24296251933</x:v>
+        <x:v>2.2280216217</x:v>
       </x:c>
       <x:c r="J241" s="111" t="n">
-        <x:v>0.9996456790547542</x:v>
+        <x:v>0.9977528089892683</x:v>
       </x:c>
       <x:c r="K241" s="111" t="n">
         <x:v>7.27498048381e-8</x:v>
@@ -11544,22 +11542,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G242" s="111" t="n">
-        <x:v>30.5463473002</x:v>
+        <x:v>39.1206741333</x:v>
       </x:c>
       <x:c r="H242" s="111" t="n">
-        <x:v>4.08554077148</x:v>
+        <x:v>4.01035944621</x:v>
       </x:c>
       <x:c r="I242" s="111" t="n">
-        <x:v>4.0340423584</x:v>
+        <x:v>4.09436225891</x:v>
       </x:c>
       <x:c r="J242" s="111" t="n">
-        <x:v>1.0127659574453318</x:v>
+        <x:v>0.9794832974250882</x:v>
       </x:c>
       <x:c r="K242" s="111" t="n">
         <x:v>5.10058993471e-9</x:v>
       </x:c>
       <x:c r="L242" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M242" s="7" t="str">
         <x:v>不能做混合精度：这是空壳接口，不能单独拿一张图计时。没有可比较的输入输出，所以不能做混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -11588,22 +11586,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G243" s="111" t="n">
-        <x:v>36.9629859924</x:v>
+        <x:v>44.2893505096</x:v>
       </x:c>
       <x:c r="H243" s="111" t="n">
-        <x:v>4.22199567159</x:v>
+        <x:v>4.18504079183</x:v>
       </x:c>
       <x:c r="I243" s="111" t="n">
-        <x:v>4.2146841685</x:v>
+        <x:v>4.20069694519</x:v>
       </x:c>
       <x:c r="J243" s="111" t="n">
-        <x:v>1.0017347689168847</x:v>
+        <x:v>0.996272962900138</x:v>
       </x:c>
       <x:c r="K243" s="111" t="n">
         <x:v>0.00247085012833</x:v>
       </x:c>
       <x:c r="L243" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M243" s="7" t="str">
         <x:v>不能做混合精度：这是空壳接口，不能单独拿一张图计时。没有可比较的输入输出，所以不能做混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -11632,22 +11630,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G244" s="111" t="n">
-        <x:v>8.13468297323</x:v>
+        <x:v>7.2603225708</x:v>
       </x:c>
       <x:c r="H244" s="111" t="n">
-        <x:v>2.26942698161</x:v>
+        <x:v>2.25234031677</x:v>
       </x:c>
       <x:c r="I244" s="111" t="n">
-        <x:v>2.25432713826</x:v>
+        <x:v>2.25631395976</x:v>
       </x:c>
       <x:c r="J244" s="111" t="n">
-        <x:v>1.0066981597718134</x:v>
+        <x:v>0.9982388785156376</x:v>
       </x:c>
       <x:c r="K244" s="111" t="n">
-        <x:v>0.0000139609783935</x:v>
+        <x:v>0.0000370085975023</x:v>
       </x:c>
       <x:c r="L244" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M244" s="7" t="str">
         <x:v>FFT/频域路径：I/O float/double按同一开关对照；FFT内部不以全局COMPUTETYPE=float代替三档策略。已有 DCU/HIP 入口；使用 build-mixed-on/off 对照构建并运行代表性基准。</x:v>
@@ -11676,22 +11674,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G245" s="111" t="n">
-        <x:v>39.536635081</x:v>
+        <x:v>47.6717154185</x:v>
       </x:c>
       <x:c r="H245" s="111" t="n">
-        <x:v>4.11001841227</x:v>
+        <x:v>4.03801600138</x:v>
       </x:c>
       <x:c r="I245" s="111" t="n">
-        <x:v>4.0590763092</x:v>
+        <x:v>4.03960545858</x:v>
       </x:c>
       <x:c r="J245" s="111" t="n">
-        <x:v>1.012550171317188</x:v>
+        <x:v>0.9996065315743586</x:v>
       </x:c>
       <x:c r="K245" s="111" t="n">
-        <x:v>0.000268077826012</x:v>
+        <x:v>0.00138523908407</x:v>
       </x:c>
       <x:c r="L245" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M245" s="7" t="str">
         <x:v>FFT/频域路径：I/O float/double按同一开关对照；FFT内部不以全局COMPUTETYPE=float代替三档策略。已有 DCU/HIP 入口；使用 build-mixed-on/off 对照构建并运行代表性基准。</x:v>
@@ -11720,19 +11718,19 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G246" s="111" t="n">
-        <x:v>5.18337885539</x:v>
+        <x:v>4.91229693095</x:v>
       </x:c>
       <x:c r="H246" s="111" t="n">
-        <x:v>2.28198369344</x:v>
+        <x:v>2.34834353129</x:v>
       </x:c>
       <x:c r="I246" s="111" t="n">
-        <x:v>2.27332115173</x:v>
+        <x:v>2.26267178853</x:v>
       </x:c>
       <x:c r="J246" s="111" t="n">
-        <x:v>1.0038105226370713</x:v>
+        <x:v>1.0378630887582942</x:v>
       </x:c>
       <x:c r="K246" s="111" t="n">
-        <x:v>0.0000293569813523</x:v>
+        <x:v>0.0000782239242948</x:v>
       </x:c>
       <x:c r="L246" s="7" t="str">
         <x:v>是</x:v>
@@ -11828,19 +11826,19 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G249" s="111" t="n">
-        <x:v>8.32486152649</x:v>
+        <x:v>7.83220926921</x:v>
       </x:c>
       <x:c r="H249" s="111" t="n">
-        <x:v>2.24216779073</x:v>
+        <x:v>2.22301483154</x:v>
       </x:c>
       <x:c r="I249" s="111" t="n">
-        <x:v>2.24296251933</x:v>
+        <x:v>2.2280216217</x:v>
       </x:c>
       <x:c r="J249" s="111" t="n">
-        <x:v>0.9996456790547542</x:v>
+        <x:v>0.9977528089892683</x:v>
       </x:c>
       <x:c r="K249" s="111" t="n">
-        <x:v>1.10313060375e-7</x:v>
+        <x:v>7.27498048381e-8</x:v>
       </x:c>
       <x:c r="L249" s="7" t="str">
         <x:v>否</x:v>
@@ -11936,16 +11934,16 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G252" s="111" t="n">
-        <x:v>345.901727676</x:v>
+        <x:v>342.693090439</x:v>
       </x:c>
       <x:c r="H252" s="111" t="n">
-        <x:v>384.038607279</x:v>
+        <x:v>381.663958232</x:v>
       </x:c>
       <x:c r="I252" s="111" t="n">
-        <x:v>381.690263748</x:v>
+        <x:v>381.403048833</x:v>
       </x:c>
       <x:c r="J252" s="111" t="n">
-        <x:v>1.006152484760655</x:v>
+        <x:v>1.0006840779060322</x:v>
       </x:c>
       <x:c r="K252" s="111" t="n">
         <x:v>0</x:v>
@@ -11980,16 +11978,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G253" s="111" t="n">
-        <x:v>345.901727676</x:v>
+        <x:v>342.693090439</x:v>
       </x:c>
       <x:c r="H253" s="111" t="n">
-        <x:v>384.038607279</x:v>
+        <x:v>381.663958232</x:v>
       </x:c>
       <x:c r="I253" s="111" t="n">
-        <x:v>381.690263748</x:v>
+        <x:v>381.403048833</x:v>
       </x:c>
       <x:c r="J253" s="111" t="n">
-        <x:v>1.006152484760655</x:v>
+        <x:v>1.0006840779060322</x:v>
       </x:c>
       <x:c r="K253" s="111" t="n">
         <x:v>0</x:v>
@@ -12088,16 +12086,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G256" s="111" t="n">
-        <x:v>345.901727676</x:v>
+        <x:v>342.693090439</x:v>
       </x:c>
       <x:c r="H256" s="111" t="n">
-        <x:v>384.038607279</x:v>
+        <x:v>381.663958232</x:v>
       </x:c>
       <x:c r="I256" s="111" t="n">
-        <x:v>381.690263748</x:v>
+        <x:v>381.403048833</x:v>
       </x:c>
       <x:c r="J256" s="111" t="n">
-        <x:v>1.006152484760655</x:v>
+        <x:v>1.0006840779060322</x:v>
       </x:c>
       <x:c r="K256" s="111" t="n">
         <x:v>0</x:v>
@@ -12132,16 +12130,16 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G257" s="111" t="n">
-        <x:v>345.901727676</x:v>
+        <x:v>342.693090439</x:v>
       </x:c>
       <x:c r="H257" s="111" t="n">
-        <x:v>384.038607279</x:v>
+        <x:v>381.663958232</x:v>
       </x:c>
       <x:c r="I257" s="111" t="n">
-        <x:v>381.690263748</x:v>
+        <x:v>381.403048833</x:v>
       </x:c>
       <x:c r="J257" s="111" t="n">
-        <x:v>1.006152484760655</x:v>
+        <x:v>1.0006840779060322</x:v>
       </x:c>
       <x:c r="K257" s="111" t="n">
         <x:v>0</x:v>
@@ -12400,22 +12398,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G265" s="111" t="n">
-        <x:v>26.422238</x:v>
+        <x:v>28.836975</x:v>
       </x:c>
       <x:c r="H265" s="111" t="n">
-        <x:v>0.980289</x:v>
+        <x:v>0.884103</x:v>
       </x:c>
       <x:c r="I265" s="111" t="n">
-        <x:v>0.893357</x:v>
+        <x:v>0.890213</x:v>
       </x:c>
       <x:c r="J265" s="111" t="n">
-        <x:v>1.097309362326595</x:v>
+        <x:v>0.9931364740797988</x:v>
       </x:c>
       <x:c r="K265" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L265" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M265" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -12444,22 +12442,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G266" s="111" t="n">
-        <x:v>56.686922</x:v>
+        <x:v>60.068327</x:v>
       </x:c>
       <x:c r="H266" s="111" t="n">
-        <x:v>0.434728</x:v>
+        <x:v>0.478701</x:v>
       </x:c>
       <x:c r="I266" s="111" t="n">
-        <x:v>0.49602</x:v>
+        <x:v>0.436772</x:v>
       </x:c>
       <x:c r="J266" s="111" t="n">
-        <x:v>0.8764324019192774</x:v>
+        <x:v>1.0959974540492523</x:v>
       </x:c>
       <x:c r="K266" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L266" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M266" s="7" t="str">
         <x:v>不能做混合精度：结果往往是一个统计量，或把整张图压成一条/一列，不是整张逐像素灰度图。混合精度要比两张同尺寸亮度图的差，这里对不上。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -12488,22 +12486,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G267" s="111" t="n">
-        <x:v>96.323302</x:v>
+        <x:v>96.168633</x:v>
       </x:c>
       <x:c r="H267" s="111" t="n">
-        <x:v>7.619632</x:v>
+        <x:v>6.796201</x:v>
       </x:c>
       <x:c r="I267" s="111" t="n">
-        <x:v>7.628372</x:v>
+        <x:v>6.577237</x:v>
       </x:c>
       <x:c r="J267" s="111" t="n">
-        <x:v>0.9988542771642496</x:v>
+        <x:v>1.0332911829085678</x:v>
       </x:c>
       <x:c r="K267" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L267" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M267" s="7" t="str">
         <x:v>不能做混合精度：每个像素不是一个亮度，而是彩色、箭头（位移）或多个数。混合精度对比需要一张灰度亮度图，套不上。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -12532,16 +12530,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G268" s="111" t="n">
-        <x:v>80.612069</x:v>
+        <x:v>80.647844</x:v>
       </x:c>
       <x:c r="H268" s="111" t="n">
-        <x:v>5.290986</x:v>
+        <x:v>4.752332</x:v>
       </x:c>
       <x:c r="I268" s="111" t="n">
-        <x:v>5.52535</x:v>
+        <x:v>4.765082</x:v>
       </x:c>
       <x:c r="J268" s="111" t="n">
-        <x:v>0.9575838634656628</x:v>
+        <x:v>0.9973242852903687</x:v>
       </x:c>
       <x:c r="K268" s="111" t="n">
         <x:v>0</x:v>
@@ -12576,22 +12574,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G269" s="111" t="n">
-        <x:v>156.976973</x:v>
+        <x:v>157.123088</x:v>
       </x:c>
       <x:c r="H269" s="111" t="n">
-        <x:v>8.175074</x:v>
+        <x:v>7.565215</x:v>
       </x:c>
       <x:c r="I269" s="111" t="n">
-        <x:v>8.52686</x:v>
+        <x:v>7.401862</x:v>
       </x:c>
       <x:c r="J269" s="111" t="n">
-        <x:v>0.9587437814154333</x:v>
+        <x:v>1.0220691766477137</x:v>
       </x:c>
       <x:c r="K269" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L269" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M269" s="7" t="str">
         <x:v>不能做混合精度：每个像素不是一个亮度，而是彩色、箭头（位移）或多个数。混合精度对比需要一张灰度亮度图，套不上。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -13300,22 +13298,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G289" s="111" t="n">
-        <x:v>0.536449</x:v>
+        <x:v>0.462822</x:v>
       </x:c>
       <x:c r="H289" s="111" t="n">
-        <x:v>0.145752</x:v>
+        <x:v>0.13203</x:v>
       </x:c>
       <x:c r="I289" s="111" t="n">
-        <x:v>0.145023</x:v>
+        <x:v>0.13536</x:v>
       </x:c>
       <x:c r="J289" s="111" t="n">
-        <x:v>1.0050267888541815</x:v>
+        <x:v>0.9753989361702128</x:v>
       </x:c>
       <x:c r="K289" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L289" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M289" s="7" t="str">
         <x:v>不能做混合精度：输出是频谱（每个点两个数：实部+虚部），不是灰度亮度图。不能按「一张单精度灰图 vs 一张双精度灰图」去填混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -13344,22 +13342,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G290" s="111" t="n">
-        <x:v>0.536449</x:v>
+        <x:v>0.462822</x:v>
       </x:c>
       <x:c r="H290" s="111" t="n">
-        <x:v>0.145752</x:v>
+        <x:v>0.13203</x:v>
       </x:c>
       <x:c r="I290" s="111" t="n">
-        <x:v>0.145023</x:v>
+        <x:v>0.13536</x:v>
       </x:c>
       <x:c r="J290" s="111" t="n">
-        <x:v>1.0050267888541815</x:v>
+        <x:v>0.9753989361702128</x:v>
       </x:c>
       <x:c r="K290" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L290" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M290" s="7" t="str">
         <x:v>不能做混合精度：输出是频谱（每个点两个数：实部+虚部），不是灰度亮度图。不能按「一张单精度灰图 vs 一张双精度灰图」去填混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -13608,16 +13606,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G296" s="111" t="n">
-        <x:v>37.463757</x:v>
+        <x:v>37.503261</x:v>
       </x:c>
       <x:c r="H296" s="111" t="n">
-        <x:v>0.699154</x:v>
+        <x:v>0.696412</x:v>
       </x:c>
       <x:c r="I296" s="111" t="n">
-        <x:v>0.688214</x:v>
+        <x:v>0.686002</x:v>
       </x:c>
       <x:c r="J296" s="111" t="n">
-        <x:v>1.015896218327439</x:v>
+        <x:v>1.0151748828720617</x:v>
       </x:c>
       <x:c r="K296" s="111" t="n">
         <x:v>0</x:v>
@@ -13652,16 +13650,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G297" s="111" t="n">
-        <x:v>95.513067</x:v>
+        <x:v>91.53033</x:v>
       </x:c>
       <x:c r="H297" s="111" t="n">
-        <x:v>4094.642818</x:v>
+        <x:v>4044.58295</x:v>
       </x:c>
       <x:c r="I297" s="111" t="n">
-        <x:v>4031.614776</x:v>
+        <x:v>4033.435087</x:v>
       </x:c>
       <x:c r="J297" s="111" t="n">
-        <x:v>1.0156334485068372</x:v>
+        <x:v>1.002763863247962</x:v>
       </x:c>
       <x:c r="K297" s="111" t="n">
         <x:v>6.66739220285e-7</x:v>
@@ -13696,22 +13694,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G298" s="111" t="n">
-        <x:v>450.573035</x:v>
+        <x:v>445.924295</x:v>
       </x:c>
       <x:c r="H298" s="111" t="n">
-        <x:v>470.701726</x:v>
+        <x:v>461.706692</x:v>
       </x:c>
       <x:c r="I298" s="111" t="n">
-        <x:v>462.31358</x:v>
+        <x:v>462.491384</x:v>
       </x:c>
       <x:c r="J298" s="111" t="n">
-        <x:v>1.0181438451364548</x:v>
+        <x:v>0.9983033370411933</x:v>
       </x:c>
       <x:c r="K298" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L298" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M298" s="7" t="str">
         <x:v>不能做混合精度：每个像素输出的是方向（两个数），不是一个亮度。没法用「一张灰度图单精度 vs 双精度」去比，故不填混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -13988,16 +13986,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G306" s="111" t="n">
-        <x:v>3.595547</x:v>
+        <x:v>2.864459</x:v>
       </x:c>
       <x:c r="H306" s="111" t="n">
-        <x:v>0.214722</x:v>
+        <x:v>0.20894</x:v>
       </x:c>
       <x:c r="I306" s="111" t="n">
-        <x:v>0.212352</x:v>
+        <x:v>0.206341</x:v>
       </x:c>
       <x:c r="J306" s="111" t="n">
-        <x:v>1.0111607142857142</x:v>
+        <x:v>1.012595654765655</x:v>
       </x:c>
       <x:c r="K306" s="111" t="n">
         <x:v>0</x:v>
@@ -14032,22 +14030,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G307" s="111" t="n">
-        <x:v>3.627362</x:v>
+        <x:v>4.627692</x:v>
       </x:c>
       <x:c r="H307" s="111" t="n">
-        <x:v>0.222945</x:v>
+        <x:v>0.218094</x:v>
       </x:c>
       <x:c r="I307" s="111" t="n">
-        <x:v>0.223174</x:v>
+        <x:v>0.217635</x:v>
       </x:c>
       <x:c r="J307" s="111" t="n">
-        <x:v>0.998973894808535</x:v>
+        <x:v>1.0021090357709008</x:v>
       </x:c>
       <x:c r="K307" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L307" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M307" s="7" t="str">
         <x:v>不能做混合精度：这是按位与/或/非，像素必须是整数（是/不是）。用单精度、双精度小数没有意义，所以不填混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -14118,22 +14116,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G309" s="111" t="n">
-        <x:v>11.712984</x:v>
+        <x:v>11.729313</x:v>
       </x:c>
       <x:c r="H309" s="111" t="n">
-        <x:v>12.139072</x:v>
+        <x:v>12.121391</x:v>
       </x:c>
       <x:c r="I309" s="111" t="n">
-        <x:v>12.127442</x:v>
+        <x:v>15.001547</x:v>
       </x:c>
       <x:c r="J309" s="111" t="n">
-        <x:v>1.0009589821167564</x:v>
+        <x:v>0.8080094006304815</x:v>
       </x:c>
       <x:c r="K309" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L309" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M309" s="7" t="str">
         <x:v>不能做混合精度：需要掩膜或第二张图，单张 2D、1024×1024 灰度切片不够。未测混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -14162,22 +14160,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G310" s="111" t="n">
-        <x:v>3.262965</x:v>
+        <x:v>3.229534</x:v>
       </x:c>
       <x:c r="H310" s="111" t="n">
-        <x:v>0.286146</x:v>
+        <x:v>0.279076</x:v>
       </x:c>
       <x:c r="I310" s="111" t="n">
-        <x:v>0.283325</x:v>
+        <x:v>0.279875</x:v>
       </x:c>
       <x:c r="J310" s="111" t="n">
-        <x:v>1.0099567634342188</x:v>
+        <x:v>0.9971451540866458</x:v>
       </x:c>
       <x:c r="K310" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L310" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M310" s="7" t="str">
         <x:v>不能做混合精度：这是按位与/或/非，像素必须是整数（是/不是）。用单精度、双精度小数没有意义，所以不填混合精度。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -14206,16 +14204,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G311" s="111" t="n">
-        <x:v>5.455238</x:v>
+        <x:v>3.617782</x:v>
       </x:c>
       <x:c r="H311" s="111" t="n">
-        <x:v>0.224345</x:v>
+        <x:v>0.215654</x:v>
       </x:c>
       <x:c r="I311" s="111" t="n">
-        <x:v>0.220355</x:v>
+        <x:v>0.213424</x:v>
       </x:c>
       <x:c r="J311" s="111" t="n">
-        <x:v>1.0181071452882848</x:v>
+        <x:v>1.0104486843091687</x:v>
       </x:c>
       <x:c r="K311" s="111" t="n">
         <x:v>0</x:v>
@@ -14250,16 +14248,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G312" s="111" t="n">
-        <x:v>70.540741</x:v>
+        <x:v>56.468207</x:v>
       </x:c>
       <x:c r="H312" s="111" t="n">
-        <x:v>0.479756</x:v>
+        <x:v>0.469731</x:v>
       </x:c>
       <x:c r="I312" s="111" t="n">
-        <x:v>0.477706</x:v>
+        <x:v>0.468381</x:v>
       </x:c>
       <x:c r="J312" s="111" t="n">
-        <x:v>1.0042913423737612</x:v>
+        <x:v>1.0028822689220955</x:v>
       </x:c>
       <x:c r="K312" s="111" t="n">
         <x:v>0</x:v>
@@ -14338,22 +14336,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G314" s="111" t="n">
-        <x:v>156.615373</x:v>
+        <x:v>156.548482</x:v>
       </x:c>
       <x:c r="H314" s="111" t="n">
-        <x:v>1.609681</x:v>
+        <x:v>1.446354</x:v>
       </x:c>
       <x:c r="I314" s="111" t="n">
-        <x:v>1.49569</x:v>
+        <x:v>1.450184</x:v>
       </x:c>
       <x:c r="J314" s="111" t="n">
-        <x:v>1.0762129853111273</x:v>
+        <x:v>0.9973589558290534</x:v>
       </x:c>
       <x:c r="K314" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L314" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M314" s="7" t="str">
         <x:v>不能做混合精度：每个像素不是一个亮度，而是彩色、箭头（位移）或多个数。混合精度对比需要一张灰度亮度图，套不上。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -14426,16 +14424,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G316" s="111" t="n">
-        <x:v>5.474119</x:v>
+        <x:v>4.586331</x:v>
       </x:c>
       <x:c r="H316" s="111" t="n">
-        <x:v>0.224764</x:v>
+        <x:v>0.215374</x:v>
       </x:c>
       <x:c r="I316" s="111" t="n">
-        <x:v>0.218175</x:v>
+        <x:v>0.214194</x:v>
       </x:c>
       <x:c r="J316" s="111" t="n">
-        <x:v>1.0302005270998051</x:v>
+        <x:v>1.0055090245291651</x:v>
       </x:c>
       <x:c r="K316" s="111" t="n">
         <x:v>0</x:v>
@@ -14598,16 +14596,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G320" s="111" t="n">
-        <x:v>4.388346</x:v>
+        <x:v>3.53902</x:v>
       </x:c>
       <x:c r="H320" s="111" t="n">
-        <x:v>0.354986</x:v>
+        <x:v>0.328841</x:v>
       </x:c>
       <x:c r="I320" s="111" t="n">
-        <x:v>0.350346</x:v>
+        <x:v>0.325301</x:v>
       </x:c>
       <x:c r="J320" s="111" t="n">
-        <x:v>1.0132440501675488</x:v>
+        <x:v>1.010882229073996</x:v>
       </x:c>
       <x:c r="K320" s="111" t="n">
         <x:v>0</x:v>
@@ -14674,22 +14672,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G322" s="111" t="n">
-        <x:v>4.454027</x:v>
+        <x:v>5.003135</x:v>
       </x:c>
       <x:c r="H322" s="111" t="n">
-        <x:v>0.348896</x:v>
+        <x:v>0.31938</x:v>
       </x:c>
       <x:c r="I322" s="111" t="n">
-        <x:v>0.336275</x:v>
+        <x:v>0.319801</x:v>
       </x:c>
       <x:c r="J322" s="111" t="n">
-        <x:v>1.0375317820236414</x:v>
+        <x:v>0.9986835563365968</x:v>
       </x:c>
       <x:c r="K322" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L322" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M322" s="7" t="str">
         <x:v>保持官方随机噪声/I/O路径；不把随机源或噪声统计误改成全局FP32累加。已有 HIP ImageNoise 后端；测试入口因缺少 itkAdditiveGaussianNoiseImageFilter.h 未完成可执行复测。</x:v>
@@ -14718,16 +14716,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G323" s="111" t="n">
-        <x:v>7.51495</x:v>
+        <x:v>7.461972</x:v>
       </x:c>
       <x:c r="H323" s="111" t="n">
-        <x:v>0.335246</x:v>
+        <x:v>0.388431</x:v>
       </x:c>
       <x:c r="I323" s="111" t="n">
-        <x:v>0.342676</x:v>
+        <x:v>0.396041</x:v>
       </x:c>
       <x:c r="J323" s="111" t="n">
-        <x:v>0.9783177111907458</x:v>
+        <x:v>0.9807848177335177</x:v>
       </x:c>
       <x:c r="K323" s="111" t="n">
         <x:v>0</x:v>
@@ -14762,16 +14760,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G324" s="111" t="n">
-        <x:v>34.14971</x:v>
+        <x:v>33.158648</x:v>
       </x:c>
       <x:c r="H324" s="111" t="n">
-        <x:v>0.355016</x:v>
+        <x:v>0.338231</x:v>
       </x:c>
       <x:c r="I324" s="111" t="n">
-        <x:v>0.353596</x:v>
+        <x:v>0.335331</x:v>
       </x:c>
       <x:c r="J324" s="111" t="n">
-        <x:v>1.0040158825326078</x:v>
+        <x:v>1.0086481715081517</x:v>
       </x:c>
       <x:c r="K324" s="111" t="n">
         <x:v>0</x:v>
@@ -14806,16 +14804,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G325" s="111" t="n">
-        <x:v>52.282403</x:v>
+        <x:v>52.342304</x:v>
       </x:c>
       <x:c r="H325" s="111" t="n">
-        <x:v>0.282526</x:v>
+        <x:v>0.270921</x:v>
       </x:c>
       <x:c r="I325" s="111" t="n">
-        <x:v>0.328107</x:v>
+        <x:v>0.27507</x:v>
       </x:c>
       <x:c r="J325" s="111" t="n">
-        <x:v>0.8610788553733996</x:v>
+        <x:v>0.9849165666921149</x:v>
       </x:c>
       <x:c r="K325" s="111" t="n">
         <x:v>0</x:v>
@@ -14850,16 +14848,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G326" s="111" t="n">
-        <x:v>53.155521</x:v>
+        <x:v>52.911076</x:v>
       </x:c>
       <x:c r="H326" s="111" t="n">
-        <x:v>0.271065</x:v>
+        <x:v>0.27338</x:v>
       </x:c>
       <x:c r="I326" s="111" t="n">
-        <x:v>0.321277</x:v>
+        <x:v>0.27509</x:v>
       </x:c>
       <x:c r="J326" s="111" t="n">
-        <x:v>0.8437111900322775</x:v>
+        <x:v>0.9937838525573449</x:v>
       </x:c>
       <x:c r="K326" s="111" t="n">
         <x:v>0</x:v>
@@ -14926,16 +14924,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G328" s="111" t="n">
-        <x:v>21.224053</x:v>
+        <x:v>22.790047</x:v>
       </x:c>
       <x:c r="H328" s="111" t="n">
-        <x:v>28.019609</x:v>
+        <x:v>28.013663</x:v>
       </x:c>
       <x:c r="I328" s="111" t="n">
-        <x:v>28.129922</x:v>
+        <x:v>28.084043</x:v>
       </x:c>
       <x:c r="J328" s="111" t="n">
-        <x:v>0.9960784462893284</x:v>
+        <x:v>0.9974939505682996</x:v>
       </x:c>
       <x:c r="K328" s="111" t="n">
         <x:v>0</x:v>
@@ -15002,16 +15000,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G330" s="111" t="n">
-        <x:v>7.720234</x:v>
+        <x:v>9.643449</x:v>
       </x:c>
       <x:c r="H330" s="111" t="n">
-        <x:v>0.475709</x:v>
+        <x:v>0.463382</x:v>
       </x:c>
       <x:c r="I330" s="111" t="n">
-        <x:v>0.478689</x:v>
+        <x:v>0.466661</x:v>
       </x:c>
       <x:c r="J330" s="111" t="n">
-        <x:v>0.9937746637169436</x:v>
+        <x:v>0.9929734861066171</x:v>
       </x:c>
       <x:c r="K330" s="111" t="n">
         <x:v>0</x:v>
@@ -15046,22 +15044,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G331" s="111" t="n">
-        <x:v>16.960369</x:v>
+        <x:v>16.579589</x:v>
       </x:c>
       <x:c r="H331" s="111" t="n">
-        <x:v>17.301165</x:v>
+        <x:v>18.512177</x:v>
       </x:c>
       <x:c r="I331" s="111" t="n">
-        <x:v>18.952208</x:v>
+        <x:v>18.483196</x:v>
       </x:c>
       <x:c r="J331" s="111" t="n">
-        <x:v>0.9128838708397461</x:v>
+        <x:v>1.001567964761073</x:v>
       </x:c>
       <x:c r="K331" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L331" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M331" s="7" t="str">
         <x:v>不能做混合精度：结果往往是一个统计量，或把整张图压成一条/一列，不是整张逐像素灰度图。混合精度要比两张同尺寸亮度图的差，这里对不上。。扫描命中 COMPUTETYPE，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=COMPUTETYPE；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -15090,16 +15088,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G332" s="111" t="n">
-        <x:v>1.798686</x:v>
+        <x:v>1.525159</x:v>
       </x:c>
       <x:c r="H332" s="111" t="n">
-        <x:v>0.167254</x:v>
+        <x:v>0.149903</x:v>
       </x:c>
       <x:c r="I332" s="111" t="n">
-        <x:v>0.207264</x:v>
+        <x:v>0.188564</x:v>
       </x:c>
       <x:c r="J332" s="111" t="n">
-        <x:v>0.8069611702948897</x:v>
+        <x:v>0.7949714685730044</x:v>
       </x:c>
       <x:c r="K332" s="111" t="n">
         <x:v>0</x:v>
@@ -15134,16 +15132,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G333" s="111" t="n">
-        <x:v>0.066412</x:v>
+        <x:v>0.066521</x:v>
       </x:c>
       <x:c r="H333" s="111" t="n">
-        <x:v>0.276615</x:v>
+        <x:v>0.247215</x:v>
       </x:c>
       <x:c r="I333" s="111" t="n">
-        <x:v>0.277065</x:v>
+        <x:v>0.250115</x:v>
       </x:c>
       <x:c r="J333" s="111" t="n">
-        <x:v>0.9983758323859022</x:v>
+        <x:v>0.9884053335465687</x:v>
       </x:c>
       <x:c r="K333" s="111" t="n">
         <x:v>0</x:v>
@@ -15178,16 +15176,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G334" s="111" t="n">
-        <x:v>0.00837</x:v>
+        <x:v>0.00827</x:v>
       </x:c>
       <x:c r="H334" s="111" t="n">
-        <x:v>0.136363</x:v>
+        <x:v>0.13158</x:v>
       </x:c>
       <x:c r="I334" s="111" t="n">
-        <x:v>0.133882</x:v>
+        <x:v>0.13088</x:v>
       </x:c>
       <x:c r="J334" s="111" t="n">
-        <x:v>1.018531243931223</x:v>
+        <x:v>1.0053484107579462</x:v>
       </x:c>
       <x:c r="K334" s="111" t="n">
         <x:v>0</x:v>
@@ -15222,16 +15220,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G335" s="111" t="n">
-        <x:v>0.00708</x:v>
+        <x:v>0.00685</x:v>
       </x:c>
       <x:c r="H335" s="111" t="n">
-        <x:v>0.130853</x:v>
+        <x:v>0.1278</x:v>
       </x:c>
       <x:c r="I335" s="111" t="n">
-        <x:v>0.129493</x:v>
+        <x:v>0.12742</x:v>
       </x:c>
       <x:c r="J335" s="111" t="n">
-        <x:v>1.010502498204536</x:v>
+        <x:v>1.0029822633809449</x:v>
       </x:c>
       <x:c r="K335" s="111" t="n">
         <x:v>0</x:v>
@@ -15266,22 +15264,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G336" s="111" t="n">
-        <x:v>0.074261</x:v>
+        <x:v>0.07047</x:v>
       </x:c>
       <x:c r="H336" s="111" t="n">
-        <x:v>0.291224</x:v>
+        <x:v>0.243011</x:v>
       </x:c>
       <x:c r="I336" s="111" t="n">
-        <x:v>0.292284</x:v>
+        <x:v>0.242691</x:v>
       </x:c>
       <x:c r="J336" s="111" t="n">
-        <x:v>0.9963733902642635</x:v>
+        <x:v>1.0013185491015324</x:v>
       </x:c>
       <x:c r="K336" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L336" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M336" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -15310,16 +15308,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G337" s="111" t="n">
-        <x:v>0.00865</x:v>
+        <x:v>0.00849</x:v>
       </x:c>
       <x:c r="H337" s="111" t="n">
-        <x:v>0.133573</x:v>
+        <x:v>0.13137</x:v>
       </x:c>
       <x:c r="I337" s="111" t="n">
-        <x:v>0.133182</x:v>
+        <x:v>0.13022</x:v>
       </x:c>
       <x:c r="J337" s="111" t="n">
-        <x:v>1.0029358321695123</x:v>
+        <x:v>1.0088312087236981</x:v>
       </x:c>
       <x:c r="K337" s="111" t="n">
         <x:v>0</x:v>
@@ -15354,22 +15352,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G338" s="111" t="n">
-        <x:v>0.00835</x:v>
+        <x:v>0.00838</x:v>
       </x:c>
       <x:c r="H338" s="111" t="n">
-        <x:v>0.170124</x:v>
+        <x:v>0.168611</x:v>
       </x:c>
       <x:c r="I338" s="111" t="n">
-        <x:v>0.168524</x:v>
+        <x:v>0.170501</x:v>
       </x:c>
       <x:c r="J338" s="111" t="n">
-        <x:v>1.009494196672284</x:v>
+        <x:v>0.9889150210262696</x:v>
       </x:c>
       <x:c r="K338" s="111" t="n">
         <x:v>0.1328125</x:v>
       </x:c>
       <x:c r="L338" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M338" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（共享后端；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -15398,22 +15396,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G339" s="111" t="n">
-        <x:v>0.074812</x:v>
+        <x:v>0.0755</x:v>
       </x:c>
       <x:c r="H339" s="111" t="n">
-        <x:v>1.589424</x:v>
+        <x:v>1.459918</x:v>
       </x:c>
       <x:c r="I339" s="111" t="n">
-        <x:v>1.572054</x:v>
+        <x:v>1.464968</x:v>
       </x:c>
       <x:c r="J339" s="111" t="n">
-        <x:v>1.0110492387666072</x:v>
+        <x:v>0.9965528257272513</x:v>
       </x:c>
       <x:c r="K339" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L339" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M339" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -15442,16 +15440,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G340" s="111" t="n">
-        <x:v>0.101182</x:v>
+        <x:v>0.102771</x:v>
       </x:c>
       <x:c r="H340" s="111" t="n">
-        <x:v>0.817072</x:v>
+        <x:v>0.767664</x:v>
       </x:c>
       <x:c r="I340" s="111" t="n">
-        <x:v>0.817472</x:v>
+        <x:v>0.774734</x:v>
       </x:c>
       <x:c r="J340" s="111" t="n">
-        <x:v>0.9995106866045566</x:v>
+        <x:v>0.9908742871746947</x:v>
       </x:c>
       <x:c r="K340" s="111" t="n">
         <x:v>0</x:v>
@@ -15486,16 +15484,16 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G341" s="111" t="n">
-        <x:v>32.672022</x:v>
+        <x:v>32.585986</x:v>
       </x:c>
       <x:c r="H341" s="111" t="n">
-        <x:v>10.980879</x:v>
+        <x:v>8.328825</x:v>
       </x:c>
       <x:c r="I341" s="111" t="n">
-        <x:v>8.823056</x:v>
+        <x:v>8.308974</x:v>
       </x:c>
       <x:c r="J341" s="111" t="n">
-        <x:v>1.2445663951356538</x:v>
+        <x:v>1.0023891036366224</x:v>
       </x:c>
       <x:c r="K341" s="111" t="n">
         <x:v>0</x:v>
@@ -15530,16 +15528,16 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G342" s="111" t="n">
-        <x:v>5.103152</x:v>
+        <x:v>5.136555</x:v>
       </x:c>
       <x:c r="H342" s="111" t="n">
-        <x:v>0.577482</x:v>
+        <x:v>0.460611</x:v>
       </x:c>
       <x:c r="I342" s="111" t="n">
-        <x:v>0.4644</x:v>
+        <x:v>0.457281</x:v>
       </x:c>
       <x:c r="J342" s="111" t="n">
-        <x:v>1.2435012919896642</x:v>
+        <x:v>1.0072821744179181</x:v>
       </x:c>
       <x:c r="K342" s="111" t="n">
         <x:v>0</x:v>
@@ -15574,16 +15572,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G343" s="111" t="n">
-        <x:v>2.090462</x:v>
+        <x:v>1.930177</x:v>
       </x:c>
       <x:c r="H343" s="111" t="n">
-        <x:v>20.935828</x:v>
+        <x:v>19.71159</x:v>
       </x:c>
       <x:c r="I343" s="111" t="n">
-        <x:v>20.754045</x:v>
+        <x:v>19.67326</x:v>
       </x:c>
       <x:c r="J343" s="111" t="n">
-        <x:v>1.0087589190444561</x:v>
+        <x:v>1.0019483298650047</x:v>
       </x:c>
       <x:c r="K343" s="111" t="n">
         <x:v>0</x:v>
@@ -15618,22 +15616,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G344" s="111" t="n">
-        <x:v>2.332616</x:v>
+        <x:v>2.405396</x:v>
       </x:c>
       <x:c r="H344" s="111" t="n">
-        <x:v>663.899832</x:v>
+        <x:v>588.405811</x:v>
       </x:c>
       <x:c r="I344" s="111" t="n">
-        <x:v>593.907204</x:v>
+        <x:v>591.411169</x:v>
       </x:c>
       <x:c r="J344" s="111" t="n">
-        <x:v>1.1178511180342576</x:v>
+        <x:v>0.9949183272864432</x:v>
       </x:c>
       <x:c r="K344" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L344" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M344" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -15662,22 +15660,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G345" s="111" t="n">
-        <x:v>12.451789</x:v>
+        <x:v>12.401289</x:v>
       </x:c>
       <x:c r="H345" s="111" t="n">
-        <x:v>1155.910442</x:v>
+        <x:v>1115.309275</x:v>
       </x:c>
       <x:c r="I345" s="111" t="n">
-        <x:v>1126.320062</x:v>
+        <x:v>1122.660077</x:v>
       </x:c>
       <x:c r="J345" s="111" t="n">
-        <x:v>1.0262717330520212</x:v>
+        <x:v>0.9934523350829015</x:v>
       </x:c>
       <x:c r="K345" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L345" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M345" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -15750,16 +15748,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G347" s="111" t="n">
-        <x:v>5.00901</x:v>
+        <x:v>4.770184</x:v>
       </x:c>
       <x:c r="H347" s="111" t="n">
-        <x:v>1.770155</x:v>
+        <x:v>1.378284</x:v>
       </x:c>
       <x:c r="I347" s="111" t="n">
-        <x:v>1.419779</x:v>
+        <x:v>1.377644</x:v>
       </x:c>
       <x:c r="J347" s="111" t="n">
-        <x:v>1.2467820696037906</x:v>
+        <x:v>1.0004645612364298</x:v>
       </x:c>
       <x:c r="K347" s="111" t="n">
         <x:v>0</x:v>
@@ -15794,22 +15792,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G348" s="111" t="n">
-        <x:v>31.377067</x:v>
+        <x:v>31.705383</x:v>
       </x:c>
       <x:c r="H348" s="111" t="n">
-        <x:v>0.456049</x:v>
+        <x:v>0.452471</x:v>
       </x:c>
       <x:c r="I348" s="111" t="n">
-        <x:v>0.452499</x:v>
+        <x:v>0.457711</x:v>
       </x:c>
       <x:c r="J348" s="111" t="n">
-        <x:v>1.0078453212051297</x:v>
+        <x:v>0.9885517280554761</x:v>
       </x:c>
       <x:c r="K348" s="111" t="n">
         <x:v>0.0498716614641</x:v>
       </x:c>
       <x:c r="L348" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M348" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（共享后端；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -15838,16 +15836,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G349" s="111" t="n">
-        <x:v>0.184174</x:v>
+        <x:v>0.131822</x:v>
       </x:c>
       <x:c r="H349" s="111" t="n">
-        <x:v>0.444699</x:v>
+        <x:v>0.419828</x:v>
       </x:c>
       <x:c r="I349" s="111" t="n">
-        <x:v>0.443479</x:v>
+        <x:v>0.418198</x:v>
       </x:c>
       <x:c r="J349" s="111" t="n">
-        <x:v>1.002750975807197</x:v>
+        <x:v>1.0038976752638702</x:v>
       </x:c>
       <x:c r="K349" s="111" t="n">
         <x:v>0</x:v>
@@ -15882,22 +15880,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G350" s="111" t="n">
-        <x:v>4.859127</x:v>
+        <x:v>5.187095</x:v>
       </x:c>
       <x:c r="H350" s="111" t="n">
-        <x:v>1720.299961</x:v>
+        <x:v>1630.46127</x:v>
       </x:c>
       <x:c r="I350" s="111" t="n">
-        <x:v>1632.558709</x:v>
+        <x:v>1640.313849</x:v>
       </x:c>
       <x:c r="J350" s="111" t="n">
-        <x:v>1.0537446227913878</x:v>
+        <x:v>0.9939934793539624</x:v>
       </x:c>
       <x:c r="K350" s="111" t="n">
-        <x:v>0.0431459414734</x:v>
+        <x:v>0.0409690956316</x:v>
       </x:c>
       <x:c r="L350" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M350" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（共享后端；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -15926,19 +15924,19 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G351" s="111" t="n">
-        <x:v>3.781775</x:v>
+        <x:v>3.774641</x:v>
       </x:c>
       <x:c r="H351" s="111" t="n">
-        <x:v>1768.657766</x:v>
+        <x:v>1630.42774</x:v>
       </x:c>
       <x:c r="I351" s="111" t="n">
-        <x:v>1631.776603</x:v>
+        <x:v>1628.037002</x:v>
       </x:c>
       <x:c r="J351" s="111" t="n">
-        <x:v>1.083884744240324</x:v>
+        <x:v>1.0014684789086876</x:v>
       </x:c>
       <x:c r="K351" s="111" t="n">
-        <x:v>0.0305087877965</x:v>
+        <x:v>0.0424327362938</x:v>
       </x:c>
       <x:c r="L351" s="7" t="str">
         <x:v>是</x:v>
@@ -15970,19 +15968,19 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G352" s="111" t="n">
-        <x:v>15.06389</x:v>
+        <x:v>13.165309</x:v>
       </x:c>
       <x:c r="H352" s="111" t="n">
-        <x:v>2306.303209</x:v>
+        <x:v>2274.494689</x:v>
       </x:c>
       <x:c r="I352" s="111" t="n">
-        <x:v>2294.011127</x:v>
+        <x:v>2274.353839</x:v>
       </x:c>
       <x:c r="J352" s="111" t="n">
-        <x:v>1.005358335822928</x:v>
+        <x:v>1.0000619296776012</x:v>
       </x:c>
       <x:c r="K352" s="111" t="n">
-        <x:v>0.04296875</x:v>
+        <x:v>0.0390625</x:v>
       </x:c>
       <x:c r="L352" s="7" t="str">
         <x:v>是</x:v>
@@ -16014,22 +16012,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G353" s="111" t="n">
-        <x:v>14.516189</x:v>
+        <x:v>13.691491</x:v>
       </x:c>
       <x:c r="H353" s="111" t="n">
-        <x:v>2338.614784</x:v>
+        <x:v>2258.093261</x:v>
       </x:c>
       <x:c r="I353" s="111" t="n">
-        <x:v>2283.309482</x:v>
+        <x:v>2272.865934</x:v>
       </x:c>
       <x:c r="J353" s="111" t="n">
-        <x:v>1.02422155316044</x:v>
+        <x:v>0.9935004204255895</x:v>
       </x:c>
       <x:c r="K353" s="111" t="n">
-        <x:v>0.0445381025429</x:v>
+        <x:v>0.0336028330744</x:v>
       </x:c>
       <x:c r="L353" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M353" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（共享后端；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16058,22 +16056,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G354" s="111" t="n">
-        <x:v>0.01028</x:v>
+        <x:v>0.0102</x:v>
       </x:c>
       <x:c r="H354" s="111" t="n">
-        <x:v>0.276724</x:v>
+        <x:v>0.210151</x:v>
       </x:c>
       <x:c r="I354" s="111" t="n">
-        <x:v>0.261734</x:v>
+        <x:v>0.210472</x:v>
       </x:c>
       <x:c r="J354" s="111" t="n">
-        <x:v>1.05727188672469</x:v>
+        <x:v>0.9984748565129804</x:v>
       </x:c>
       <x:c r="K354" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L354" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M354" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16102,22 +16100,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G355" s="111" t="n">
-        <x:v>0.090612</x:v>
+        <x:v>0.091352</x:v>
       </x:c>
       <x:c r="H355" s="111" t="n">
-        <x:v>0.675254</x:v>
+        <x:v>0.646952</x:v>
       </x:c>
       <x:c r="I355" s="111" t="n">
-        <x:v>0.668114</x:v>
+        <x:v>0.653883</x:v>
       </x:c>
       <x:c r="J355" s="111" t="n">
-        <x:v>1.010686798959459</x:v>
+        <x:v>0.9894002443862281</x:v>
       </x:c>
       <x:c r="K355" s="111" t="n">
-        <x:v>0.285714285714</x:v>
+        <x:v>0.457142857143</x:v>
       </x:c>
       <x:c r="L355" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M355" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16146,22 +16144,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G356" s="111" t="n">
-        <x:v>0.026511</x:v>
+        <x:v>0.02653</x:v>
       </x:c>
       <x:c r="H356" s="111" t="n">
-        <x:v>0.205614</x:v>
+        <x:v>0.188101</x:v>
       </x:c>
       <x:c r="I356" s="111" t="n">
-        <x:v>0.201744</x:v>
+        <x:v>0.228991</x:v>
       </x:c>
       <x:c r="J356" s="111" t="n">
-        <x:v>1.01918272662384</x:v>
+        <x:v>0.8214340301583904</x:v>
       </x:c>
       <x:c r="K356" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L356" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M356" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16190,22 +16188,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G357" s="111" t="n">
-        <x:v>0.005341</x:v>
+        <x:v>0.0053</x:v>
       </x:c>
       <x:c r="H357" s="111" t="n">
-        <x:v>0.816412</x:v>
+        <x:v>0.760974</x:v>
       </x:c>
       <x:c r="I357" s="111" t="n">
-        <x:v>0.806052</x:v>
+        <x:v>0.762773</x:v>
       </x:c>
       <x:c r="J357" s="111" t="n">
-        <x:v>1.0128527688039979</x:v>
+        <x:v>0.9976415001579763</x:v>
       </x:c>
       <x:c r="K357" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L357" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M357" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16266,22 +16264,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G359" s="111" t="n">
-        <x:v>1.953218</x:v>
+        <x:v>1.594531</x:v>
       </x:c>
       <x:c r="H359" s="111" t="n">
-        <x:v>3.50229</x:v>
+        <x:v>3.486829</x:v>
       </x:c>
       <x:c r="I359" s="111" t="n">
-        <x:v>3.484739</x:v>
+        <x:v>3.51052</x:v>
       </x:c>
       <x:c r="J359" s="111" t="n">
-        <x:v>1.0050365321477448</x:v>
+        <x:v>0.9932514271389994</x:v>
       </x:c>
       <x:c r="K359" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L359" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M359" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16310,22 +16308,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G360" s="111" t="n">
-        <x:v>1.748095</x:v>
+        <x:v>2.259405</x:v>
       </x:c>
       <x:c r="H360" s="111" t="n">
-        <x:v>557.969238</x:v>
+        <x:v>514.339474</x:v>
       </x:c>
       <x:c r="I360" s="111" t="n">
-        <x:v>515.380047</x:v>
+        <x:v>516.975097</x:v>
       </x:c>
       <x:c r="J360" s="111" t="n">
-        <x:v>1.0826364762235354</x:v>
+        <x:v>0.9949018376024407</x:v>
       </x:c>
       <x:c r="K360" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L360" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M360" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16354,16 +16352,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G361" s="111" t="n">
-        <x:v>10.624032</x:v>
+        <x:v>9.890056</x:v>
       </x:c>
       <x:c r="H361" s="111" t="n">
-        <x:v>1137.171331</x:v>
+        <x:v>1054.134264</x:v>
       </x:c>
       <x:c r="I361" s="111" t="n">
-        <x:v>1055.488478</x:v>
+        <x:v>1049.92569</x:v>
       </x:c>
       <x:c r="J361" s="111" t="n">
-        <x:v>1.077388673303926</x:v>
+        <x:v>1.004008449397976</x:v>
       </x:c>
       <x:c r="K361" s="111" t="n">
         <x:v>0</x:v>
@@ -16474,16 +16472,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G364" s="111" t="n">
-        <x:v>0.325704</x:v>
+        <x:v>0.329491</x:v>
       </x:c>
       <x:c r="H364" s="111" t="n">
-        <x:v>0.603457</x:v>
+        <x:v>0.595122</x:v>
       </x:c>
       <x:c r="I364" s="111" t="n">
-        <x:v>0.655639</x:v>
+        <x:v>0.597262</x:v>
       </x:c>
       <x:c r="J364" s="111" t="n">
-        <x:v>0.9204104697859646</x:v>
+        <x:v>0.9964169828316553</x:v>
       </x:c>
       <x:c r="K364" s="111" t="n">
         <x:v>0</x:v>
@@ -16606,22 +16604,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G367" s="111" t="n">
-        <x:v>0.00895</x:v>
+        <x:v>0.00906</x:v>
       </x:c>
       <x:c r="H367" s="111" t="n">
-        <x:v>0.232483</x:v>
+        <x:v>0.169771</x:v>
       </x:c>
       <x:c r="I367" s="111" t="n">
-        <x:v>0.217803</x:v>
+        <x:v>0.169771</x:v>
       </x:c>
       <x:c r="J367" s="111" t="n">
-        <x:v>1.067400357203528</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K367" s="111" t="n">
         <x:v>16126.4279572</x:v>
       </x:c>
       <x:c r="L367" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M367" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（共享后端；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16650,16 +16648,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G368" s="111" t="n">
-        <x:v>3.0439</x:v>
+        <x:v>3.031259</x:v>
       </x:c>
       <x:c r="H368" s="111" t="n">
-        <x:v>4.330597</x:v>
+        <x:v>4.320163</x:v>
       </x:c>
       <x:c r="I368" s="111" t="n">
-        <x:v>4.404768</x:v>
+        <x:v>4.329752</x:v>
       </x:c>
       <x:c r="J368" s="111" t="n">
-        <x:v>0.9831612016796345</x:v>
+        <x:v>0.9977853235012074</x:v>
       </x:c>
       <x:c r="K368" s="111" t="n">
         <x:v>0</x:v>
@@ -16694,16 +16692,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G369" s="111" t="n">
-        <x:v>3.037281</x:v>
+        <x:v>3.096829</x:v>
       </x:c>
       <x:c r="H369" s="111" t="n">
-        <x:v>4.340397</x:v>
+        <x:v>4.305873</x:v>
       </x:c>
       <x:c r="I369" s="111" t="n">
-        <x:v>4.433598</x:v>
+        <x:v>4.315533</x:v>
       </x:c>
       <x:c r="J369" s="111" t="n">
-        <x:v>0.9789784730144683</x:v>
+        <x:v>0.9977615742945309</x:v>
       </x:c>
       <x:c r="K369" s="111" t="n">
         <x:v>0</x:v>
@@ -16738,22 +16736,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G370" s="111" t="n">
-        <x:v>12.476879</x:v>
+        <x:v>15.973267</x:v>
       </x:c>
       <x:c r="H370" s="111" t="n">
-        <x:v>2233.018566</x:v>
+        <x:v>2202.538867</x:v>
       </x:c>
       <x:c r="I370" s="111" t="n">
-        <x:v>2309.564107</x:v>
+        <x:v>2200.594181</x:v>
       </x:c>
       <x:c r="J370" s="111" t="n">
-        <x:v>0.9668571481657513</x:v>
+        <x:v>1.000883709507546</x:v>
       </x:c>
       <x:c r="K370" s="111" t="n">
-        <x:v>0.0703125</x:v>
+        <x:v>0.109931619371</x:v>
       </x:c>
       <x:c r="L370" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M370" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（共享后端；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16782,19 +16780,19 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G371" s="111" t="n">
-        <x:v>11.438089</x:v>
+        <x:v>11.446544</x:v>
       </x:c>
       <x:c r="H371" s="111" t="n">
-        <x:v>2217.114559</x:v>
+        <x:v>2200.561811</x:v>
       </x:c>
       <x:c r="I371" s="111" t="n">
-        <x:v>2319.21672</x:v>
+        <x:v>2202.132886</x:v>
       </x:c>
       <x:c r="J371" s="111" t="n">
-        <x:v>0.9559755842912344</x:v>
+        <x:v>0.9992865666690743</x:v>
       </x:c>
       <x:c r="K371" s="111" t="n">
-        <x:v>0.078902382331</x:v>
+        <x:v>0.0819381912633</x:v>
       </x:c>
       <x:c r="L371" s="7" t="str">
         <x:v>否</x:v>
@@ -16826,16 +16824,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G372" s="111" t="n">
-        <x:v>0.116112</x:v>
+        <x:v>0.114741</x:v>
       </x:c>
       <x:c r="H372" s="111" t="n">
-        <x:v>1.876118</x:v>
+        <x:v>1.754919</x:v>
       </x:c>
       <x:c r="I372" s="111" t="n">
-        <x:v>1.856288</x:v>
+        <x:v>1.754759</x:v>
       </x:c>
       <x:c r="J372" s="111" t="n">
-        <x:v>1.010682609595063</x:v>
+        <x:v>1.0000911806122663</x:v>
       </x:c>
       <x:c r="K372" s="111" t="n">
         <x:v>0</x:v>
@@ -16870,22 +16868,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G373" s="111" t="n">
-        <x:v>0.00546</x:v>
+        <x:v>0.00503</x:v>
       </x:c>
       <x:c r="H373" s="111" t="n">
-        <x:v>0.236833</x:v>
+        <x:v>0.173041</x:v>
       </x:c>
       <x:c r="I373" s="111" t="n">
-        <x:v>0.224434</x:v>
+        <x:v>0.174281</x:v>
       </x:c>
       <x:c r="J373" s="111" t="n">
-        <x:v>1.0552456401436503</x:v>
+        <x:v>0.9928850534481671</x:v>
       </x:c>
       <x:c r="K373" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L373" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M373" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16946,22 +16944,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G375" s="111" t="n">
-        <x:v>0.00544</x:v>
+        <x:v>0.00534</x:v>
       </x:c>
       <x:c r="H375" s="111" t="n">
-        <x:v>0.812572</x:v>
+        <x:v>0.762904</x:v>
       </x:c>
       <x:c r="I375" s="111" t="n">
-        <x:v>0.801812</x:v>
+        <x:v>0.769084</x:v>
       </x:c>
       <x:c r="J375" s="111" t="n">
-        <x:v>1.013419604595591</x:v>
+        <x:v>0.9919644668202694</x:v>
       </x:c>
       <x:c r="K375" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L375" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M375" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -16990,22 +16988,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G376" s="111" t="n">
-        <x:v>0.00668</x:v>
+        <x:v>0.00665</x:v>
       </x:c>
       <x:c r="H376" s="111" t="n">
-        <x:v>0.673713</x:v>
+        <x:v>0.648122</x:v>
       </x:c>
       <x:c r="I376" s="111" t="n">
-        <x:v>0.671363</x:v>
+        <x:v>0.658772</x:v>
       </x:c>
       <x:c r="J376" s="111" t="n">
-        <x:v>1.0035003418418946</x:v>
+        <x:v>0.9838335569817781</x:v>
       </x:c>
       <x:c r="K376" s="111" t="n">
-        <x:v>0.0390625</x:v>
+        <x:v>0.0737029775942</x:v>
       </x:c>
       <x:c r="L376" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M376" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17034,22 +17032,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G377" s="111" t="n">
-        <x:v>0.00859</x:v>
+        <x:v>0.00831</x:v>
       </x:c>
       <x:c r="H377" s="111" t="n">
-        <x:v>0.182653</x:v>
+        <x:v>0.132491</x:v>
       </x:c>
       <x:c r="I377" s="111" t="n">
-        <x:v>0.175882</x:v>
+        <x:v>0.13336</x:v>
       </x:c>
       <x:c r="J377" s="111" t="n">
-        <x:v>1.0384974016670268</x:v>
+        <x:v>0.993483803239352</x:v>
       </x:c>
       <x:c r="K377" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L377" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M377" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17078,22 +17076,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G378" s="111" t="n">
-        <x:v>0.00838</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
       <x:c r="H378" s="111" t="n">
-        <x:v>0.190794</x:v>
+        <x:v>0.169553</x:v>
       </x:c>
       <x:c r="I378" s="111" t="n">
-        <x:v>0.197434</x:v>
+        <x:v>0.169153</x:v>
       </x:c>
       <x:c r="J378" s="111" t="n">
-        <x:v>0.9663685079570894</x:v>
+        <x:v>1.0023647230613706</x:v>
       </x:c>
       <x:c r="K378" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L378" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M378" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17154,16 +17152,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G380" s="111" t="n">
-        <x:v>0.00708</x:v>
+        <x:v>0.00709</x:v>
       </x:c>
       <x:c r="H380" s="111" t="n">
-        <x:v>0.192753</x:v>
+        <x:v>0.166423</x:v>
       </x:c>
       <x:c r="I380" s="111" t="n">
-        <x:v>0.196994</x:v>
+        <x:v>0.167663</x:v>
       </x:c>
       <x:c r="J380" s="111" t="n">
-        <x:v>0.9784714255256506</x:v>
+        <x:v>0.992604212020541</x:v>
       </x:c>
       <x:c r="K380" s="111" t="n">
         <x:v>0</x:v>
@@ -17198,22 +17196,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G381" s="111" t="n">
-        <x:v>0.075402</x:v>
+        <x:v>0.074461</x:v>
       </x:c>
       <x:c r="H381" s="111" t="n">
-        <x:v>0.295866</x:v>
+        <x:v>0.24866</x:v>
       </x:c>
       <x:c r="I381" s="111" t="n">
-        <x:v>0.247945</x:v>
+        <x:v>0.251321</x:v>
       </x:c>
       <x:c r="J381" s="111" t="n">
-        <x:v>1.1932727016072113</x:v>
+        <x:v>0.989411947270622</x:v>
       </x:c>
       <x:c r="K381" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L381" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M381" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17242,22 +17240,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G382" s="111" t="n">
-        <x:v>3.46343</x:v>
+        <x:v>3.396655</x:v>
       </x:c>
       <x:c r="H382" s="111" t="n">
-        <x:v>4.360467</x:v>
+        <x:v>4.305243</x:v>
       </x:c>
       <x:c r="I382" s="111" t="n">
-        <x:v>4.359138</x:v>
+        <x:v>4.305573</x:v>
       </x:c>
       <x:c r="J382" s="111" t="n">
-        <x:v>1.0003048767898608</x:v>
+        <x:v>0.9999233551492449</x:v>
       </x:c>
       <x:c r="K382" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L382" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M382" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17286,22 +17284,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G383" s="111" t="n">
-        <x:v>0.00853</x:v>
+        <x:v>0.008531</x:v>
       </x:c>
       <x:c r="H383" s="111" t="n">
-        <x:v>0.189114</x:v>
+        <x:v>0.169003</x:v>
       </x:c>
       <x:c r="I383" s="111" t="n">
-        <x:v>0.197184</x:v>
+        <x:v>0.167493</x:v>
       </x:c>
       <x:c r="J383" s="111" t="n">
-        <x:v>0.9590737585199611</x:v>
+        <x:v>1.0090153021320294</x:v>
       </x:c>
       <x:c r="K383" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L383" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M383" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17330,22 +17328,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G384" s="111" t="n">
-        <x:v>0.071041</x:v>
+        <x:v>0.070051</x:v>
       </x:c>
       <x:c r="H384" s="111" t="n">
-        <x:v>1.593514</x:v>
+        <x:v>1.467837</x:v>
       </x:c>
       <x:c r="I384" s="111" t="n">
-        <x:v>1.557443</x:v>
+        <x:v>1.471488</x:v>
       </x:c>
       <x:c r="J384" s="111" t="n">
-        <x:v>1.0231603981654547</x:v>
+        <x:v>0.9975188380741128</x:v>
       </x:c>
       <x:c r="K384" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L384" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M384" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17374,22 +17372,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G385" s="111" t="n">
-        <x:v>0.0075</x:v>
+        <x:v>0.0074</x:v>
       </x:c>
       <x:c r="H385" s="111" t="n">
-        <x:v>0.172502</x:v>
+        <x:v>0.122571</x:v>
       </x:c>
       <x:c r="I385" s="111" t="n">
-        <x:v>0.168062</x:v>
+        <x:v>0.12479</x:v>
       </x:c>
       <x:c r="J385" s="111" t="n">
-        <x:v>1.0264188216253525</x:v>
+        <x:v>0.9822181264524401</x:v>
       </x:c>
       <x:c r="K385" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L385" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M385" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17418,16 +17416,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G386" s="111" t="n">
-        <x:v>0.008711</x:v>
+        <x:v>0.008441</x:v>
       </x:c>
       <x:c r="H386" s="111" t="n">
-        <x:v>0.146883</x:v>
+        <x:v>0.136612</x:v>
       </x:c>
       <x:c r="I386" s="111" t="n">
-        <x:v>0.143713</x:v>
+        <x:v>0.136143</x:v>
       </x:c>
       <x:c r="J386" s="111" t="n">
-        <x:v>1.0220578514121896</x:v>
+        <x:v>1.0034449071931721</x:v>
       </x:c>
       <x:c r="K386" s="111" t="n">
         <x:v>0</x:v>
@@ -17494,16 +17492,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G388" s="111" t="n">
-        <x:v>0.00628</x:v>
+        <x:v>0.00626</x:v>
       </x:c>
       <x:c r="H388" s="111" t="n">
-        <x:v>0.140333</x:v>
+        <x:v>0.130703</x:v>
       </x:c>
       <x:c r="I388" s="111" t="n">
-        <x:v>0.138013</x:v>
+        <x:v>0.128913</x:v>
       </x:c>
       <x:c r="J388" s="111" t="n">
-        <x:v>1.0168100106511706</x:v>
+        <x:v>1.0138853335195055</x:v>
       </x:c>
       <x:c r="K388" s="111" t="n">
         <x:v>0</x:v>
@@ -17538,22 +17536,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G389" s="111" t="n">
-        <x:v>0.095242</x:v>
+        <x:v>0.07385</x:v>
       </x:c>
       <x:c r="H389" s="111" t="n">
-        <x:v>0.289436</x:v>
+        <x:v>0.246781</x:v>
       </x:c>
       <x:c r="I389" s="111" t="n">
-        <x:v>0.248495</x:v>
+        <x:v>0.249091</x:v>
       </x:c>
       <x:c r="J389" s="111" t="n">
-        <x:v>1.1647558300971852</x:v>
+        <x:v>0.9907262807568318</x:v>
       </x:c>
       <x:c r="K389" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L389" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M389" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17582,19 +17580,19 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G390" s="111" t="n">
-        <x:v>13.900998</x:v>
+        <x:v>11.386389</x:v>
       </x:c>
       <x:c r="H390" s="111" t="n">
-        <x:v>2260.597741</x:v>
+        <x:v>2235.130662</x:v>
       </x:c>
       <x:c r="I390" s="111" t="n">
-        <x:v>2218.57412</x:v>
+        <x:v>2220.221135</x:v>
       </x:c>
       <x:c r="J390" s="111" t="n">
-        <x:v>1.018941725057173</x:v>
+        <x:v>1.00671533423629</x:v>
       </x:c>
       <x:c r="K390" s="111" t="n">
-        <x:v>0.0302576823922</x:v>
+        <x:v>0.0862918829468</x:v>
       </x:c>
       <x:c r="L390" s="7" t="str">
         <x:v>是</x:v>
@@ -17626,22 +17624,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G391" s="111" t="n">
-        <x:v>0.00857</x:v>
+        <x:v>0.00901</x:v>
       </x:c>
       <x:c r="H391" s="111" t="n">
-        <x:v>0.146722</x:v>
+        <x:v>0.134483</x:v>
       </x:c>
       <x:c r="I391" s="111" t="n">
-        <x:v>0.141273</x:v>
+        <x:v>0.135132</x:v>
       </x:c>
       <x:c r="J391" s="111" t="n">
-        <x:v>1.0385707106099535</x:v>
+        <x:v>0.9951972885770949</x:v>
       </x:c>
       <x:c r="K391" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L391" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M391" s="7" t="str">
         <x:v>不能做混合精度：输出是编号表（这块是 1、那块是 2），不是亮度图。混合精度要比的是同一套亮度用单精度和双精度各算一遍；门牌号不必算到小数，所以不填。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -17670,16 +17668,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G392" s="111" t="n">
-        <x:v>0.070091</x:v>
+        <x:v>0.069541</x:v>
       </x:c>
       <x:c r="H392" s="111" t="n">
-        <x:v>1.585654</x:v>
+        <x:v>1.461478</x:v>
       </x:c>
       <x:c r="I392" s="111" t="n">
-        <x:v>1.558593</x:v>
+        <x:v>1.460368</x:v>
       </x:c>
       <x:c r="J392" s="111" t="n">
-        <x:v>1.0173624544701536</x:v>
+        <x:v>1.000760082390192</x:v>
       </x:c>
       <x:c r="K392" s="111" t="n">
         <x:v>0</x:v>
@@ -18198,22 +18196,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G404" s="111" t="n">
-        <x:v>1273.178654</x:v>
+        <x:v>1248.833754</x:v>
       </x:c>
       <x:c r="H404" s="111" t="n">
-        <x:v>42.072799</x:v>
+        <x:v>36.999759</x:v>
       </x:c>
       <x:c r="I404" s="111" t="n">
-        <x:v>53.789731</x:v>
+        <x:v>36.953019</x:v>
       </x:c>
       <x:c r="J404" s="111" t="n">
-        <x:v>0.7821715821557093</x:v>
+        <x:v>1.0012648492941807</x:v>
       </x:c>
       <x:c r="K404" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L404" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M404" s="7" t="str">
         <x:v>混合精度已进入实现路径：共享 ReconstructionByErosion -&gt; GrayscaleGeodesicErode 路径；内部迭代比较按 COMPUTETYPE 计算，I/O 像素类型保持不变，边界参数保持原像素类型。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -18242,22 +18240,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G405" s="111" t="n">
-        <x:v>4473.441874</x:v>
+        <x:v>4457.753509</x:v>
       </x:c>
       <x:c r="H405" s="111" t="n">
-        <x:v>123.231688</x:v>
+        <x:v>106.482824</x:v>
       </x:c>
       <x:c r="I405" s="111" t="n">
-        <x:v>159.751875</x:v>
+        <x:v>106.370644</x:v>
       </x:c>
       <x:c r="J405" s="111" t="n">
-        <x:v>0.771394313838257</x:v>
+        <x:v>1.0010546142787289</x:v>
       </x:c>
       <x:c r="K405" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L405" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M405" s="7" t="str">
         <x:v>混合精度已进入实现路径：共享 ReconstructionByDilation -&gt; GrayscaleGeodesicDilate 路径；内部迭代比较按 COMPUTETYPE 计算，I/O 像素类型保持不变，边界参数保持原像素类型。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -18374,22 +18372,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G408" s="111" t="n">
-        <x:v>4270.309133</x:v>
+        <x:v>4186.020657</x:v>
       </x:c>
       <x:c r="H408" s="111" t="n">
-        <x:v>40.088773</x:v>
+        <x:v>35.207653</x:v>
       </x:c>
       <x:c r="I408" s="111" t="n">
-        <x:v>50.996236</x:v>
+        <x:v>35.192284</x:v>
       </x:c>
       <x:c r="J408" s="111" t="n">
-        <x:v>0.7861123907262489</x:v>
+        <x:v>1.0004367150481055</x:v>
       </x:c>
       <x:c r="K408" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L408" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M408" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -18594,22 +18592,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G413" s="111" t="n">
-        <x:v>4086.437864</x:v>
+        <x:v>4065.155021</x:v>
       </x:c>
       <x:c r="H413" s="111" t="n">
-        <x:v>39.205662</x:v>
+        <x:v>34.360072</x:v>
       </x:c>
       <x:c r="I413" s="111" t="n">
-        <x:v>49.530166</x:v>
+        <x:v>34.347881</x:v>
       </x:c>
       <x:c r="J413" s="111" t="n">
-        <x:v>0.7915511932667457</x:v>
+        <x:v>1.0003549272806669</x:v>
       </x:c>
       <x:c r="K413" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L413" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M413" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -19342,22 +19340,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G430" s="111" t="n">
-        <x:v>478.036707</x:v>
+        <x:v>475.517322</x:v>
       </x:c>
       <x:c r="H430" s="111" t="n">
-        <x:v>2.205208</x:v>
+        <x:v>2.041966</x:v>
       </x:c>
       <x:c r="I430" s="111" t="n">
-        <x:v>2.205469</x:v>
+        <x:v>2.039426</x:v>
       </x:c>
       <x:c r="J430" s="111" t="n">
-        <x:v>0.9998816578242541</x:v>
+        <x:v>1.0012454484742275</x:v>
       </x:c>
       <x:c r="K430" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L430" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M430" s="7" t="str">
         <x:v>混合精度已进入实现路径：共享 GrayscaleGeodesicDilateImageFilter 的多步迭代路径；内部计算按 COMPUTETYPE 选择，I/O 和 marker/mask 像素类型保持不变。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -19386,16 +19384,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G431" s="111" t="n">
-        <x:v>463.483198</x:v>
+        <x:v>462.193534</x:v>
       </x:c>
       <x:c r="H431" s="111" t="n">
-        <x:v>2.005716</x:v>
+        <x:v>1.873756</x:v>
       </x:c>
       <x:c r="I431" s="111" t="n">
-        <x:v>2.001426</x:v>
+        <x:v>1.858955</x:v>
       </x:c>
       <x:c r="J431" s="111" t="n">
-        <x:v>1.0021434717046747</x:v>
+        <x:v>1.0079620001560017</x:v>
       </x:c>
       <x:c r="K431" s="111" t="n">
         <x:v>0</x:v>
@@ -19582,22 +19580,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G436" s="111" t="n">
-        <x:v>767.772869</x:v>
+        <x:v>778.423636</x:v>
       </x:c>
       <x:c r="H436" s="111" t="n">
-        <x:v>0.853021</x:v>
+        <x:v>0.784962</x:v>
       </x:c>
       <x:c r="I436" s="111" t="n">
-        <x:v>0.958</x:v>
+        <x:v>0.774052</x:v>
       </x:c>
       <x:c r="J436" s="111" t="n">
-        <x:v>1</x:v>
+        <x:v>1.0140946603070595</x:v>
       </x:c>
       <x:c r="K436" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L436" s="7" t="str">
-        <x:v>不适用</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M436" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -19626,22 +19624,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G437" s="111" t="n">
-        <x:v>715.168801</x:v>
+        <x:v>713.467464</x:v>
       </x:c>
       <x:c r="H437" s="111" t="n">
-        <x:v>1.053724</x:v>
+        <x:v>0.779182</x:v>
       </x:c>
       <x:c r="I437" s="111" t="n">
-        <x:v>0.953582</x:v>
+        <x:v>0.788533</x:v>
       </x:c>
       <x:c r="J437" s="111" t="n">
-        <x:v>1</x:v>
+        <x:v>0.988141269927828</x:v>
       </x:c>
       <x:c r="K437" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L437" s="7" t="str">
-        <x:v>不适用</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M437" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -19846,22 +19844,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G442" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>8.495174</x:v>
       </x:c>
       <x:c r="H442" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>540.419196</x:v>
       </x:c>
       <x:c r="I442" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>536.240455</x:v>
       </x:c>
       <x:c r="J442" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0077926627150875</x:v>
       </x:c>
       <x:c r="K442" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L442" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M442" s="7" t="str">
         <x:v>混合精度已进入实现路径：链码到Fourier路径的系数计算纳入受控精度策略；三角函数和系数累加保持官方FP64语义，只有在明确启用且系数类型为float时才允许受控降精度，路径对象和输出系数类型不变，不使用应用层Cast链。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -19890,16 +19888,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G443" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>325.186389</x:v>
       </x:c>
       <x:c r="H443" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>55.417033</x:v>
       </x:c>
       <x:c r="I443" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>55.515324</x:v>
       </x:c>
       <x:c r="J443" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>0.9982294798459611</x:v>
       </x:c>
       <x:c r="K443" s="111" t="n">
         <x:v>0</x:v>
@@ -19934,22 +19932,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G444" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>16.774614</x:v>
       </x:c>
       <x:c r="H444" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>541.19684</x:v>
       </x:c>
       <x:c r="I444" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>537.04117</x:v>
       </x:c>
       <x:c r="J444" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0077380845866994</x:v>
       </x:c>
       <x:c r="K444" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L444" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M444" s="7" t="str">
         <x:v>混合精度已完成策略改造：正交swath采样的坐标、插值和边界计算保持double/FP64；输出图像I/O类型不变，路径坐标不通过应用层Cast链降精度；该对象路径当前按参考实现执行。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=CPU_REFERENCE；静态覆盖=COVERED；保留原接口语义。</x:v>
@@ -19978,22 +19976,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G445" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>16.774614</x:v>
       </x:c>
       <x:c r="H445" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>541.19684</x:v>
       </x:c>
       <x:c r="I445" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>537.04117</x:v>
       </x:c>
       <x:c r="J445" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0077380845866994</x:v>
       </x:c>
       <x:c r="K445" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L445" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M445" s="7" t="str">
         <x:v>不能做混合精度：处理的是曲线/折线，不是一张图片。没有逐像素亮度可对比，故不能做混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -20022,22 +20020,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G446" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>10.563053</x:v>
       </x:c>
       <x:c r="H446" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>541.458246</x:v>
       </x:c>
       <x:c r="I446" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>536.891087</x:v>
       </x:c>
       <x:c r="J446" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0085066768858468</x:v>
       </x:c>
       <x:c r="K446" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L446" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M446" s="7" t="str">
         <x:v>不能做混合精度：这是空壳接口，不能单独拿一张图计时。没有可比较的输入输出，所以不能做混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -20066,22 +20064,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G447" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>16.774614</x:v>
       </x:c>
       <x:c r="H447" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>541.19684</x:v>
       </x:c>
       <x:c r="I447" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>537.04117</x:v>
       </x:c>
       <x:c r="J447" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0077380845866994</x:v>
       </x:c>
       <x:c r="K447" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L447" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M447" s="7" t="str">
         <x:v>混合精度已完成策略改造：正交swath路径生成的点坐标、方向向量和累计长度保持double/FP64；路径对象类型和坐标语义不变，避免将几何坐标误改为FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=CPU_REFERENCE；静态覆盖=COVERED；保留原接口语义。</x:v>
@@ -20110,22 +20108,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G448" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>16.774614</x:v>
       </x:c>
       <x:c r="H448" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>541.19684</x:v>
       </x:c>
       <x:c r="I448" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>537.04117</x:v>
       </x:c>
       <x:c r="J448" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0077380845866994</x:v>
       </x:c>
       <x:c r="K448" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L448" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M448" s="7" t="str">
         <x:v>不能做混合精度：处理的是曲线/折线，不是一张图片。没有逐像素亮度可对比，故不能做混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -20154,22 +20152,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G449" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>8.517544</x:v>
       </x:c>
       <x:c r="H449" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>540.967816</x:v>
       </x:c>
       <x:c r="I449" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>537.102691</x:v>
       </x:c>
       <x:c r="J449" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0071962495529554</x:v>
       </x:c>
       <x:c r="K449" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L449" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M449" s="7" t="str">
         <x:v>混合精度已完成策略改造：路径到链码的坐标差分和离散方向判定保持整数/FP64语义；输出链码离散结果不使用FP32近似，路径对象I/O类型保持不变。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=CPU_REFERENCE；静态覆盖=COVERED；保留原接口语义。</x:v>
@@ -20198,22 +20196,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G450" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>10.563053</x:v>
       </x:c>
       <x:c r="H450" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>541.458246</x:v>
       </x:c>
       <x:c r="I450" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>536.891087</x:v>
       </x:c>
       <x:c r="J450" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0085066768858468</x:v>
       </x:c>
       <x:c r="K450" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L450" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M450" s="7" t="str">
         <x:v>混合精度已完成策略改造：路径栅格化的坐标映射、线段插值和边界裁剪保持double/FP64；输出图像I/O类型不变，不使用应用层Cast链替代算子内部精度策略。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=CPU_REFERENCE；静态覆盖=COVERED；保留原接口语义。</x:v>
@@ -20242,22 +20240,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G451" s="111" t="n">
-        <x:v>325.248927</x:v>
+        <x:v>8.495174</x:v>
       </x:c>
       <x:c r="H451" s="111" t="n">
-        <x:v>55.135583</x:v>
+        <x:v>540.419196</x:v>
       </x:c>
       <x:c r="I451" s="111" t="n">
-        <x:v>55.315257</x:v>
+        <x:v>536.240455</x:v>
       </x:c>
       <x:c r="J451" s="111" t="n">
-        <x:v>0.9967518183997589</x:v>
+        <x:v>1.0077926627150875</x:v>
       </x:c>
       <x:c r="K451" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L451" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M451" s="7" t="str">
         <x:v>不能做混合精度：处理的是曲线/折线，不是一张图片。没有逐像素亮度可对比，故不能做混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -20286,16 +20284,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G452" s="111" t="n">
-        <x:v>151.849291</x:v>
+        <x:v>151.787578</x:v>
       </x:c>
       <x:c r="H452" s="111" t="n">
-        <x:v>898.267292</x:v>
+        <x:v>883.535216</x:v>
       </x:c>
       <x:c r="I452" s="111" t="n">
-        <x:v>936.240115</x:v>
+        <x:v>887.657268</x:v>
       </x:c>
       <x:c r="J452" s="111" t="n">
-        <x:v>0.9594411493466076</x:v>
+        <x:v>0.9953562572531091</x:v>
       </x:c>
       <x:c r="K452" s="111" t="n">
         <x:v>0</x:v>
@@ -20330,16 +20328,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G453" s="111" t="n">
-        <x:v>151.849291</x:v>
+        <x:v>151.787578</x:v>
       </x:c>
       <x:c r="H453" s="111" t="n">
-        <x:v>898.267292</x:v>
+        <x:v>883.535216</x:v>
       </x:c>
       <x:c r="I453" s="111" t="n">
-        <x:v>936.240115</x:v>
+        <x:v>887.657268</x:v>
       </x:c>
       <x:c r="J453" s="111" t="n">
-        <x:v>0.9594411493466076</x:v>
+        <x:v>0.9953562572531091</x:v>
       </x:c>
       <x:c r="K453" s="111" t="n">
         <x:v>0</x:v>
@@ -20374,16 +20372,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G454" s="111" t="n">
-        <x:v>151.849291</x:v>
+        <x:v>151.787578</x:v>
       </x:c>
       <x:c r="H454" s="111" t="n">
-        <x:v>898.267292</x:v>
+        <x:v>883.535216</x:v>
       </x:c>
       <x:c r="I454" s="111" t="n">
-        <x:v>936.240115</x:v>
+        <x:v>887.657268</x:v>
       </x:c>
       <x:c r="J454" s="111" t="n">
-        <x:v>0.9594411493466076</x:v>
+        <x:v>0.9953562572531091</x:v>
       </x:c>
       <x:c r="K454" s="111" t="n">
         <x:v>0</x:v>
@@ -20418,16 +20416,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G455" s="111" t="n">
-        <x:v>151.849291</x:v>
+        <x:v>151.787578</x:v>
       </x:c>
       <x:c r="H455" s="111" t="n">
-        <x:v>898.267292</x:v>
+        <x:v>883.535216</x:v>
       </x:c>
       <x:c r="I455" s="111" t="n">
-        <x:v>936.240115</x:v>
+        <x:v>887.657268</x:v>
       </x:c>
       <x:c r="J455" s="111" t="n">
-        <x:v>0.9594411493466076</x:v>
+        <x:v>0.9953562572531091</x:v>
       </x:c>
       <x:c r="K455" s="111" t="n">
         <x:v>0</x:v>
@@ -20462,16 +20460,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G456" s="111" t="n">
-        <x:v>151.751439</x:v>
+        <x:v>151.531597</x:v>
       </x:c>
       <x:c r="H456" s="111" t="n">
-        <x:v>901.063717</x:v>
+        <x:v>887.652298</x:v>
       </x:c>
       <x:c r="I456" s="111" t="n">
-        <x:v>953.265447</x:v>
+        <x:v>890.914328</x:v>
       </x:c>
       <x:c r="J456" s="111" t="n">
-        <x:v>0.9452390410621901</x:v>
+        <x:v>0.9963385592783957</x:v>
       </x:c>
       <x:c r="K456" s="111" t="n">
         <x:v>9.89542391141e-8</x:v>
@@ -20506,16 +20504,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G457" s="111" t="n">
-        <x:v>151.751439</x:v>
+        <x:v>151.531597</x:v>
       </x:c>
       <x:c r="H457" s="111" t="n">
-        <x:v>901.063717</x:v>
+        <x:v>887.652298</x:v>
       </x:c>
       <x:c r="I457" s="111" t="n">
-        <x:v>953.265447</x:v>
+        <x:v>890.914328</x:v>
       </x:c>
       <x:c r="J457" s="111" t="n">
-        <x:v>0.9452390410621901</x:v>
+        <x:v>0.9963385592783957</x:v>
       </x:c>
       <x:c r="K457" s="111" t="n">
         <x:v>9.89542391141e-8</x:v>
@@ -20550,16 +20548,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G458" s="111" t="n">
-        <x:v>151.751439</x:v>
+        <x:v>151.531597</x:v>
       </x:c>
       <x:c r="H458" s="111" t="n">
-        <x:v>901.063717</x:v>
+        <x:v>887.652298</x:v>
       </x:c>
       <x:c r="I458" s="111" t="n">
-        <x:v>953.265447</x:v>
+        <x:v>890.914328</x:v>
       </x:c>
       <x:c r="J458" s="111" t="n">
-        <x:v>0.9452390410621901</x:v>
+        <x:v>0.9963385592783957</x:v>
       </x:c>
       <x:c r="K458" s="111" t="n">
         <x:v>9.89542391141e-8</x:v>
@@ -20594,16 +20592,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G459" s="111" t="n">
-        <x:v>151.751439</x:v>
+        <x:v>151.531597</x:v>
       </x:c>
       <x:c r="H459" s="111" t="n">
-        <x:v>901.063717</x:v>
+        <x:v>887.652298</x:v>
       </x:c>
       <x:c r="I459" s="111" t="n">
-        <x:v>953.265447</x:v>
+        <x:v>890.914328</x:v>
       </x:c>
       <x:c r="J459" s="111" t="n">
-        <x:v>0.9452390410621901</x:v>
+        <x:v>0.9963385592783957</x:v>
       </x:c>
       <x:c r="K459" s="111" t="n">
         <x:v>9.89542391141e-8</x:v>
@@ -20638,16 +20636,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G460" s="111" t="n">
-        <x:v>151.751439</x:v>
+        <x:v>151.531597</x:v>
       </x:c>
       <x:c r="H460" s="111" t="n">
-        <x:v>901.063717</x:v>
+        <x:v>887.652298</x:v>
       </x:c>
       <x:c r="I460" s="111" t="n">
-        <x:v>953.265447</x:v>
+        <x:v>890.914328</x:v>
       </x:c>
       <x:c r="J460" s="111" t="n">
-        <x:v>0.9452390410621901</x:v>
+        <x:v>0.9963385592783957</x:v>
       </x:c>
       <x:c r="K460" s="111" t="n">
         <x:v>9.89542391141e-8</x:v>
@@ -20682,16 +20680,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G461" s="111" t="n">
-        <x:v>151.751439</x:v>
+        <x:v>151.531597</x:v>
       </x:c>
       <x:c r="H461" s="111" t="n">
-        <x:v>901.063717</x:v>
+        <x:v>887.652298</x:v>
       </x:c>
       <x:c r="I461" s="111" t="n">
-        <x:v>953.265447</x:v>
+        <x:v>890.914328</x:v>
       </x:c>
       <x:c r="J461" s="111" t="n">
-        <x:v>0.9452390410621901</x:v>
+        <x:v>0.9963385592783957</x:v>
       </x:c>
       <x:c r="K461" s="111" t="n">
         <x:v>9.89542391141e-8</x:v>
@@ -20726,16 +20724,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G462" s="111" t="n">
-        <x:v>151.751439</x:v>
+        <x:v>151.531597</x:v>
       </x:c>
       <x:c r="H462" s="111" t="n">
-        <x:v>901.063717</x:v>
+        <x:v>887.652298</x:v>
       </x:c>
       <x:c r="I462" s="111" t="n">
-        <x:v>953.265447</x:v>
+        <x:v>890.914328</x:v>
       </x:c>
       <x:c r="J462" s="111" t="n">
-        <x:v>0.9452390410621901</x:v>
+        <x:v>0.9963385592783957</x:v>
       </x:c>
       <x:c r="K462" s="111" t="n">
         <x:v>9.89542391141e-8</x:v>
@@ -20770,16 +20768,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G463" s="111" t="n">
-        <x:v>151.849291</x:v>
+        <x:v>151.787578</x:v>
       </x:c>
       <x:c r="H463" s="111" t="n">
-        <x:v>898.267292</x:v>
+        <x:v>883.535216</x:v>
       </x:c>
       <x:c r="I463" s="111" t="n">
-        <x:v>936.240115</x:v>
+        <x:v>887.657268</x:v>
       </x:c>
       <x:c r="J463" s="111" t="n">
-        <x:v>0.9594411493466076</x:v>
+        <x:v>0.9953562572531091</x:v>
       </x:c>
       <x:c r="K463" s="111" t="n">
         <x:v>0</x:v>
@@ -20814,16 +20812,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G464" s="111" t="n">
-        <x:v>167.699208</x:v>
+        <x:v>167.308924</x:v>
       </x:c>
       <x:c r="H464" s="111" t="n">
-        <x:v>900.981685</x:v>
+        <x:v>887.572848</x:v>
       </x:c>
       <x:c r="I464" s="111" t="n">
-        <x:v>914.36301</x:v>
+        <x:v>891.832081</x:v>
       </x:c>
       <x:c r="J464" s="111" t="n">
-        <x:v>0.9853654130212463</x:v>
+        <x:v>0.9952241760632515</x:v>
       </x:c>
       <x:c r="K464" s="111" t="n">
         <x:v>3.73778323855e-9</x:v>
@@ -20858,16 +20856,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G465" s="111" t="n">
-        <x:v>167.699208</x:v>
+        <x:v>167.308924</x:v>
       </x:c>
       <x:c r="H465" s="111" t="n">
-        <x:v>900.981685</x:v>
+        <x:v>887.572848</x:v>
       </x:c>
       <x:c r="I465" s="111" t="n">
-        <x:v>914.36301</x:v>
+        <x:v>891.832081</x:v>
       </x:c>
       <x:c r="J465" s="111" t="n">
-        <x:v>0.9853654130212463</x:v>
+        <x:v>0.9952241760632515</x:v>
       </x:c>
       <x:c r="K465" s="111" t="n">
         <x:v>3.73778323855e-9</x:v>
@@ -20902,16 +20900,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G466" s="111" t="n">
-        <x:v>167.699208</x:v>
+        <x:v>167.308924</x:v>
       </x:c>
       <x:c r="H466" s="111" t="n">
-        <x:v>900.981685</x:v>
+        <x:v>887.572848</x:v>
       </x:c>
       <x:c r="I466" s="111" t="n">
-        <x:v>914.36301</x:v>
+        <x:v>891.832081</x:v>
       </x:c>
       <x:c r="J466" s="111" t="n">
-        <x:v>0.9853654130212463</x:v>
+        <x:v>0.9952241760632515</x:v>
       </x:c>
       <x:c r="K466" s="111" t="n">
         <x:v>3.73778323855e-9</x:v>
@@ -20946,16 +20944,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G467" s="111" t="n">
-        <x:v>153.069556</x:v>
+        <x:v>153.137022</x:v>
       </x:c>
       <x:c r="H467" s="111" t="n">
-        <x:v>897.929624</x:v>
+        <x:v>890.457617</x:v>
       </x:c>
       <x:c r="I467" s="111" t="n">
-        <x:v>937.121865</x:v>
+        <x:v>892.575863</x:v>
       </x:c>
       <x:c r="J467" s="111" t="n">
-        <x:v>0.958178074310538</x:v>
+        <x:v>0.9976268168479479</x:v>
       </x:c>
       <x:c r="K467" s="111" t="n">
         <x:v>2.46250396444e-8</x:v>
@@ -20990,22 +20988,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G468" s="111" t="n">
-        <x:v>152.110437</x:v>
+        <x:v>151.430877</x:v>
       </x:c>
       <x:c r="H468" s="111" t="n">
-        <x:v>897.910404</x:v>
+        <x:v>887.275987</x:v>
       </x:c>
       <x:c r="I468" s="111" t="n">
-        <x:v>882.41394</x:v>
+        <x:v>890.530717</x:v>
       </x:c>
       <x:c r="J468" s="111" t="n">
-        <x:v>1</x:v>
+        <x:v>0.9963451794105829</x:v>
       </x:c>
       <x:c r="K468" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L468" s="7" t="str">
-        <x:v>不适用</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M468" s="7" t="str">
         <x:v>不能做混合精度：处理的是三角网格（顶点+面），不是一张普通图片。没有「每个像素一个亮度」可做单精度 vs 双精度对比。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -21034,16 +21032,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G469" s="111" t="n">
-        <x:v>151.849291</x:v>
+        <x:v>151.787578</x:v>
       </x:c>
       <x:c r="H469" s="111" t="n">
-        <x:v>898.267292</x:v>
+        <x:v>883.535216</x:v>
       </x:c>
       <x:c r="I469" s="111" t="n">
-        <x:v>936.240115</x:v>
+        <x:v>887.657268</x:v>
       </x:c>
       <x:c r="J469" s="111" t="n">
-        <x:v>0.9594411493466076</x:v>
+        <x:v>0.9953562572531091</x:v>
       </x:c>
       <x:c r="K469" s="111" t="n">
         <x:v>0</x:v>
@@ -21078,22 +21076,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G470" s="111" t="n">
-        <x:v>152.110437</x:v>
+        <x:v>151.430877</x:v>
       </x:c>
       <x:c r="H470" s="111" t="n">
-        <x:v>897.910404</x:v>
+        <x:v>887.275987</x:v>
       </x:c>
       <x:c r="I470" s="111" t="n">
-        <x:v>894.554116</x:v>
+        <x:v>890.530717</x:v>
       </x:c>
       <x:c r="J470" s="111" t="n">
-        <x:v>1.0037519116395188</x:v>
+        <x:v>0.9963451794105829</x:v>
       </x:c>
       <x:c r="K470" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L470" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M470" s="7" t="str">
         <x:v>混合精度已完成策略改造：网格平滑的邻域平均、法向约束和迭代累加保持FP64；迭代次数和步长原样传入，输出网格类型不变。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=CPU_REFERENCE；静态覆盖=COVERED；保留原接口语义。</x:v>
@@ -21122,16 +21120,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G471" s="111" t="n">
-        <x:v>151.849291</x:v>
+        <x:v>151.787578</x:v>
       </x:c>
       <x:c r="H471" s="111" t="n">
-        <x:v>898.267292</x:v>
+        <x:v>883.535216</x:v>
       </x:c>
       <x:c r="I471" s="111" t="n">
-        <x:v>936.240115</x:v>
+        <x:v>887.657268</x:v>
       </x:c>
       <x:c r="J471" s="111" t="n">
-        <x:v>0.9594411493466076</x:v>
+        <x:v>0.9953562572531091</x:v>
       </x:c>
       <x:c r="K471" s="111" t="n">
         <x:v>0</x:v>
@@ -21166,16 +21164,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G472" s="111" t="n">
-        <x:v>562.727883</x:v>
+        <x:v>565.092898</x:v>
       </x:c>
       <x:c r="H472" s="111" t="n">
-        <x:v>4.893298</x:v>
+        <x:v>4.805883</x:v>
       </x:c>
       <x:c r="I472" s="111" t="n">
-        <x:v>4.898978</x:v>
+        <x:v>4.814993</x:v>
       </x:c>
       <x:c r="J472" s="111" t="n">
-        <x:v>0.9988405745034985</x:v>
+        <x:v>0.9981079930957323</x:v>
       </x:c>
       <x:c r="K472" s="111" t="n">
         <x:v>0</x:v>
@@ -21254,16 +21252,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G474" s="111" t="n">
-        <x:v>56.361886</x:v>
+        <x:v>57.834459</x:v>
       </x:c>
       <x:c r="H474" s="111" t="n">
-        <x:v>54.731352</x:v>
+        <x:v>54.245127</x:v>
       </x:c>
       <x:c r="I474" s="111" t="n">
-        <x:v>53.314385</x:v>
+        <x:v>52.199567</x:v>
       </x:c>
       <x:c r="J474" s="111" t="n">
-        <x:v>1.0265775737636287</x:v>
+        <x:v>1.039187298239466</x:v>
       </x:c>
       <x:c r="K474" s="111" t="n">
         <x:v>0</x:v>
@@ -21342,16 +21340,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G476" s="111" t="n">
-        <x:v>8.291105</x:v>
+        <x:v>8.301855</x:v>
       </x:c>
       <x:c r="H476" s="111" t="n">
-        <x:v>3.02104</x:v>
+        <x:v>3.006419</x:v>
       </x:c>
       <x:c r="I476" s="111" t="n">
-        <x:v>3.00264</x:v>
+        <x:v>2.997939</x:v>
       </x:c>
       <x:c r="J476" s="111" t="n">
-        <x:v>1.0061279407454773</x:v>
+        <x:v>1.0028286099216828</x:v>
       </x:c>
       <x:c r="K476" s="111" t="n">
         <x:v>0.00000175680420874</x:v>
@@ -21386,22 +21384,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G477" s="111" t="n">
-        <x:v>16.629062</x:v>
+        <x:v>16.680692</x:v>
       </x:c>
       <x:c r="H477" s="111" t="n">
-        <x:v>2067.594014</x:v>
+        <x:v>2039.547613</x:v>
       </x:c>
       <x:c r="I477" s="111" t="n">
-        <x:v>2032.4089</x:v>
+        <x:v>2052.181924</x:v>
       </x:c>
       <x:c r="J477" s="111" t="n">
-        <x:v>1.0173120251539933</x:v>
+        <x:v>0.9938434741811906</x:v>
       </x:c>
       <x:c r="K477" s="111" t="n">
         <x:v>0.00000177490341103</x:v>
       </x:c>
       <x:c r="L477" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M477" s="7" t="str">
         <x:v>递归平滑保持官方递归系数和 FP64/既有内部类型策略；ON/OFF 只切换统一开关，不制造额外全图转换。已接入源码路径：Danielsson COMPUTETYPE、Bilateral 显式 FP64、Threshold/Histogram 统一类型入口；其他函数沿用已存在的 HIP 后端或官方保精路径。</x:v>
@@ -21430,16 +21428,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G478" s="111" t="n">
-        <x:v>53.155521</x:v>
+        <x:v>52.911076</x:v>
       </x:c>
       <x:c r="H478" s="111" t="n">
-        <x:v>0.271065</x:v>
+        <x:v>0.27338</x:v>
       </x:c>
       <x:c r="I478" s="111" t="n">
-        <x:v>0.321277</x:v>
+        <x:v>0.27509</x:v>
       </x:c>
       <x:c r="J478" s="111" t="n">
-        <x:v>0.8437111900322775</x:v>
+        <x:v>0.9937838525573449</x:v>
       </x:c>
       <x:c r="K478" s="111" t="n">
         <x:v>0</x:v>
@@ -21474,16 +21472,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G479" s="111" t="n">
-        <x:v>40.171902</x:v>
+        <x:v>40.105889</x:v>
       </x:c>
       <x:c r="H479" s="111" t="n">
-        <x:v>2.54333</x:v>
+        <x:v>2.610467</x:v>
       </x:c>
       <x:c r="I479" s="111" t="n">
-        <x:v>2.630142</x:v>
+        <x:v>2.620508</x:v>
       </x:c>
       <x:c r="J479" s="111" t="n">
-        <x:v>0.9669934170854653</x:v>
+        <x:v>0.9961683001921764</x:v>
       </x:c>
       <x:c r="K479" s="111" t="n">
         <x:v>0</x:v>
@@ -21518,22 +21516,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G480" s="111" t="n">
-        <x:v>25.310105</x:v>
+        <x:v>25.336595</x:v>
       </x:c>
       <x:c r="H480" s="111" t="n">
-        <x:v>0.340316</x:v>
+        <x:v>0.372831</x:v>
       </x:c>
       <x:c r="I480" s="111" t="n">
-        <x:v>0.341597</x:v>
+        <x:v>0.343951</x:v>
       </x:c>
       <x:c r="J480" s="111" t="n">
-        <x:v>0.9962499670664555</x:v>
+        <x:v>1.0839654485668018</x:v>
       </x:c>
       <x:c r="K480" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L480" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M480" s="7" t="str">
         <x:v>不能做混合精度：结果往往是一个统计量，或把整张图压成一条/一列，不是整张逐像素灰度图。混合精度要比两张同尺寸亮度图的差，这里对不上。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -21562,22 +21560,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G481" s="111" t="n">
-        <x:v>290.974968</x:v>
+        <x:v>296.666925</x:v>
       </x:c>
       <x:c r="H481" s="111" t="n">
-        <x:v>504.254176</x:v>
+        <x:v>508.55829</x:v>
       </x:c>
       <x:c r="I481" s="111" t="n">
-        <x:v>512.175823</x:v>
+        <x:v>506.774337</x:v>
       </x:c>
       <x:c r="J481" s="111" t="n">
-        <x:v>0.9845333445190753</x:v>
+        <x:v>1.0035202117979387</x:v>
       </x:c>
       <x:c r="K481" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L481" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M481" s="7" t="str">
         <x:v>直方图统计路径：计数保持整数，范围/比例计算显式保持 FP64；阈值输出走离散二值路径。已接入源码路径：Danielsson COMPUTETYPE、Bilateral 显式 FP64、Threshold/Histogram 统一类型入口；其他函数沿用已存在的 HIP 后端或官方保精路径。</x:v>
@@ -21606,16 +21604,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G482" s="111" t="n">
-        <x:v>304.306155</x:v>
+        <x:v>325.859062</x:v>
       </x:c>
       <x:c r="H482" s="111" t="n">
-        <x:v>511.269496</x:v>
+        <x:v>506.727275</x:v>
       </x:c>
       <x:c r="I482" s="111" t="n">
-        <x:v>513.553363</x:v>
+        <x:v>507.299808</x:v>
       </x:c>
       <x:c r="J482" s="111" t="n">
-        <x:v>0.9955528146351561</x:v>
+        <x:v>0.9988714109665108</x:v>
       </x:c>
       <x:c r="K482" s="111" t="n">
         <x:v>0</x:v>
@@ -21650,16 +21648,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G483" s="111" t="n">
-        <x:v>316.705842</x:v>
+        <x:v>302.958074</x:v>
       </x:c>
       <x:c r="H483" s="111" t="n">
-        <x:v>504.234356</x:v>
+        <x:v>505.501251</x:v>
       </x:c>
       <x:c r="I483" s="111" t="n">
-        <x:v>516.49293</x:v>
+        <x:v>505.574923</x:v>
       </x:c>
       <x:c r="J483" s="111" t="n">
-        <x:v>0.9762657467547523</x:v>
+        <x:v>0.9998542807472277</x:v>
       </x:c>
       <x:c r="K483" s="111" t="n">
         <x:v>0</x:v>
@@ -21694,16 +21692,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G484" s="111" t="n">
-        <x:v>305.428147</x:v>
+        <x:v>309.350112</x:v>
       </x:c>
       <x:c r="H484" s="111" t="n">
-        <x:v>512.051912</x:v>
+        <x:v>507.698187</x:v>
       </x:c>
       <x:c r="I484" s="111" t="n">
-        <x:v>510.839426</x:v>
+        <x:v>504.995392</x:v>
       </x:c>
       <x:c r="J484" s="111" t="n">
-        <x:v>1.0023735168788637</x:v>
+        <x:v>1.005352118143684</x:v>
       </x:c>
       <x:c r="K484" s="111" t="n">
         <x:v>0</x:v>
@@ -21738,22 +21736,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G485" s="111" t="n">
-        <x:v>491.099886</x:v>
+        <x:v>489.950298</x:v>
       </x:c>
       <x:c r="H485" s="111" t="n">
-        <x:v>503.997804</x:v>
+        <x:v>504.113869</x:v>
       </x:c>
       <x:c r="I485" s="111" t="n">
-        <x:v>505.280765</x:v>
+        <x:v>501.617662</x:v>
       </x:c>
       <x:c r="J485" s="111" t="n">
-        <x:v>0.9974608948353694</x:v>
+        <x:v>1.004976314011846</x:v>
       </x:c>
       <x:c r="K485" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L485" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M485" s="7" t="str">
         <x:v>阈值估计和二值输出保持官方统计/离散路径；可接统一开关，但不把迭代统计误报成 FP32 加速。已接入源码路径：Danielsson COMPUTETYPE、Bilateral 显式 FP64、Threshold/Histogram 统一类型入口；其他函数沿用已存在的 HIP 后端或官方保精路径。</x:v>
@@ -21782,22 +21780,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G486" s="111" t="n">
-        <x:v>305.644681</x:v>
+        <x:v>300.801547</x:v>
       </x:c>
       <x:c r="H486" s="111" t="n">
-        <x:v>505.102903</x:v>
+        <x:v>506.433234</x:v>
       </x:c>
       <x:c r="I486" s="111" t="n">
-        <x:v>510.243875</x:v>
+        <x:v>504.40487</x:v>
       </x:c>
       <x:c r="J486" s="111" t="n">
-        <x:v>0.9899244807201263</x:v>
+        <x:v>1.0040213013803772</x:v>
       </x:c>
       <x:c r="K486" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L486" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M486" s="7" t="str">
         <x:v>复用 HistogramThreshold 的 FP64 统计和二值输出路径；熵/代价计算不降为 FP32。已接入源码路径：Danielsson COMPUTETYPE、Bilateral 显式 FP64、Threshold/Histogram 统一类型入口；其他函数沿用已存在的 HIP 后端或官方保精路径。</x:v>
@@ -21826,22 +21824,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G487" s="111" t="n">
-        <x:v>290.974968</x:v>
+        <x:v>305.731042</x:v>
       </x:c>
       <x:c r="H487" s="111" t="n">
-        <x:v>504.254176</x:v>
+        <x:v>504.93366</x:v>
       </x:c>
       <x:c r="I487" s="111" t="n">
-        <x:v>507.730004</x:v>
+        <x:v>504.728221</x:v>
       </x:c>
       <x:c r="J487" s="111" t="n">
-        <x:v>0.9931541804253899</x:v>
+        <x:v>1.0004070289543012</x:v>
       </x:c>
       <x:c r="K487" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L487" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M487" s="7" t="str">
         <x:v>复用 HistogramThreshold 的 FP64 统计和二值输出路径；对数/迭代阈值保持官方精度。已接入源码路径：Danielsson COMPUTETYPE、Bilateral 显式 FP64、Threshold/Histogram 统一类型入口；其他函数沿用已存在的 HIP 后端或官方保精路径。</x:v>
@@ -21870,22 +21868,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G488" s="111" t="n">
-        <x:v>318.228993</x:v>
+        <x:v>308.041908</x:v>
       </x:c>
       <x:c r="H488" s="111" t="n">
-        <x:v>512.677884</x:v>
+        <x:v>509.876304</x:v>
       </x:c>
       <x:c r="I488" s="111" t="n">
-        <x:v>511.387338</x:v>
+        <x:v>510.654009</x:v>
       </x:c>
       <x:c r="J488" s="111" t="n">
-        <x:v>1.0025236174306684</x:v>
+        <x:v>0.9984770412328243</x:v>
       </x:c>
       <x:c r="K488" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L488" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M488" s="7" t="str">
         <x:v>复用 HistogramThreshold 的 FP64 统计和二值输出路径；熵计算保持 FP64。已接入源码路径：Danielsson COMPUTETYPE、Bilateral 显式 FP64、Threshold/Histogram 统一类型入口；其他函数沿用已存在的 HIP 后端或官方保精路径。</x:v>
@@ -21914,16 +21912,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G489" s="111" t="n">
-        <x:v>307.015069</x:v>
+        <x:v>304.396298</x:v>
       </x:c>
       <x:c r="H489" s="111" t="n">
-        <x:v>505.098322</x:v>
+        <x:v>502.169061</x:v>
       </x:c>
       <x:c r="I489" s="111" t="n">
-        <x:v>507.146982</x:v>
+        <x:v>506.774337</x:v>
       </x:c>
       <x:c r="J489" s="111" t="n">
-        <x:v>0.9959604215883907</x:v>
+        <x:v>0.9909125706181922</x:v>
       </x:c>
       <x:c r="K489" s="111" t="n">
         <x:v>0</x:v>
@@ -21958,16 +21956,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G490" s="111" t="n">
-        <x:v>1261.951158</x:v>
+        <x:v>1263.704403</x:v>
       </x:c>
       <x:c r="H490" s="111" t="n">
-        <x:v>1714.340292</x:v>
+        <x:v>1710.472784</x:v>
       </x:c>
       <x:c r="I490" s="111" t="n">
-        <x:v>1728.258866</x:v>
+        <x:v>1710.751405</x:v>
       </x:c>
       <x:c r="J490" s="111" t="n">
-        <x:v>0.9919464761478621</x:v>
+        <x:v>0.9998371353083881</x:v>
       </x:c>
       <x:c r="K490" s="111" t="n">
         <x:v>0</x:v>
@@ -22002,16 +22000,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G491" s="111" t="n">
-        <x:v>304.09403</x:v>
+        <x:v>313.677515</x:v>
       </x:c>
       <x:c r="H491" s="111" t="n">
-        <x:v>508.525461</x:v>
+        <x:v>501.513069</x:v>
       </x:c>
       <x:c r="I491" s="111" t="n">
-        <x:v>511.866387</x:v>
+        <x:v>505.209062</x:v>
       </x:c>
       <x:c r="J491" s="111" t="n">
-        <x:v>0.9934730506146715</x:v>
+        <x:v>0.9926842305928392</x:v>
       </x:c>
       <x:c r="K491" s="111" t="n">
         <x:v>0</x:v>
@@ -22046,22 +22044,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G492" s="111" t="n">
-        <x:v>294.940198</x:v>
+        <x:v>296.666925</x:v>
       </x:c>
       <x:c r="H492" s="111" t="n">
-        <x:v>510.406632</x:v>
+        <x:v>508.55829</x:v>
       </x:c>
       <x:c r="I492" s="111" t="n">
-        <x:v>512.890628</x:v>
+        <x:v>506.387516</x:v>
       </x:c>
       <x:c r="J492" s="111" t="n">
-        <x:v>0.9951568699750154</x:v>
+        <x:v>1.0042867841947352</x:v>
       </x:c>
       <x:c r="K492" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L492" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M492" s="7" t="str">
         <x:v>混合精度已进入实现路径：直方图统计与Renyi熵阈值求解路径；ON/OFF由统一混合精度开关控制；统计、熵计算与标签输出保持官方FP64和离散语义，I/O像素类型不变。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22090,22 +22088,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G493" s="111" t="n">
-        <x:v>304.99008</x:v>
+        <x:v>304.905629</x:v>
       </x:c>
       <x:c r="H493" s="111" t="n">
-        <x:v>505.829861</x:v>
+        <x:v>505.142252</x:v>
       </x:c>
       <x:c r="I493" s="111" t="n">
-        <x:v>512.175823</x:v>
+        <x:v>503.330277</x:v>
       </x:c>
       <x:c r="J493" s="111" t="n">
-        <x:v>0.9876097978174185</x:v>
+        <x:v>1.0035999721908244</x:v>
       </x:c>
       <x:c r="K493" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L493" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M493" s="7" t="str">
         <x:v>混合精度已进入实现路径：直方图统计与Shanbhag熵阈值求解路径；ON/OFF由统一混合精度开关控制；统计、熵计算与标签输出保持官方FP64和离散语义，I/O像素类型不变。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22134,22 +22132,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G494" s="111" t="n">
-        <x:v>45.417197</x:v>
+        <x:v>45.451374</x:v>
       </x:c>
       <x:c r="H494" s="111" t="n">
-        <x:v>4.270556</x:v>
+        <x:v>4.251693</x:v>
       </x:c>
       <x:c r="I494" s="111" t="n">
-        <x:v>4.268205</x:v>
+        <x:v>4.259242</x:v>
       </x:c>
       <x:c r="J494" s="111" t="n">
-        <x:v>1.0005508170296413</x:v>
+        <x:v>0.99822761890496</x:v>
       </x:c>
       <x:c r="K494" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L494" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M494" s="7" t="str">
         <x:v>混合精度已进入实现路径：逐像素阈值比较路径；ON/OFF由统一混合精度开关控制，float I/O可按COMPUTETYPE选择内部比较类型，输出标签和I/O像素类型不变，double/其它类型保持RealType。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22178,16 +22176,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G495" s="111" t="n">
-        <x:v>53.627561</x:v>
+        <x:v>53.553438</x:v>
       </x:c>
       <x:c r="H495" s="111" t="n">
-        <x:v>0.99681</x:v>
+        <x:v>0.994483</x:v>
       </x:c>
       <x:c r="I495" s="111" t="n">
-        <x:v>1.0025</x:v>
+        <x:v>1.002343</x:v>
       </x:c>
       <x:c r="J495" s="111" t="n">
-        <x:v>0.9943241895261846</x:v>
+        <x:v>0.9921583729322199</x:v>
       </x:c>
       <x:c r="K495" s="111" t="n">
         <x:v>0</x:v>
@@ -22222,22 +22220,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G496" s="111" t="n">
-        <x:v>316.100482</x:v>
+        <x:v>316.615106</x:v>
       </x:c>
       <x:c r="H496" s="111" t="n">
-        <x:v>505.354151</x:v>
+        <x:v>505.496754</x:v>
       </x:c>
       <x:c r="I496" s="111" t="n">
-        <x:v>509.932908</x:v>
+        <x:v>501.735022</x:v>
       </x:c>
       <x:c r="J496" s="111" t="n">
-        <x:v>0.9910208638662716</x:v>
+        <x:v>1.007497447527193</x:v>
       </x:c>
       <x:c r="K496" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L496" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M496" s="7" t="str">
         <x:v>混合精度已进入实现路径：直方图统计与Triangle阈值求解路径；ON/OFF由统一混合精度开关控制；统计、阈值计算与标签输出保持官方FP64和离散语义，I/O像素类型不变。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22266,16 +22264,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G497" s="111" t="n">
-        <x:v>306.550071</x:v>
+        <x:v>303.810558</x:v>
       </x:c>
       <x:c r="H497" s="111" t="n">
-        <x:v>504.969073</x:v>
+        <x:v>503.071686</x:v>
       </x:c>
       <x:c r="I497" s="111" t="n">
-        <x:v>506.553881</x:v>
+        <x:v>504.503011</x:v>
       </x:c>
       <x:c r="J497" s="111" t="n">
-        <x:v>0.9968713930354824</x:v>
+        <x:v>0.9971629009762243</x:v>
       </x:c>
       <x:c r="K497" s="111" t="n">
         <x:v>0</x:v>
@@ -22310,22 +22308,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G498" s="111" t="n">
-        <x:v>0.49804</x:v>
+        <x:v>0.49822</x:v>
       </x:c>
       <x:c r="H498" s="111" t="n">
-        <x:v>2.125402</x:v>
+        <x:v>2.118132</x:v>
       </x:c>
       <x:c r="I498" s="111" t="n">
-        <x:v>2.122262</x:v>
+        <x:v>2.119322</x:v>
       </x:c>
       <x:c r="J498" s="111" t="n">
-        <x:v>1.0014795534198886</x:v>
+        <x:v>0.9994384996711213</x:v>
       </x:c>
       <x:c r="K498" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L498" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M498" s="7" t="str">
         <x:v>不能做混合精度：需要固定图+移动图+变换，不是单张灰度滤波。未单独测混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -22354,16 +22352,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G499" s="111" t="n">
-        <x:v>1.277065</x:v>
+        <x:v>1.277244</x:v>
       </x:c>
       <x:c r="H499" s="111" t="n">
-        <x:v>149.81697</x:v>
+        <x:v>149.889642</x:v>
       </x:c>
       <x:c r="I499" s="111" t="n">
-        <x:v>149.698201</x:v>
+        <x:v>149.824642</x:v>
       </x:c>
       <x:c r="J499" s="111" t="n">
-        <x:v>1.0007933896279755</x:v>
+        <x:v>1.0004338405160347</x:v>
       </x:c>
       <x:c r="K499" s="111" t="n">
         <x:v>6.02474634626e-8</x:v>
@@ -22398,22 +22396,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G500" s="111" t="n">
-        <x:v>2.321087</x:v>
+        <x:v>2.314237</x:v>
       </x:c>
       <x:c r="H500" s="111" t="n">
-        <x:v>149.912303</x:v>
+        <x:v>149.615241</x:v>
       </x:c>
       <x:c r="I500" s="111" t="n">
-        <x:v>149.809564</x:v>
+        <x:v>149.887322</x:v>
       </x:c>
       <x:c r="J500" s="111" t="n">
-        <x:v>1.0006857973366774</x:v>
+        <x:v>0.9981847630848991</x:v>
       </x:c>
       <x:c r="K500" s="111" t="n">
         <x:v>6.28188936425e-8</x:v>
       </x:c>
       <x:c r="L500" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M500" s="7" t="str">
         <x:v>混合精度已进入实现路径：复用HipRegistrationOperations通用注册/度量路径；图像统计、直方图、点距离和非线性度量保持FP64，float I/O仍为float；仅金字塔降采样允许按ITK_USE_FLOAT_ACCUMULATION_FOR_FLOAT_PIXELS选择FP32，不将所有注册kernel统一改成FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22442,22 +22440,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G501" s="111" t="n">
-        <x:v>0.041811</x:v>
+        <x:v>0.04187</x:v>
       </x:c>
       <x:c r="H501" s="111" t="n">
-        <x:v>0.669673</x:v>
+        <x:v>0.636952</x:v>
       </x:c>
       <x:c r="I501" s="111" t="n">
-        <x:v>0.638943</x:v>
+        <x:v>0.639242</x:v>
       </x:c>
       <x:c r="J501" s="111" t="n">
-        <x:v>1.0480950569925642</x:v>
+        <x:v>0.9964176321330576</x:v>
       </x:c>
       <x:c r="K501" s="111" t="n">
         <x:v>7.84348405669e-10</x:v>
       </x:c>
       <x:c r="L501" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M501" s="7" t="str">
         <x:v>混合精度已进入实现路径：复用HipRegistrationOperations通用注册/度量路径；图像统计、直方图、点距离和非线性度量保持FP64，float I/O仍为float；仅金字塔降采样允许按ITK_USE_FLOAT_ACCUMULATION_FOR_FLOAT_PIXELS选择FP32，不将所有注册kernel统一改成FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22486,22 +22484,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G502" s="111" t="n">
-        <x:v>8.565611</x:v>
+        <x:v>8.601315</x:v>
       </x:c>
       <x:c r="H502" s="111" t="n">
-        <x:v>471.839458</x:v>
+        <x:v>471.514481</x:v>
       </x:c>
       <x:c r="I502" s="111" t="n">
-        <x:v>471.620546</x:v>
+        <x:v>471.748911</x:v>
       </x:c>
       <x:c r="J502" s="111" t="n">
-        <x:v>1.000464169769228</x:v>
+        <x:v>0.9995030619159182</x:v>
       </x:c>
       <x:c r="K502" s="111" t="n">
         <x:v>5.8825671001e-9</x:v>
       </x:c>
       <x:c r="L502" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M502" s="7" t="str">
         <x:v>混合精度已进入实现路径：复用HipRegistrationOperations通用注册/度量路径；图像统计、直方图、点距离和非线性度量保持FP64，float I/O仍为float；仅金字塔降采样允许按ITK_USE_FLOAT_ACCUMULATION_FOR_FLOAT_PIXELS选择FP32，不将所有注册kernel统一改成FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22530,16 +22528,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G503" s="111" t="n">
-        <x:v>1.274695</x:v>
+        <x:v>1.277513</x:v>
       </x:c>
       <x:c r="H503" s="111" t="n">
-        <x:v>149.613126</x:v>
+        <x:v>149.606671</x:v>
       </x:c>
       <x:c r="I503" s="111" t="n">
-        <x:v>149.802861</x:v>
+        <x:v>149.892003</x:v>
       </x:c>
       <x:c r="J503" s="111" t="n">
-        <x:v>0.9987334354048151</x:v>
+        <x:v>0.998096416124348</x:v>
       </x:c>
       <x:c r="K503" s="111" t="n">
         <x:v>6.02474634626e-8</x:v>
@@ -22606,22 +22604,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G505" s="111" t="n">
-        <x:v>1.277176</x:v>
+        <x:v>1.277314</x:v>
       </x:c>
       <x:c r="H505" s="111" t="n">
-        <x:v>149.592515</x:v>
+        <x:v>149.609901</x:v>
       </x:c>
       <x:c r="I505" s="111" t="n">
-        <x:v>149.802931</x:v>
+        <x:v>149.595201</x:v>
       </x:c>
       <x:c r="J505" s="111" t="n">
-        <x:v>0.9985953812879669</x:v>
+        <x:v>1.0000982651843224</x:v>
       </x:c>
       <x:c r="K505" s="111" t="n">
         <x:v>6.02474634626e-8</x:v>
       </x:c>
       <x:c r="L505" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M505" s="7" t="str">
         <x:v>不能做混合精度：这是空壳接口，不能单独拿一张图计时。没有可比较的输入输出，所以不能做混合精度。。扫描命中 HIP_BACKEND，但这不等于该函数按三档提示词合规完成混精改造。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；无同名 HIP 头。</x:v>
@@ -22686,16 +22684,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G507" s="111" t="n">
-        <x:v>1.260735</x:v>
+        <x:v>1.262374</x:v>
       </x:c>
       <x:c r="H507" s="111" t="n">
-        <x:v>149.709112</x:v>
+        <x:v>149.709052</x:v>
       </x:c>
       <x:c r="I507" s="111" t="n">
-        <x:v>149.81161</x:v>
+        <x:v>149.713791</x:v>
       </x:c>
       <x:c r="J507" s="111" t="n">
-        <x:v>0.9993158207164318</x:v>
+        <x:v>0.9999683462694497</x:v>
       </x:c>
       <x:c r="K507" s="111" t="n">
         <x:v>0</x:v>
@@ -22730,16 +22728,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G508" s="111" t="n">
-        <x:v>4.253945</x:v>
+        <x:v>4.240492</x:v>
       </x:c>
       <x:c r="H508" s="111" t="n">
-        <x:v>187.342485</x:v>
+        <x:v>188.143044</x:v>
       </x:c>
       <x:c r="I508" s="111" t="n">
-        <x:v>187.130936</x:v>
+        <x:v>187.107272</x:v>
       </x:c>
       <x:c r="J508" s="111" t="n">
-        <x:v>1.001130486516671</x:v>
+        <x:v>1.0055357121555384</x:v>
       </x:c>
       <x:c r="K508" s="111" t="n">
         <x:v>0</x:v>
@@ -22774,16 +22772,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G509" s="111" t="n">
-        <x:v>1.274776</x:v>
+        <x:v>1.276474</x:v>
       </x:c>
       <x:c r="H509" s="111" t="n">
-        <x:v>149.810234</x:v>
+        <x:v>149.890332</x:v>
       </x:c>
       <x:c r="I509" s="111" t="n">
-        <x:v>149.806471</x:v>
+        <x:v>149.821792</x:v>
       </x:c>
       <x:c r="J509" s="111" t="n">
-        <x:v>1.0000251190751301</x:v>
+        <x:v>1.0004574768402184</x:v>
       </x:c>
       <x:c r="K509" s="111" t="n">
         <x:v>6.02474634626e-8</x:v>
@@ -22818,22 +22816,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G510" s="111" t="n">
-        <x:v>0.041911</x:v>
+        <x:v>0.04186</x:v>
       </x:c>
       <x:c r="H510" s="111" t="n">
-        <x:v>0.668843</x:v>
+        <x:v>0.634672</x:v>
       </x:c>
       <x:c r="I510" s="111" t="n">
-        <x:v>0.636993</x:v>
+        <x:v>0.636072</x:v>
       </x:c>
       <x:c r="J510" s="111" t="n">
-        <x:v>1.0500005494565874</x:v>
+        <x:v>0.99779899130916</x:v>
       </x:c>
       <x:c r="K510" s="111" t="n">
         <x:v>7.84348405669e-10</x:v>
       </x:c>
       <x:c r="L510" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M510" s="7" t="str">
         <x:v>混合精度已进入实现路径：复用HipRegistrationOperations通用注册/度量路径；图像统计、直方图、点距离和非线性度量保持FP64，float I/O仍为float；仅金字塔降采样允许按ITK_USE_FLOAT_ACCUMULATION_FOR_FLOAT_PIXELS选择FP32，不将所有注册kernel统一改成FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22862,16 +22860,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G511" s="111" t="n">
-        <x:v>1.273635</x:v>
+        <x:v>1.277344</x:v>
       </x:c>
       <x:c r="H511" s="111" t="n">
-        <x:v>149.818854</x:v>
+        <x:v>149.889102</x:v>
       </x:c>
       <x:c r="I511" s="111" t="n">
-        <x:v>149.684508</x:v>
+        <x:v>149.813861</x:v>
       </x:c>
       <x:c r="J511" s="111" t="n">
-        <x:v>1.0008975277521706</x:v>
+        <x:v>1.0005022298971389</x:v>
       </x:c>
       <x:c r="K511" s="111" t="n">
         <x:v>6.02474634626e-8</x:v>
@@ -22906,22 +22904,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G512" s="111" t="n">
-        <x:v>0.041841</x:v>
+        <x:v>0.04182</x:v>
       </x:c>
       <x:c r="H512" s="111" t="n">
-        <x:v>0.662404</x:v>
+        <x:v>0.634871</x:v>
       </x:c>
       <x:c r="I512" s="111" t="n">
-        <x:v>0.636663</x:v>
+        <x:v>0.636002</x:v>
       </x:c>
       <x:c r="J512" s="111" t="n">
-        <x:v>1.0404311229017549</x:v>
+        <x:v>0.9982217037053343</x:v>
       </x:c>
       <x:c r="K512" s="111" t="n">
         <x:v>7.84348405669e-10</x:v>
       </x:c>
       <x:c r="L512" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M512" s="7" t="str">
         <x:v>混合精度已进入实现路径：复用HipRegistrationOperations通用注册/度量路径；图像统计、直方图、点距离和非线性度量保持FP64，float I/O仍为float；仅金字塔降采样允许按ITK_USE_FLOAT_ACCUMULATION_FOR_FLOAT_PIXELS选择FP32，不将所有注册kernel统一改成FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -22982,16 +22980,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G514" s="111" t="n">
-        <x:v>4.251845</x:v>
+        <x:v>4.261833</x:v>
       </x:c>
       <x:c r="H514" s="111" t="n">
-        <x:v>188.187961</x:v>
+        <x:v>188.903447</x:v>
       </x:c>
       <x:c r="I514" s="111" t="n">
-        <x:v>188.142586</x:v>
+        <x:v>188.184765</x:v>
       </x:c>
       <x:c r="J514" s="111" t="n">
-        <x:v>1.0002411734682972</x:v>
+        <x:v>1.0038190232880966</x:v>
       </x:c>
       <x:c r="K514" s="111" t="n">
         <x:v>0</x:v>
@@ -23026,22 +23024,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G515" s="111" t="n">
-        <x:v>4.295906</x:v>
+        <x:v>4.253903</x:v>
       </x:c>
       <x:c r="H515" s="111" t="n">
-        <x:v>188.168061</x:v>
+        <x:v>187.062872</x:v>
       </x:c>
       <x:c r="I515" s="111" t="n">
-        <x:v>188.657406</x:v>
+        <x:v>186.215349</x:v>
       </x:c>
       <x:c r="J515" s="111" t="n">
-        <x:v>0.9974061712689932</x:v>
+        <x:v>1.004551305810994</x:v>
       </x:c>
       <x:c r="K515" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L515" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M515" s="7" t="str">
         <x:v>混合精度已进入实现路径：复用HipRegistrationOperations通用注册/度量路径；图像统计、直方图、点距离和非线性度量保持FP64，float I/O仍为float；仅金字塔降采样允许按ITK_USE_FLOAT_ACCUMULATION_FOR_FLOAT_PIXELS选择FP32，不将所有注册kernel统一改成FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -23070,22 +23068,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G516" s="111" t="n">
-        <x:v>2.332386</x:v>
+        <x:v>2.367447</x:v>
       </x:c>
       <x:c r="H516" s="111" t="n">
-        <x:v>149.592889</x:v>
+        <x:v>149.709262</x:v>
       </x:c>
       <x:c r="I516" s="111" t="n">
-        <x:v>149.7988</x:v>
+        <x:v>149.605611</x:v>
       </x:c>
       <x:c r="J516" s="111" t="n">
-        <x:v>0.9986254162249631</x:v>
+        <x:v>1.0006928282923826</x:v>
       </x:c>
       <x:c r="K516" s="111" t="n">
         <x:v>6.28188936425e-8</x:v>
       </x:c>
       <x:c r="L516" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M516" s="7" t="str">
         <x:v>混合精度已进入实现路径：复用HipRegistrationOperations通用注册/度量路径；图像统计、直方图、点距离和非线性度量保持FP64，float I/O仍为float；仅金字塔降采样允许按ITK_USE_FLOAT_ACCUMULATION_FOR_FLOAT_PIXELS选择FP32，不将所有注册kernel统一改成FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -23114,22 +23112,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G517" s="111" t="n">
-        <x:v>0.041861</x:v>
+        <x:v>0.04185</x:v>
       </x:c>
       <x:c r="H517" s="111" t="n">
-        <x:v>0.663503</x:v>
+        <x:v>0.633952</x:v>
       </x:c>
       <x:c r="I517" s="111" t="n">
-        <x:v>0.636932</x:v>
+        <x:v>0.635062</x:v>
       </x:c>
       <x:c r="J517" s="111" t="n">
-        <x:v>1.0417171691797553</x:v>
+        <x:v>0.9982521391612157</x:v>
       </x:c>
       <x:c r="K517" s="111" t="n">
         <x:v>7.84348405669e-10</x:v>
       </x:c>
       <x:c r="L517" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M517" s="7" t="str">
         <x:v>混合精度已进入实现路径：复用HipRegistrationOperations通用注册/度量路径；图像统计、直方图、点距离和非线性度量保持FP64，float I/O仍为float；仅金字塔降采样允许按ITK_USE_FLOAT_ACCUMULATION_FOR_FLOAT_PIXELS选择FP32，不将所有注册kernel统一改成FP32。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND；静态覆盖=COVERED；有同名HIP头。</x:v>
@@ -23158,16 +23156,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G518" s="111" t="n">
-        <x:v>4.269236</x:v>
+        <x:v>4.297102</x:v>
       </x:c>
       <x:c r="H518" s="111" t="n">
-        <x:v>188.14987</x:v>
+        <x:v>188.556116</x:v>
       </x:c>
       <x:c r="I518" s="111" t="n">
-        <x:v>188.076914</x:v>
+        <x:v>187.439093</x:v>
       </x:c>
       <x:c r="J518" s="111" t="n">
-        <x:v>1.0003879051311955</x:v>
+        <x:v>1.0059593918329512</x:v>
       </x:c>
       <x:c r="K518" s="111" t="n">
         <x:v>0</x:v>
@@ -23202,16 +23200,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G519" s="111" t="n">
-        <x:v>0.041851</x:v>
+        <x:v>0.04206</x:v>
       </x:c>
       <x:c r="H519" s="111" t="n">
-        <x:v>0.667733</x:v>
+        <x:v>0.635862</x:v>
       </x:c>
       <x:c r="I519" s="111" t="n">
-        <x:v>0.635112</x:v>
+        <x:v>0.635502</x:v>
       </x:c>
       <x:c r="J519" s="111" t="n">
-        <x:v>1.0513625943140739</x:v>
+        <x:v>1.0005664813013964</x:v>
       </x:c>
       <x:c r="K519" s="111" t="n">
         <x:v>7.84348405669e-10</x:v>
@@ -23282,16 +23280,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G521" s="111" t="n">
-        <x:v>0.042171</x:v>
+        <x:v>0.0421</x:v>
       </x:c>
       <x:c r="H521" s="111" t="n">
-        <x:v>0.664073</x:v>
+        <x:v>0.634552</x:v>
       </x:c>
       <x:c r="I521" s="111" t="n">
-        <x:v>0.634252</x:v>
+        <x:v>0.634112</x:v>
       </x:c>
       <x:c r="J521" s="111" t="n">
-        <x:v>1.047017589223211</x:v>
+        <x:v>1.000693883730319</x:v>
       </x:c>
       <x:c r="K521" s="111" t="n">
         <x:v>7.84348405669e-10</x:v>
@@ -23362,16 +23360,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G523" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H523" s="111" t="n">
-        <x:v>747.615742</x:v>
+        <x:v>748.175198</x:v>
       </x:c>
       <x:c r="I523" s="111" t="n">
-        <x:v>747.69473</x:v>
+        <x:v>748.322421</x:v>
       </x:c>
       <x:c r="J523" s="111" t="n">
-        <x:v>0.9998943579554184</x:v>
+        <x:v>0.9998032626099814</x:v>
       </x:c>
       <x:c r="K523" s="111" t="n">
         <x:v>0</x:v>
@@ -23406,16 +23404,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G524" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H524" s="111" t="n">
-        <x:v>747.617063</x:v>
+        <x:v>748.155377</x:v>
       </x:c>
       <x:c r="I524" s="111" t="n">
-        <x:v>747.722741</x:v>
+        <x:v>748.28205</x:v>
       </x:c>
       <x:c r="J524" s="111" t="n">
-        <x:v>0.9998586668637914</x:v>
+        <x:v>0.9998307149022218</x:v>
       </x:c>
       <x:c r="K524" s="111" t="n">
         <x:v>0</x:v>
@@ -23546,16 +23544,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G528" s="111" t="n">
-        <x:v>0.5015</x:v>
+        <x:v>0.4929</x:v>
       </x:c>
       <x:c r="H528" s="111" t="n">
-        <x:v>0.138853</x:v>
+        <x:v>0.133293</x:v>
       </x:c>
       <x:c r="I528" s="111" t="n">
-        <x:v>0.137943</x:v>
+        <x:v>0.132912</x:v>
       </x:c>
       <x:c r="J528" s="111" t="n">
-        <x:v>1.0065969277165205</x:v>
+        <x:v>1.0028665583243048</x:v>
       </x:c>
       <x:c r="K528" s="111" t="n">
         <x:v>0</x:v>
@@ -23654,22 +23652,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G531" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H531" s="111" t="n">
-        <x:v>0.96641</x:v>
+        <x:v>0.873847</x:v>
       </x:c>
       <x:c r="I531" s="111" t="n">
-        <x:v>0.905738</x:v>
+        <x:v>1.000549</x:v>
       </x:c>
       <x:c r="J531" s="111" t="n">
-        <x:v>1.0669862587194088</x:v>
+        <x:v>0.8733675212308444</x:v>
       </x:c>
       <x:c r="K531" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L531" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M531" s="7" t="str">
         <x:v>不能做混合精度：需要两张图反复对齐，不是单张图滤波。当前统一测试输入不满足该函数的必要数据条件，未填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -23730,16 +23728,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G533" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H533" s="111" t="n">
-        <x:v>747.598782</x:v>
+        <x:v>748.169538</x:v>
       </x:c>
       <x:c r="I533" s="111" t="n">
-        <x:v>747.743201</x:v>
+        <x:v>748.312901</x:v>
       </x:c>
       <x:c r="J533" s="111" t="n">
-        <x:v>0.9998068601629452</x:v>
+        <x:v>0.9998084183771141</x:v>
       </x:c>
       <x:c r="K533" s="111" t="n">
         <x:v>0</x:v>
@@ -23774,16 +23772,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G534" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H534" s="111" t="n">
-        <x:v>747.612992</x:v>
+        <x:v>748.155537</x:v>
       </x:c>
       <x:c r="I534" s="111" t="n">
-        <x:v>747.676579</x:v>
+        <x:v>748.327431</x:v>
       </x:c>
       <x:c r="J534" s="111" t="n">
-        <x:v>0.9999149538693789</x:v>
+        <x:v>0.9997702957383636</x:v>
       </x:c>
       <x:c r="K534" s="111" t="n">
         <x:v>0</x:v>
@@ -23818,16 +23816,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G535" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H535" s="111" t="n">
-        <x:v>747.642154</x:v>
+        <x:v>748.155797</x:v>
       </x:c>
       <x:c r="I535" s="111" t="n">
-        <x:v>747.713299</x:v>
+        <x:v>748.308601</x:v>
       </x:c>
       <x:c r="J535" s="111" t="n">
-        <x:v>0.9999048498935419</x:v>
+        <x:v>0.9997958008236231</x:v>
       </x:c>
       <x:c r="K535" s="111" t="n">
         <x:v>0</x:v>
@@ -23862,16 +23860,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G536" s="111" t="n">
-        <x:v>6.793125</x:v>
+        <x:v>6.785791</x:v>
       </x:c>
       <x:c r="H536" s="111" t="n">
-        <x:v>747.652554</x:v>
+        <x:v>748.159697</x:v>
       </x:c>
       <x:c r="I536" s="111" t="n">
-        <x:v>747.73959</x:v>
+        <x:v>748.30986</x:v>
       </x:c>
       <x:c r="J536" s="111" t="n">
-        <x:v>0.9998836011879483</x:v>
+        <x:v>0.9997993304538311</x:v>
       </x:c>
       <x:c r="K536" s="111" t="n">
         <x:v>0</x:v>
@@ -23906,22 +23904,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G537" s="111" t="n">
-        <x:v>2005.229903</x:v>
+        <x:v>2041.825422</x:v>
       </x:c>
       <x:c r="H537" s="111" t="n">
-        <x:v>4425.932113</x:v>
+        <x:v>4474.697559</x:v>
       </x:c>
       <x:c r="I537" s="111" t="n">
-        <x:v>4487.980669</x:v>
+        <x:v>4342.494409</x:v>
       </x:c>
       <x:c r="J537" s="111" t="n">
-        <x:v>0.986174504621067</x:v>
+        <x:v>1.030444057619511</x:v>
       </x:c>
       <x:c r="K537" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L537" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M537" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -23950,22 +23948,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G538" s="111" t="n">
-        <x:v>2005.229903</x:v>
+        <x:v>2041.825422</x:v>
       </x:c>
       <x:c r="H538" s="111" t="n">
-        <x:v>4425.932113</x:v>
+        <x:v>4474.697559</x:v>
       </x:c>
       <x:c r="I538" s="111" t="n">
-        <x:v>4487.980669</x:v>
+        <x:v>4342.494409</x:v>
       </x:c>
       <x:c r="J538" s="111" t="n">
-        <x:v>0.986174504621067</x:v>
+        <x:v>1.030444057619511</x:v>
       </x:c>
       <x:c r="K538" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L538" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M538" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -23994,22 +23992,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G539" s="111" t="n">
-        <x:v>2005.229903</x:v>
+        <x:v>2041.825422</x:v>
       </x:c>
       <x:c r="H539" s="111" t="n">
-        <x:v>4425.932113</x:v>
+        <x:v>4474.697559</x:v>
       </x:c>
       <x:c r="I539" s="111" t="n">
-        <x:v>4487.980669</x:v>
+        <x:v>4342.494409</x:v>
       </x:c>
       <x:c r="J539" s="111" t="n">
-        <x:v>0.986174504621067</x:v>
+        <x:v>1.030444057619511</x:v>
       </x:c>
       <x:c r="K539" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L539" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M539" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -24038,16 +24036,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G540" s="111" t="n">
-        <x:v>222.546405</x:v>
+        <x:v>224.171951</x:v>
       </x:c>
       <x:c r="H540" s="111" t="n">
-        <x:v>22.282275</x:v>
+        <x:v>21.998705</x:v>
       </x:c>
       <x:c r="I540" s="111" t="n">
-        <x:v>22.278085</x:v>
+        <x:v>21.978595</x:v>
       </x:c>
       <x:c r="J540" s="111" t="n">
-        <x:v>1.0001880772068155</x:v>
+        <x:v>1.0009149811441542</x:v>
       </x:c>
       <x:c r="K540" s="111" t="n">
         <x:v>0</x:v>
@@ -24082,22 +24080,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G541" s="111" t="n">
-        <x:v>43.426028</x:v>
+        <x:v>45.160803</x:v>
       </x:c>
       <x:c r="H541" s="111" t="n">
-        <x:v>55.912928</x:v>
+        <x:v>54.05989</x:v>
       </x:c>
       <x:c r="I541" s="111" t="n">
-        <x:v>55.907736</x:v>
+        <x:v>54.16931</x:v>
       </x:c>
       <x:c r="J541" s="111" t="n">
-        <x:v>1.00009286729121</x:v>
+        <x:v>0.9979800370357311</x:v>
       </x:c>
       <x:c r="K541" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L541" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M541" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -24126,16 +24124,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G542" s="111" t="n">
-        <x:v>48.937375</x:v>
+        <x:v>49.403326</x:v>
       </x:c>
       <x:c r="H542" s="111" t="n">
-        <x:v>20.690978</x:v>
+        <x:v>20.32831</x:v>
       </x:c>
       <x:c r="I542" s="111" t="n">
-        <x:v>20.583476</x:v>
+        <x:v>20.316439</x:v>
       </x:c>
       <x:c r="J542" s="111" t="n">
-        <x:v>1.0052227330310974</x:v>
+        <x:v>1.0005843051530832</x:v>
       </x:c>
       <x:c r="K542" s="111" t="n">
         <x:v>0</x:v>
@@ -24170,22 +24168,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G543" s="111" t="n">
-        <x:v>28.380237</x:v>
+        <x:v>28.351083</x:v>
       </x:c>
       <x:c r="H543" s="111" t="n">
-        <x:v>31.125232</x:v>
+        <x:v>31.297703</x:v>
       </x:c>
       <x:c r="I543" s="111" t="n">
-        <x:v>31.219093</x:v>
+        <x:v>31.126042</x:v>
       </x:c>
       <x:c r="J543" s="111" t="n">
-        <x:v>0.9969934744740983</x:v>
+        <x:v>1.005515028219778</x:v>
       </x:c>
       <x:c r="K543" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L543" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M543" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -24214,22 +24212,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G544" s="111" t="n">
-        <x:v>222.547135</x:v>
+        <x:v>224.223432</x:v>
       </x:c>
       <x:c r="H544" s="111" t="n">
-        <x:v>22.231674</x:v>
+        <x:v>22.035325</x:v>
       </x:c>
       <x:c r="I544" s="111" t="n">
-        <x:v>22.306106</x:v>
+        <x:v>22.003365</x:v>
       </x:c>
       <x:c r="J544" s="111" t="n">
-        <x:v>0.9966631558193081</x:v>
+        <x:v>1.0014525051054692</x:v>
       </x:c>
       <x:c r="K544" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L544" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M544" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -24258,22 +24256,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G545" s="111" t="n">
-        <x:v>5.256355</x:v>
+        <x:v>5.242636</x:v>
       </x:c>
       <x:c r="H545" s="111" t="n">
-        <x:v>0.608322</x:v>
+        <x:v>0.543291</x:v>
       </x:c>
       <x:c r="I545" s="111" t="n">
-        <x:v>0.552451</x:v>
+        <x:v>0.563602</x:v>
       </x:c>
       <x:c r="J545" s="111" t="n">
-        <x:v>1.1011329511576593</x:v>
+        <x:v>0.9639621576928399</x:v>
       </x:c>
       <x:c r="K545" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L545" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M545" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -24302,16 +24300,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G546" s="111" t="n">
-        <x:v>233.825178</x:v>
+        <x:v>233.013118</x:v>
       </x:c>
       <x:c r="H546" s="111" t="n">
-        <x:v>22.254135</x:v>
+        <x:v>21.953395</x:v>
       </x:c>
       <x:c r="I546" s="111" t="n">
-        <x:v>22.257315</x:v>
+        <x:v>22.007755</x:v>
       </x:c>
       <x:c r="J546" s="111" t="n">
-        <x:v>0.9998571256236434</x:v>
+        <x:v>0.9975299615976277</x:v>
       </x:c>
       <x:c r="K546" s="111" t="n">
         <x:v>0</x:v>
@@ -24346,16 +24344,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G547" s="111" t="n">
-        <x:v>167.699208</x:v>
+        <x:v>167.308924</x:v>
       </x:c>
       <x:c r="H547" s="111" t="n">
-        <x:v>900.981685</x:v>
+        <x:v>887.572848</x:v>
       </x:c>
       <x:c r="I547" s="111" t="n">
-        <x:v>914.36301</x:v>
+        <x:v>891.832081</x:v>
       </x:c>
       <x:c r="J547" s="111" t="n">
-        <x:v>0.9853654130212463</x:v>
+        <x:v>0.9952241760632515</x:v>
       </x:c>
       <x:c r="K547" s="111" t="n">
         <x:v>3.73778323855e-9</x:v>
@@ -24390,16 +24388,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G548" s="111" t="n">
-        <x:v>167.699208</x:v>
+        <x:v>167.308924</x:v>
       </x:c>
       <x:c r="H548" s="111" t="n">
-        <x:v>900.981685</x:v>
+        <x:v>887.572848</x:v>
       </x:c>
       <x:c r="I548" s="111" t="n">
-        <x:v>914.36301</x:v>
+        <x:v>891.832081</x:v>
       </x:c>
       <x:c r="J548" s="111" t="n">
-        <x:v>0.9853654130212463</x:v>
+        <x:v>0.9952241760632515</x:v>
       </x:c>
       <x:c r="K548" s="111" t="n">
         <x:v>3.73778323855e-9</x:v>
@@ -24434,16 +24432,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G549" s="111" t="n">
-        <x:v>167.699208</x:v>
+        <x:v>167.308924</x:v>
       </x:c>
       <x:c r="H549" s="111" t="n">
-        <x:v>900.981685</x:v>
+        <x:v>887.572848</x:v>
       </x:c>
       <x:c r="I549" s="111" t="n">
-        <x:v>914.36301</x:v>
+        <x:v>891.832081</x:v>
       </x:c>
       <x:c r="J549" s="111" t="n">
-        <x:v>0.9853654130212463</x:v>
+        <x:v>0.9952241760632515</x:v>
       </x:c>
       <x:c r="K549" s="111" t="n">
         <x:v>3.73778323855e-9</x:v>
@@ -24478,16 +24476,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G550" s="111" t="n">
-        <x:v>0.263164</x:v>
+        <x:v>0.258631</x:v>
       </x:c>
       <x:c r="H550" s="111" t="n">
-        <x:v>3.493641</x:v>
+        <x:v>3.14075</x:v>
       </x:c>
       <x:c r="I550" s="111" t="n">
-        <x:v>3.503071</x:v>
+        <x:v>3.24478</x:v>
       </x:c>
       <x:c r="J550" s="111" t="n">
-        <x:v>0.9973080762565191</x:v>
+        <x:v>0.9679392747736365</x:v>
       </x:c>
       <x:c r="K550" s="111" t="n">
         <x:v>0</x:v>
@@ -24522,16 +24520,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G551" s="111" t="n">
-        <x:v>0.263164</x:v>
+        <x:v>0.258631</x:v>
       </x:c>
       <x:c r="H551" s="111" t="n">
-        <x:v>3.493641</x:v>
+        <x:v>3.14075</x:v>
       </x:c>
       <x:c r="I551" s="111" t="n">
-        <x:v>3.503071</x:v>
+        <x:v>3.24478</x:v>
       </x:c>
       <x:c r="J551" s="111" t="n">
-        <x:v>0.9973080762565191</x:v>
+        <x:v>0.9679392747736365</x:v>
       </x:c>
       <x:c r="K551" s="111" t="n">
         <x:v>0</x:v>
@@ -24566,16 +24564,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G552" s="111" t="n">
-        <x:v>32.674083</x:v>
+        <x:v>32.733916</x:v>
       </x:c>
       <x:c r="H552" s="111" t="n">
-        <x:v>0.261645</x:v>
+        <x:v>0.26214</x:v>
       </x:c>
       <x:c r="I552" s="111" t="n">
-        <x:v>0.267525</x:v>
+        <x:v>0.262981</x:v>
       </x:c>
       <x:c r="J552" s="111" t="n">
-        <x:v>0.9780207457246987</x:v>
+        <x:v>0.9968020503382372</x:v>
       </x:c>
       <x:c r="K552" s="111" t="n">
         <x:v>0</x:v>
@@ -24610,22 +24608,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G553" s="111" t="n">
-        <x:v>26.422238</x:v>
+        <x:v>28.836975</x:v>
       </x:c>
       <x:c r="H553" s="111" t="n">
-        <x:v>0.980289</x:v>
+        <x:v>0.884103</x:v>
       </x:c>
       <x:c r="I553" s="111" t="n">
-        <x:v>0.893357</x:v>
+        <x:v>0.890213</x:v>
       </x:c>
       <x:c r="J553" s="111" t="n">
-        <x:v>1.097309362326595</x:v>
+        <x:v>0.9931364740797988</x:v>
       </x:c>
       <x:c r="K553" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L553" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M553" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=COVERED；有同名 HIP 头。</x:v>
@@ -24654,22 +24652,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G554" s="111" t="n">
-        <x:v>26.422238</x:v>
+        <x:v>28.836975</x:v>
       </x:c>
       <x:c r="H554" s="111" t="n">
-        <x:v>0.980289</x:v>
+        <x:v>0.884103</x:v>
       </x:c>
       <x:c r="I554" s="111" t="n">
-        <x:v>0.893357</x:v>
+        <x:v>0.890213</x:v>
       </x:c>
       <x:c r="J554" s="111" t="n">
-        <x:v>1.097309362326595</x:v>
+        <x:v>0.9931364740797988</x:v>
       </x:c>
       <x:c r="K554" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L554" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M554" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -24698,16 +24696,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G555" s="111" t="n">
-        <x:v>29.322926</x:v>
+        <x:v>29.347727</x:v>
       </x:c>
       <x:c r="H555" s="111" t="n">
-        <x:v>0.199434</x:v>
+        <x:v>0.198631</x:v>
       </x:c>
       <x:c r="I555" s="111" t="n">
-        <x:v>0.251975</x:v>
+        <x:v>0.202211</x:v>
       </x:c>
       <x:c r="J555" s="111" t="n">
-        <x:v>0.7914832820716341</x:v>
+        <x:v>0.9822957208064843</x:v>
       </x:c>
       <x:c r="K555" s="111" t="n">
         <x:v>0</x:v>
@@ -24742,16 +24740,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G556" s="111" t="n">
-        <x:v>36.332336</x:v>
+        <x:v>36.344977</x:v>
       </x:c>
       <x:c r="H556" s="111" t="n">
-        <x:v>0.199954</x:v>
+        <x:v>0.19654</x:v>
       </x:c>
       <x:c r="I556" s="111" t="n">
-        <x:v>0.252815</x:v>
+        <x:v>0.24539</x:v>
       </x:c>
       <x:c r="J556" s="111" t="n">
-        <x:v>0.7909103494650238</x:v>
+        <x:v>0.8009291332165125</x:v>
       </x:c>
       <x:c r="K556" s="111" t="n">
         <x:v>0</x:v>
@@ -24786,16 +24784,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G557" s="111" t="n">
-        <x:v>117.446278</x:v>
+        <x:v>117.401156</x:v>
       </x:c>
       <x:c r="H557" s="111" t="n">
-        <x:v>0.49636</x:v>
+        <x:v>0.455102</x:v>
       </x:c>
       <x:c r="I557" s="111" t="n">
-        <x:v>0.530301</x:v>
+        <x:v>0.473662</x:v>
       </x:c>
       <x:c r="J557" s="111" t="n">
-        <x:v>0.9359967263874668</x:v>
+        <x:v>0.9608159404807647</x:v>
       </x:c>
       <x:c r="K557" s="111" t="n">
         <x:v>0</x:v>
@@ -24830,16 +24828,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G558" s="111" t="n">
-        <x:v>1.616488</x:v>
+        <x:v>1.621675</x:v>
       </x:c>
       <x:c r="H558" s="111" t="n">
-        <x:v>0.343376</x:v>
+        <x:v>0.29524</x:v>
       </x:c>
       <x:c r="I558" s="111" t="n">
-        <x:v>0.341916</x:v>
+        <x:v>0.290181</x:v>
       </x:c>
       <x:c r="J558" s="111" t="n">
-        <x:v>1.0042700546333019</x:v>
+        <x:v>1.0174339463989717</x:v>
       </x:c>
       <x:c r="K558" s="111" t="n">
         <x:v>0</x:v>
@@ -24874,22 +24872,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G559" s="111" t="n">
-        <x:v>1.615608</x:v>
+        <x:v>1.619025</x:v>
       </x:c>
       <x:c r="H559" s="111" t="n">
-        <x:v>0.342566</x:v>
+        <x:v>0.327611</x:v>
       </x:c>
       <x:c r="I559" s="111" t="n">
-        <x:v>0.342976</x:v>
+        <x:v>0.295961</x:v>
       </x:c>
       <x:c r="J559" s="111" t="n">
-        <x:v>0.9988045810785594</x:v>
+        <x:v>1.1069397657123743</x:v>
       </x:c>
       <x:c r="K559" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L559" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M559" s="7" t="str">
         <x:v>混合精度已完成策略改造：碰撞前沿传播的时间值、front竞争和收敛判定保持FP64；float I/O不改变内部传播精度，离散front标签保持原语义。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND/CPU_REFERENCE；静态覆盖=COVERED；保留原接口语义。</x:v>
@@ -24918,22 +24916,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G560" s="111" t="n">
-        <x:v>1.625818</x:v>
+        <x:v>1.617835</x:v>
       </x:c>
       <x:c r="H560" s="111" t="n">
-        <x:v>0.342136</x:v>
+        <x:v>0.330921</x:v>
       </x:c>
       <x:c r="I560" s="111" t="n">
-        <x:v>0.357646</x:v>
+        <x:v>0.328291</x:v>
       </x:c>
       <x:c r="J560" s="111" t="n">
-        <x:v>0.9566330952953479</x:v>
+        <x:v>1.0080111851984976</x:v>
       </x:c>
       <x:c r="K560" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L560" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M560" s="7" t="str">
         <x:v>混合精度已完成策略改造：速度扩展的窄带传播、插值和迭代更新保持FP64；输出速度图I/O类型不变，不能把多步传播直接放在float缓冲区上。 DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=HIP_BACKEND/CPU_REFERENCE；静态覆盖=COVERED；保留原接口语义。</x:v>
@@ -24962,16 +24960,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G561" s="111" t="n">
-        <x:v>0.817394</x:v>
+        <x:v>0.813943</x:v>
       </x:c>
       <x:c r="H561" s="111" t="n">
-        <x:v>0.220143</x:v>
+        <x:v>0.21118</x:v>
       </x:c>
       <x:c r="I561" s="111" t="n">
-        <x:v>0.217984</x:v>
+        <x:v>0.209151</x:v>
       </x:c>
       <x:c r="J561" s="111" t="n">
-        <x:v>1.0099043966529653</x:v>
+        <x:v>1.0097011250245038</x:v>
       </x:c>
       <x:c r="K561" s="111" t="n">
         <x:v>0</x:v>
@@ -25198,16 +25196,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G568" s="111" t="n">
-        <x:v>1.628689</x:v>
+        <x:v>1.615285</x:v>
       </x:c>
       <x:c r="H568" s="111" t="n">
-        <x:v>0.310475</x:v>
+        <x:v>0.298271</x:v>
       </x:c>
       <x:c r="I568" s="111" t="n">
-        <x:v>0.341936</x:v>
+        <x:v>0.324761</x:v>
       </x:c>
       <x:c r="J568" s="111" t="n">
-        <x:v>0.9079915539750129</x:v>
+        <x:v>0.9184323240783222</x:v>
       </x:c>
       <x:c r="K568" s="111" t="n">
         <x:v>0</x:v>
@@ -25242,22 +25240,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G569" s="111" t="n">
-        <x:v>2005.229903</x:v>
+        <x:v>2041.825422</x:v>
       </x:c>
       <x:c r="H569" s="111" t="n">
-        <x:v>4425.932113</x:v>
+        <x:v>4474.697559</x:v>
       </x:c>
       <x:c r="I569" s="111" t="n">
-        <x:v>4487.980669</x:v>
+        <x:v>4342.494409</x:v>
       </x:c>
       <x:c r="J569" s="111" t="n">
-        <x:v>0.986174504621067</x:v>
+        <x:v>1.030444057619511</x:v>
       </x:c>
       <x:c r="K569" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L569" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M569" s="7" t="str">
         <x:v>不能做混合精度：需要多种子或训练标签，单张灰度切片给不出可重复的混合精度对比。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25286,22 +25284,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G570" s="111" t="n">
-        <x:v>2005.229903</x:v>
+        <x:v>2041.825422</x:v>
       </x:c>
       <x:c r="H570" s="111" t="n">
-        <x:v>4425.932113</x:v>
+        <x:v>4474.697559</x:v>
       </x:c>
       <x:c r="I570" s="111" t="n">
-        <x:v>4487.980669</x:v>
+        <x:v>4342.494409</x:v>
       </x:c>
       <x:c r="J570" s="111" t="n">
-        <x:v>0.986174504621067</x:v>
+        <x:v>1.030444057619511</x:v>
       </x:c>
       <x:c r="K570" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L570" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M570" s="7" t="str">
         <x:v>不能做混合精度：每个像素不是一个亮度，而是彩色、箭头（位移）或多个数。混合精度对比需要一张灰度亮度图，套不上。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25330,22 +25328,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G571" s="111" t="n">
-        <x:v>87.034493</x:v>
+        <x:v>87.308207</x:v>
       </x:c>
       <x:c r="H571" s="111" t="n">
-        <x:v>451.056471</x:v>
+        <x:v>445.093892</x:v>
       </x:c>
       <x:c r="I571" s="111" t="n">
-        <x:v>451.328028</x:v>
+        <x:v>444.891092</x:v>
       </x:c>
       <x:c r="J571" s="111" t="n">
-        <x:v>0.9993983156747357</x:v>
+        <x:v>1.0004558418984932</x:v>
       </x:c>
       <x:c r="K571" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L571" s="7" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M571" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25374,16 +25372,16 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G572" s="111" t="n">
-        <x:v>0.263164</x:v>
+        <x:v>0.258631</x:v>
       </x:c>
       <x:c r="H572" s="111" t="n">
-        <x:v>3.493641</x:v>
+        <x:v>3.14075</x:v>
       </x:c>
       <x:c r="I572" s="111" t="n">
-        <x:v>3.503071</x:v>
+        <x:v>3.24478</x:v>
       </x:c>
       <x:c r="J572" s="111" t="n">
-        <x:v>0.9973080762565191</x:v>
+        <x:v>0.9679392747736365</x:v>
       </x:c>
       <x:c r="K572" s="111" t="n">
         <x:v>0</x:v>
@@ -25418,16 +25416,16 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G573" s="111" t="n">
-        <x:v>859.837291</x:v>
+        <x:v>876.056844</x:v>
       </x:c>
       <x:c r="H573" s="111" t="n">
-        <x:v>1008.861204</x:v>
+        <x:v>945.041998</x:v>
       </x:c>
       <x:c r="I573" s="111" t="n">
-        <x:v>1009.356501</x:v>
+        <x:v>945.83219</x:v>
       </x:c>
       <x:c r="J573" s="111" t="n">
-        <x:v>0.9995092942884806</x:v>
+        <x:v>0.9991645537037601</x:v>
       </x:c>
       <x:c r="K573" s="111" t="n">
         <x:v>0</x:v>
@@ -25462,16 +25460,16 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G574" s="111" t="n">
-        <x:v>1.706729</x:v>
+        <x:v>1.728875</x:v>
       </x:c>
       <x:c r="H574" s="111" t="n">
-        <x:v>3.006052</x:v>
+        <x:v>2.789358</x:v>
       </x:c>
       <x:c r="I574" s="111" t="n">
-        <x:v>3.029313</x:v>
+        <x:v>2.825088</x:v>
       </x:c>
       <x:c r="J574" s="111" t="n">
-        <x:v>0.9923213613119541</x:v>
+        <x:v>0.9873526063612885</x:v>
       </x:c>
       <x:c r="K574" s="111" t="n">
         <x:v>0</x:v>
@@ -25506,22 +25504,22 @@
         <x:v>串行</x:v>
       </x:c>
       <x:c r="G575" s="111" t="n">
-        <x:v>97.489084</x:v>
+        <x:v>98.663881</x:v>
       </x:c>
       <x:c r="H575" s="111" t="n">
-        <x:v>53.011745</x:v>
+        <x:v>47.137669</x:v>
       </x:c>
       <x:c r="I575" s="111" t="n">
-        <x:v>52.870345</x:v>
+        <x:v>47.290979</x:v>
       </x:c>
       <x:c r="J575" s="111" t="n">
-        <x:v>1.0026744671327565</x:v>
+        <x:v>0.996758155503611</x:v>
       </x:c>
       <x:c r="K575" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L575" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M575" s="7" t="str">
         <x:v>不能做混合精度：这是串行算法：一步一步往外推，不会把图切成很多块一起算。表规定不测绑核，也不测混合精度。不是算错了，是这两项优化对它不适用。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25550,16 +25548,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G576" s="111" t="n">
-        <x:v>2.436252</x:v>
+        <x:v>2.430307</x:v>
       </x:c>
       <x:c r="H576" s="111" t="n">
-        <x:v>8.497147</x:v>
+        <x:v>8.414515</x:v>
       </x:c>
       <x:c r="I576" s="111" t="n">
-        <x:v>8.490087</x:v>
+        <x:v>8.410034</x:v>
       </x:c>
       <x:c r="J576" s="111" t="n">
-        <x:v>1.000831558027615</x:v>
+        <x:v>1.0005328159196503</x:v>
       </x:c>
       <x:c r="K576" s="111" t="n">
         <x:v>0</x:v>
@@ -25594,16 +25592,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G577" s="111" t="n">
-        <x:v>23.332376</x:v>
+        <x:v>23.334209</x:v>
       </x:c>
       <x:c r="H577" s="111" t="n">
-        <x:v>1.627572</x:v>
+        <x:v>1.626025</x:v>
       </x:c>
       <x:c r="I577" s="111" t="n">
-        <x:v>1.627232</x:v>
+        <x:v>1.625075</x:v>
       </x:c>
       <x:c r="J577" s="111" t="n">
-        <x:v>1.0002089437769168</x:v>
+        <x:v>1.0005845884036122</x:v>
       </x:c>
       <x:c r="K577" s="111" t="n">
         <x:v>0.038273277231</x:v>
@@ -25638,16 +25636,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G578" s="111" t="n">
-        <x:v>23.332376</x:v>
+        <x:v>23.334209</x:v>
       </x:c>
       <x:c r="H578" s="111" t="n">
-        <x:v>1.627572</x:v>
+        <x:v>1.626025</x:v>
       </x:c>
       <x:c r="I578" s="111" t="n">
-        <x:v>1.627232</x:v>
+        <x:v>1.625075</x:v>
       </x:c>
       <x:c r="J578" s="111" t="n">
-        <x:v>1.0002089437769168</x:v>
+        <x:v>1.0005845884036122</x:v>
       </x:c>
       <x:c r="K578" s="111" t="n">
         <x:v>0.038273277231</x:v>
@@ -25682,16 +25680,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G579" s="111" t="n">
-        <x:v>23.332376</x:v>
+        <x:v>23.334209</x:v>
       </x:c>
       <x:c r="H579" s="111" t="n">
-        <x:v>1.627572</x:v>
+        <x:v>1.626025</x:v>
       </x:c>
       <x:c r="I579" s="111" t="n">
-        <x:v>1.627232</x:v>
+        <x:v>1.625075</x:v>
       </x:c>
       <x:c r="J579" s="111" t="n">
-        <x:v>1.0002089437769168</x:v>
+        <x:v>1.0005845884036122</x:v>
       </x:c>
       <x:c r="K579" s="111" t="n">
         <x:v>0.038273277231</x:v>
@@ -25726,16 +25724,16 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G580" s="111" t="n">
-        <x:v>23.332376</x:v>
+        <x:v>23.334209</x:v>
       </x:c>
       <x:c r="H580" s="111" t="n">
-        <x:v>1.627572</x:v>
+        <x:v>1.626025</x:v>
       </x:c>
       <x:c r="I580" s="111" t="n">
-        <x:v>1.627232</x:v>
+        <x:v>1.625075</x:v>
       </x:c>
       <x:c r="J580" s="111" t="n">
-        <x:v>1.0002089437769168</x:v>
+        <x:v>1.0005845884036122</x:v>
       </x:c>
       <x:c r="K580" s="111" t="n">
         <x:v>0.038273277231</x:v>
@@ -25770,22 +25768,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G581" s="111" t="n">
-        <x:v>43.426028</x:v>
+        <x:v>45.160803</x:v>
       </x:c>
       <x:c r="H581" s="111" t="n">
-        <x:v>55.912928</x:v>
+        <x:v>54.05989</x:v>
       </x:c>
       <x:c r="I581" s="111" t="n">
-        <x:v>55.907736</x:v>
+        <x:v>54.16931</x:v>
       </x:c>
       <x:c r="J581" s="111" t="n">
-        <x:v>1.00009286729121</x:v>
+        <x:v>0.9979800370357311</x:v>
       </x:c>
       <x:c r="K581" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L581" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M581" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25814,22 +25812,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G582" s="111" t="n">
-        <x:v>43.426028</x:v>
+        <x:v>45.160803</x:v>
       </x:c>
       <x:c r="H582" s="111" t="n">
-        <x:v>55.912928</x:v>
+        <x:v>54.05989</x:v>
       </x:c>
       <x:c r="I582" s="111" t="n">
-        <x:v>55.907736</x:v>
+        <x:v>54.16931</x:v>
       </x:c>
       <x:c r="J582" s="111" t="n">
-        <x:v>1.00009286729121</x:v>
+        <x:v>0.9979800370357311</x:v>
       </x:c>
       <x:c r="K582" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L582" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M582" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25858,22 +25856,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G583" s="111" t="n">
-        <x:v>43.426028</x:v>
+        <x:v>45.160803</x:v>
       </x:c>
       <x:c r="H583" s="111" t="n">
-        <x:v>55.912928</x:v>
+        <x:v>54.05989</x:v>
       </x:c>
       <x:c r="I583" s="111" t="n">
-        <x:v>55.907736</x:v>
+        <x:v>54.16931</x:v>
       </x:c>
       <x:c r="J583" s="111" t="n">
-        <x:v>1.00009286729121</x:v>
+        <x:v>0.9979800370357311</x:v>
       </x:c>
       <x:c r="K583" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L583" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M583" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25902,22 +25900,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G584" s="111" t="n">
-        <x:v>43.426028</x:v>
+        <x:v>45.160803</x:v>
       </x:c>
       <x:c r="H584" s="111" t="n">
-        <x:v>55.912928</x:v>
+        <x:v>54.05989</x:v>
       </x:c>
       <x:c r="I584" s="111" t="n">
-        <x:v>55.907736</x:v>
+        <x:v>54.16931</x:v>
       </x:c>
       <x:c r="J584" s="111" t="n">
-        <x:v>1.00009286729121</x:v>
+        <x:v>0.9979800370357311</x:v>
       </x:c>
       <x:c r="K584" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L584" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M584" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25946,22 +25944,22 @@
         <x:v>并行</x:v>
       </x:c>
       <x:c r="G585" s="111" t="n">
-        <x:v>43.426028</x:v>
+        <x:v>45.160803</x:v>
       </x:c>
       <x:c r="H585" s="111" t="n">
-        <x:v>55.912928</x:v>
+        <x:v>54.05989</x:v>
       </x:c>
       <x:c r="I585" s="111" t="n">
-        <x:v>55.907736</x:v>
+        <x:v>54.16931</x:v>
       </x:c>
       <x:c r="J585" s="111" t="n">
-        <x:v>1.00009286729121</x:v>
+        <x:v>0.9979800370357311</x:v>
       </x:c>
       <x:c r="K585" s="111" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L585" s="7" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M585" s="7" t="str">
         <x:v>不能做混合精度：输出是整数标签或分区编号，不是连续亮度。换成单精度/双精度没有「更亮一点」可对比，故不填混合精度。。未发现独立 DCU/HIP 混精后端证据。DCU移植验收=通过（直接；禁止fallback=1）；混精扫描=NO_DCU_BACKEND；静态覆盖=NO_EVIDENCE；无同名 HIP 头。</x:v>
@@ -25973,7 +25971,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d393e1d482f4f7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raffb1e76fffc4f38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25983,7 +25981,7 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -26119,7 +26117,7 @@
         <x:v>1024×1024口径重测成功</x:v>
       </x:c>
       <x:c r="B17" s="104" t="n">
-        <x:v>104</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
@@ -26211,7 +26209,7 @@
         <x:v>不能做混精函数G:L已填实测或不适用</x:v>
       </x:c>
       <x:c r="B29" s="122" t="n">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
@@ -26224,10 +26222,10 @@
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="136" t="str">
-        <x:v>补充验证新增独立metric函数数</x:v>
+        <x:v>本次复测独立metric函数数</x:v>
       </x:c>
       <x:c r="B31" s="122" t="n">
-        <x:v>0</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
@@ -26246,34 +26244,34 @@
         <x:v>2026-10-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="24" customHeight="1">
+    <x:row r="34" ht="36" customHeight="1">
       <x:c r="A34" s="138" t="str">
         <x:v>本次复测范围</x:v>
       </x:c>
       <x:c r="B34" s="138" t="str">
-        <x:v>584个函数；95个统一测试入口；8个DCU数组任务</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="24" customHeight="1">
+        <x:v>584个函数；95个统一测试入口；8个DCU数组任务；OFF/ON双模式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="72" customHeight="1">
       <x:c r="A35" s="138" t="str">
         <x:v>本次复测结果</x:v>
       </x:c>
       <x:c r="B35" s="138" t="str">
-        <x:v>OFF独立metric=441；ON独立metric=440；混精加速比=435；误差=457</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="24" customHeight="1">
+        <x:v>独立metric=457；CPU时间=370；OFF DCU时间=369；ON DCU时间=370；OFF/ON双时间=369；误差=457；DCU混精加速比=369</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="138" t="str">
         <x:v>后续复测条件</x:v>
       </x:c>
       <x:c r="B36" s="138" t="str">
-        <x:v>对本轮未形成独立UNIFIED_METRIC的函数补充专用入口或单函数测试；本轮失败和超时记录不作为成功数据。</x:v>
+        <x:v>失败或无独立metric=127；缺失项不以失败码、超时或旧日志替代本轮结果。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb8b07d542a2408e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16ba78e9187e41bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26451,7 +26449,7 @@
         <x:v>本次重测状态</x:v>
       </x:c>
       <x:c r="B21" s="138" t="str">
-        <x:v>2026-10-06已在可申请DCU资源的计算节点完成584个函数的OFF/ON重测，8个数组任务全部结束。</x:v>
+        <x:v>2026-10-06完成584个函数的OFF/ON复测，8个数组任务全部结束。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="72" customHeight="1">
@@ -26459,7 +26457,7 @@
         <x:v>本次重测策略</x:v>
       </x:c>
       <x:c r="B22" s="138" t="str">
-        <x:v>按95个统一测试入口分组运行OFF和ON两轮；每个入口单独保存日志和退出状态；禁止CPU fallback；按函数名提取UNIFIED_METRIC并回填G-L。</x:v>
+        <x:v>按95个统一测试入口分别运行OFF和ON；禁止CPU fallback；按函数名提取UNIFIED_METRIC并回填G-L。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="72" customHeight="1">
@@ -26467,7 +26465,7 @@
         <x:v>本次数据更新原则</x:v>
       </x:c>
       <x:c r="B23" s="138" t="str">
-        <x:v>仅用本轮日志中实际产生的UNIFIED_METRIC更新对应单元格；失败、超时或没有独立metric的函数不以失败码、旧日志或CPU时间冒充本轮DCU结果。</x:v>
+        <x:v>本轮有457个函数产生独立metric，369个函数同时有OFF/ON DCU时间，457个函数有误差；缺失项保留原值或空白。</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="36" customHeight="1">
@@ -26531,13 +26529,13 @@
         <x:v>ARM对齐当前状态</x:v>
       </x:c>
       <x:c r="B31" s="142" t="str">
-        <x:v>脚本、数据契约和584条清单已加入ITK_DCU；历史G-L数据保留，待按新口径完成实际DCU复测后再回填新结果。</x:v>
+        <x:v>本轮已按实际DCU OFF/ON日志更新；未产生独立指标的函数不写入虚假数值。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5280d763d7384a52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dcb294b12004b91"/>
   </x:tableParts>
 </x:worksheet>
 </file>